--- a/Anexo Fluxo de Pagamento Nio x Onitel.xlsx
+++ b/Anexo Fluxo de Pagamento Nio x Onitel.xlsx
@@ -5,15 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/silvio/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/silvio/Library/CloudStorage/GoogleDrive-eucastrosilvio@gmail.com/Meu Drive/1A Grupo Tigon Drive/Grupo Tigon Estratégico/Vtal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5BF885-AB2C-6A4E-B31A-B3AACA054999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C7D73B-1E83-1E4E-B4BE-9D9F60D80936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="580" windowWidth="29040" windowHeight="15160" xr2:uid="{64F40452-A3D8-4C49-BFF5-9F85CDF9315C}"/>
+    <workbookView xWindow="-140" yWindow="580" windowWidth="29040" windowHeight="15120" activeTab="2" xr2:uid="{64F40452-A3D8-4C49-BFF5-9F85CDF9315C}"/>
   </bookViews>
   <sheets>
     <sheet name="Fluxo de pagamentos" sheetId="5" r:id="rId1"/>
+    <sheet name="Resumo Fluxo de Pagamentos" sheetId="6" r:id="rId2"/>
+    <sheet name="Escrow" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="102">
   <si>
     <t>Total</t>
   </si>
@@ -236,24 +238,129 @@
     <t>Setup</t>
   </si>
   <si>
-    <t>N3</t>
-  </si>
-  <si>
     <t>Deletar&gt;&gt;</t>
   </si>
   <si>
     <t>Valor das notas mensais</t>
+  </si>
+  <si>
+    <t>Cessão Imobilizado</t>
+  </si>
+  <si>
+    <t>Contrato FTTx</t>
+  </si>
+  <si>
+    <t>FTTx - Portas Iluminadas</t>
+  </si>
+  <si>
+    <t>Valor de Emissão de NFs</t>
+  </si>
+  <si>
+    <t>Rubricas</t>
+  </si>
+  <si>
+    <t>Carteira de Clientes</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Soma</t>
+  </si>
+  <si>
+    <t>Serviço Suporte N3</t>
+  </si>
+  <si>
+    <t>Emissão de NF e Reconheciento da Receita</t>
+  </si>
+  <si>
+    <t>Soma das Receitas</t>
+  </si>
+  <si>
+    <t>Documento Fiscal</t>
+  </si>
+  <si>
+    <t>Vencimento / Valor</t>
+  </si>
+  <si>
+    <t>Data Emissao NF / Valor</t>
+  </si>
+  <si>
+    <t>Não Emite NF</t>
+  </si>
+  <si>
+    <t>Empresa Prestadora</t>
+  </si>
+  <si>
+    <t>Telecom e Serviços</t>
+  </si>
+  <si>
+    <t>Soma dos Serviços</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>NF Telecom</t>
+  </si>
+  <si>
+    <t>NF-e Imobilizado</t>
+  </si>
+  <si>
+    <t>Carteira Clientes - Pago Diretamente à Onitel Telecom</t>
+  </si>
+  <si>
+    <t>Carteira Clientes - Rateio dos valores Pagos aos Credores</t>
+  </si>
+  <si>
+    <t>Soma dos Valores Carteira de Clientes -  Parte Onitel Telecom</t>
+  </si>
+  <si>
+    <t>Carteira Clientes - Pago Diretamente à Onitel Serviços</t>
+  </si>
+  <si>
+    <t>Valores da Conta Escrow</t>
+  </si>
+  <si>
+    <t>Destinatário dos Recursos</t>
+  </si>
+  <si>
+    <t>Cev Fibra Comércio</t>
+  </si>
+  <si>
+    <t>Connectx</t>
+  </si>
+  <si>
+    <t>Soma Connectx</t>
+  </si>
+  <si>
+    <t>Soma Onitel Telecom</t>
+  </si>
+  <si>
+    <t>Credor</t>
+  </si>
+  <si>
+    <t>Valor  dos Recursos Parte Onitel Telecom: 64,7%</t>
+  </si>
+  <si>
+    <t>Valor  dos Recursos Parte Onitel Serviços: 35,3%</t>
+  </si>
+  <si>
+    <t>Saldo que a Onitel Telecom deverá repassar para a Onitel Seriços</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0_);\(#,##0\);&quot;-&quot;_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0_)%;\(#,##0.0%\);&quot;-&quot;\%_)"/>
     <numFmt numFmtId="166" formatCode="#,##0.000000000000_);\(#,##0.000000000000\);&quot;-&quot;_)"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.000%"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -343,7 +450,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -384,13 +491,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -439,11 +563,65 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{4F5C782D-03EA-4627-B955-A97548275BA1}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{473AA21B-2A84-46B7-B869-3551EEC30F29}"/>
+    <cellStyle name="Porcentagem" xfId="4" builtinId="5"/>
+    <cellStyle name="Vírgula" xfId="3" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -681,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C652803B-A63C-43C3-A58C-94A47B809FCC}">
-  <dimension ref="B2:BH42"/>
+  <dimension ref="B2:BH43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.1640625" customWidth="1"/>
@@ -691,7 +869,7 @@
     <col min="5" max="5" width="20.6640625" customWidth="1"/>
     <col min="6" max="8" width="13.6640625" customWidth="1"/>
     <col min="9" max="9" width="21.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -729,6 +907,7 @@
     <col min="57" max="57" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="9.5" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="14" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:59" x14ac:dyDescent="0.2">
@@ -4259,7 +4438,7 @@
     </row>
     <row r="22" spans="2:60" s="16" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B22" s="19" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>48</v>
@@ -4927,10 +5106,10 @@
     </row>
     <row r="26" spans="2:60" s="16" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="19" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>57</v>
@@ -5104,7 +5283,7 @@
     </row>
     <row r="27" spans="2:60" s="16" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B27" s="19" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>64</v>
@@ -5281,10 +5460,10 @@
     </row>
     <row r="28" spans="2:60" s="16" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B28" s="19" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>56</v>
@@ -5932,6 +6111,7 @@
         <f t="shared" si="14"/>
         <v>24795000</v>
       </c>
+      <c r="BH31" s="1"/>
     </row>
     <row r="32" spans="2:60" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="K32" s="4">
@@ -6131,30 +6311,45 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="33" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
+      <c r="K35" s="1">
+        <f>K26</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B36" t="str">
+        <f>C26</f>
+        <v>FTTx - Portas Iluminadas</v>
+      </c>
       <c r="I36" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="K36" s="1">
+        <f>K26</f>
+        <v>0</v>
       </c>
       <c r="L36" s="1">
         <f>$N26/3</f>
@@ -6205,9 +6400,17 @@
         <v>936585</v>
       </c>
     </row>
-    <row r="37" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B37" t="str">
+        <f>C27</f>
+        <v>Setup</v>
+      </c>
       <c r="I37" s="26" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="K37" s="1">
+        <f>K27</f>
+        <v>21432792.093905725</v>
       </c>
       <c r="L37" s="1">
         <f>$N27/3</f>
@@ -6257,8 +6460,20 @@
         <f t="shared" si="19"/>
         <v>654957.52333333308</v>
       </c>
+      <c r="AI37" s="1">
+        <f>AI27</f>
+        <v>18325081.939113364</v>
+      </c>
     </row>
-    <row r="38" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B38" t="str">
+        <f>C28</f>
+        <v>Serviço Suporte N3</v>
+      </c>
+      <c r="K38" s="1">
+        <f>K28</f>
+        <v>0</v>
+      </c>
       <c r="L38" s="1">
         <f>$N28/3</f>
         <v>270220</v>
@@ -6308,7 +6523,7 @@
         <v>270220</v>
       </c>
     </row>
-    <row r="39" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -6325,9 +6540,12 @@
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="J40" s="35">
+        <f>J26</f>
+        <v>11239020</v>
+      </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -6337,9 +6555,11 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="J41" s="35">
+        <v>62400</v>
+      </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -6349,9 +6569,12 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="5:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="J42" s="35">
+        <f>J40/J41</f>
+        <v>180.11250000000001</v>
+      </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -6361,11 +6584,6741 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="J43" s="36">
+        <f>J42/12</f>
+        <v>15.009375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="K4:BG4" formulaRange="1"/>
   </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9126A784-1C98-9F45-AB74-8C05D98CDB5F}">
+  <dimension ref="A1:CD51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="17" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="11" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="40" width="11" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="52" width="11" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="K1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="M1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="O1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="P1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="S1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="T1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="U1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="V1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="W1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="X1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AU1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AZ1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="BA1" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="28">
+        <v>46230</v>
+      </c>
+      <c r="F2" s="28">
+        <v>46265</v>
+      </c>
+      <c r="G2" s="28">
+        <v>46295</v>
+      </c>
+      <c r="H2" s="28">
+        <v>46326</v>
+      </c>
+      <c r="I2" s="28">
+        <v>46356</v>
+      </c>
+      <c r="J2" s="28">
+        <v>46387</v>
+      </c>
+      <c r="K2" s="28">
+        <v>46418</v>
+      </c>
+      <c r="L2" s="28">
+        <v>46446</v>
+      </c>
+      <c r="M2" s="28">
+        <v>46477</v>
+      </c>
+      <c r="N2" s="28">
+        <v>46507</v>
+      </c>
+      <c r="O2" s="28">
+        <v>46538</v>
+      </c>
+      <c r="P2" s="28">
+        <v>46568</v>
+      </c>
+      <c r="Q2" s="28">
+        <v>46599</v>
+      </c>
+      <c r="R2" s="28">
+        <v>46630</v>
+      </c>
+      <c r="S2" s="28">
+        <v>46660</v>
+      </c>
+      <c r="T2" s="28">
+        <v>46691</v>
+      </c>
+      <c r="U2" s="28">
+        <v>46721</v>
+      </c>
+      <c r="V2" s="28">
+        <v>46752</v>
+      </c>
+      <c r="W2" s="28">
+        <v>46783</v>
+      </c>
+      <c r="X2" s="28">
+        <v>46812</v>
+      </c>
+      <c r="Y2" s="28">
+        <v>46843</v>
+      </c>
+      <c r="Z2" s="28">
+        <v>46873</v>
+      </c>
+      <c r="AA2" s="28">
+        <v>46904</v>
+      </c>
+      <c r="AB2" s="28">
+        <v>46934</v>
+      </c>
+      <c r="AC2" s="28">
+        <v>46965</v>
+      </c>
+      <c r="AD2" s="28">
+        <v>46996</v>
+      </c>
+      <c r="AE2" s="28">
+        <v>47026</v>
+      </c>
+      <c r="AF2" s="28">
+        <v>47057</v>
+      </c>
+      <c r="AG2" s="28">
+        <v>47087</v>
+      </c>
+      <c r="AH2" s="28">
+        <v>47118</v>
+      </c>
+      <c r="AI2" s="28">
+        <v>47149</v>
+      </c>
+      <c r="AJ2" s="28">
+        <v>47177</v>
+      </c>
+      <c r="AK2" s="28">
+        <v>47208</v>
+      </c>
+      <c r="AL2" s="28">
+        <v>47238</v>
+      </c>
+      <c r="AM2" s="28">
+        <v>47269</v>
+      </c>
+      <c r="AN2" s="28">
+        <v>47299</v>
+      </c>
+      <c r="AO2" s="28">
+        <v>47330</v>
+      </c>
+      <c r="AP2" s="28">
+        <v>47361</v>
+      </c>
+      <c r="AQ2" s="28">
+        <v>47391</v>
+      </c>
+      <c r="AR2" s="28">
+        <v>47422</v>
+      </c>
+      <c r="AS2" s="28">
+        <v>47452</v>
+      </c>
+      <c r="AT2" s="28">
+        <v>47483</v>
+      </c>
+      <c r="AU2" s="28">
+        <v>47514</v>
+      </c>
+      <c r="AV2" s="28">
+        <v>47542</v>
+      </c>
+      <c r="AW2" s="28">
+        <v>47573</v>
+      </c>
+      <c r="AX2" s="28">
+        <v>47603</v>
+      </c>
+      <c r="AY2" s="28">
+        <v>47634</v>
+      </c>
+      <c r="AZ2" s="28">
+        <v>47664</v>
+      </c>
+      <c r="BA2" s="28">
+        <v>47695</v>
+      </c>
+      <c r="BB2" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
+      <c r="BX2" s="28"/>
+      <c r="BY2" s="28"/>
+      <c r="BZ2" s="28"/>
+      <c r="CA2" s="28"/>
+      <c r="CB2" s="28"/>
+      <c r="CC2" s="28"/>
+      <c r="CD2" s="28"/>
+    </row>
+    <row r="3" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="40">
+        <f>'Fluxo de pagamentos'!J19</f>
+        <v>77495078.956980914</v>
+      </c>
+      <c r="E3" s="29">
+        <f>'Fluxo de pagamentos'!K19</f>
+        <v>15924927.176094271</v>
+      </c>
+      <c r="F3" s="29">
+        <f>'Fluxo de pagamentos'!L19</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="29">
+        <f>'Fluxo de pagamentos'!M19</f>
+        <v>772015.09</v>
+      </c>
+      <c r="H3" s="29">
+        <f>'Fluxo de pagamentos'!N19</f>
+        <v>852023.41999999993</v>
+      </c>
+      <c r="I3" s="29">
+        <f>'Fluxo de pagamentos'!O19</f>
+        <v>772015.09</v>
+      </c>
+      <c r="J3" s="29">
+        <f>'Fluxo de pagamentos'!P19</f>
+        <v>540113.11</v>
+      </c>
+      <c r="K3" s="29">
+        <f>'Fluxo de pagamentos'!Q19</f>
+        <v>460129.27999999997</v>
+      </c>
+      <c r="L3" s="29">
+        <f>'Fluxo de pagamentos'!R19</f>
+        <v>537811.52</v>
+      </c>
+      <c r="M3" s="29">
+        <f>'Fluxo de pagamentos'!S19</f>
+        <v>443632.36</v>
+      </c>
+      <c r="N3" s="29">
+        <f>'Fluxo de pagamentos'!T19</f>
+        <v>522031.42</v>
+      </c>
+      <c r="O3" s="29">
+        <f>'Fluxo de pagamentos'!U19</f>
+        <v>204484.7</v>
+      </c>
+      <c r="P3" s="29">
+        <f>'Fluxo de pagamentos'!V19</f>
+        <v>204493.03</v>
+      </c>
+      <c r="Q3" s="29">
+        <f>'Fluxo de pagamentos'!W19</f>
+        <v>204484.7</v>
+      </c>
+      <c r="R3" s="29">
+        <f>'Fluxo de pagamentos'!X19</f>
+        <v>204493.03</v>
+      </c>
+      <c r="S3" s="29">
+        <f>'Fluxo de pagamentos'!Y19</f>
+        <v>201801.96</v>
+      </c>
+      <c r="T3" s="29">
+        <f>'Fluxo de pagamentos'!Z19</f>
+        <v>201810.33</v>
+      </c>
+      <c r="U3" s="29">
+        <f>'Fluxo de pagamentos'!AA19</f>
+        <v>85143.59</v>
+      </c>
+      <c r="V3" s="29">
+        <f>'Fluxo de pagamentos'!AB19</f>
+        <v>85143.59</v>
+      </c>
+      <c r="W3" s="29">
+        <f>'Fluxo de pagamentos'!AC19</f>
+        <v>82669.48000000001</v>
+      </c>
+      <c r="X3" s="29">
+        <f>'Fluxo de pagamentos'!AD19</f>
+        <v>80301.69</v>
+      </c>
+      <c r="Y3" s="29">
+        <f>'Fluxo de pagamentos'!AE19</f>
+        <v>80301.69</v>
+      </c>
+      <c r="Z3" s="29">
+        <f>'Fluxo de pagamentos'!AF19</f>
+        <v>80301.69</v>
+      </c>
+      <c r="AA3" s="29">
+        <f>'Fluxo de pagamentos'!AG19</f>
+        <v>0</v>
+      </c>
+      <c r="AB3" s="29">
+        <f>'Fluxo de pagamentos'!AH19</f>
+        <v>0</v>
+      </c>
+      <c r="AC3" s="29">
+        <f>'Fluxo de pagamentos'!AI19</f>
+        <v>5364951.0108866403</v>
+      </c>
+      <c r="AD3" s="29">
+        <f>'Fluxo de pagamentos'!AJ19</f>
+        <v>0</v>
+      </c>
+      <c r="AE3" s="29">
+        <f>'Fluxo de pagamentos'!AK19</f>
+        <v>0</v>
+      </c>
+      <c r="AF3" s="29">
+        <f>'Fluxo de pagamentos'!AL19</f>
+        <v>0</v>
+      </c>
+      <c r="AG3" s="29">
+        <f>'Fluxo de pagamentos'!AM19</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="29">
+        <f>'Fluxo de pagamentos'!AN19</f>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="29">
+        <f>'Fluxo de pagamentos'!AO19</f>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="29">
+        <f>'Fluxo de pagamentos'!AP19</f>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="29">
+        <f>'Fluxo de pagamentos'!AQ19</f>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="29">
+        <f>'Fluxo de pagamentos'!AR19</f>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="29">
+        <f>'Fluxo de pagamentos'!AS19</f>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="29">
+        <f>'Fluxo de pagamentos'!AT19</f>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="29">
+        <f>'Fluxo de pagamentos'!AU19</f>
+        <v>24795000</v>
+      </c>
+      <c r="AP3" s="29">
+        <f>'Fluxo de pagamentos'!AV19</f>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="29">
+        <f>'Fluxo de pagamentos'!AW19</f>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="29">
+        <f>'Fluxo de pagamentos'!AX19</f>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="29">
+        <f>'Fluxo de pagamentos'!AY19</f>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="29">
+        <f>'Fluxo de pagamentos'!AZ19</f>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="29">
+        <f>'Fluxo de pagamentos'!BA19</f>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="29">
+        <f>'Fluxo de pagamentos'!BB19</f>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="29">
+        <f>'Fluxo de pagamentos'!BC19</f>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="29">
+        <f>'Fluxo de pagamentos'!BD19</f>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="29">
+        <f>'Fluxo de pagamentos'!BE19</f>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="29">
+        <f>'Fluxo de pagamentos'!BF19</f>
+        <v>0</v>
+      </c>
+      <c r="BA3" s="29">
+        <f>'Fluxo de pagamentos'!BG19</f>
+        <v>24795000</v>
+      </c>
+      <c r="BB3" s="30">
+        <f>SUM(E3:BA3)</f>
+        <v>77495078.956980914</v>
+      </c>
+    </row>
+    <row r="4" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="str">
+        <f>'Fluxo de pagamentos'!B22</f>
+        <v>Cessão Imobilizado</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="40">
+        <f>'Fluxo de pagamentos'!K23</f>
+        <v>28762280.73</v>
+      </c>
+      <c r="E4" s="29">
+        <f>'Fluxo de pagamentos'!K22</f>
+        <v>28762280.73</v>
+      </c>
+      <c r="F4" s="29">
+        <f>'Fluxo de pagamentos'!L22</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="29">
+        <f>'Fluxo de pagamentos'!M22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="29">
+        <f>'Fluxo de pagamentos'!N22</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="29">
+        <f>'Fluxo de pagamentos'!O22</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="29">
+        <f>'Fluxo de pagamentos'!P22</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="29">
+        <f>'Fluxo de pagamentos'!Q22</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="29">
+        <f>'Fluxo de pagamentos'!R22</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="29">
+        <f>'Fluxo de pagamentos'!S22</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="29">
+        <f>'Fluxo de pagamentos'!T22</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="29">
+        <f>'Fluxo de pagamentos'!U22</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="29">
+        <f>'Fluxo de pagamentos'!V22</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="29">
+        <f>'Fluxo de pagamentos'!W22</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="29">
+        <f>'Fluxo de pagamentos'!X22</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="29">
+        <f>'Fluxo de pagamentos'!Y22</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="29">
+        <f>'Fluxo de pagamentos'!Z22</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="29">
+        <f>'Fluxo de pagamentos'!AA22</f>
+        <v>0</v>
+      </c>
+      <c r="V4" s="29">
+        <f>'Fluxo de pagamentos'!AB22</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="29">
+        <f>'Fluxo de pagamentos'!AC22</f>
+        <v>0</v>
+      </c>
+      <c r="X4" s="29">
+        <f>'Fluxo de pagamentos'!AD22</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="29">
+        <f>'Fluxo de pagamentos'!AE22</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="29">
+        <f>'Fluxo de pagamentos'!AF22</f>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="29">
+        <f>'Fluxo de pagamentos'!AG22</f>
+        <v>0</v>
+      </c>
+      <c r="AB4" s="29">
+        <f>'Fluxo de pagamentos'!AH22</f>
+        <v>0</v>
+      </c>
+      <c r="AC4" s="29">
+        <f>'Fluxo de pagamentos'!AI22</f>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="29">
+        <f>'Fluxo de pagamentos'!AJ22</f>
+        <v>0</v>
+      </c>
+      <c r="AE4" s="29">
+        <f>'Fluxo de pagamentos'!AK22</f>
+        <v>0</v>
+      </c>
+      <c r="AF4" s="29">
+        <f>'Fluxo de pagamentos'!AL22</f>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="29">
+        <f>'Fluxo de pagamentos'!AM22</f>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="29">
+        <f>'Fluxo de pagamentos'!AN22</f>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="29">
+        <f>'Fluxo de pagamentos'!AO22</f>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="29">
+        <f>'Fluxo de pagamentos'!AP22</f>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="29">
+        <f>'Fluxo de pagamentos'!AQ22</f>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="29">
+        <f>'Fluxo de pagamentos'!AR22</f>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="29">
+        <f>'Fluxo de pagamentos'!AS22</f>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="29">
+        <f>'Fluxo de pagamentos'!AT22</f>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="29">
+        <f>'Fluxo de pagamentos'!AU22</f>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="29">
+        <f>'Fluxo de pagamentos'!AV22</f>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="29">
+        <f>'Fluxo de pagamentos'!AW22</f>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="29">
+        <f>'Fluxo de pagamentos'!AX22</f>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="29">
+        <f>'Fluxo de pagamentos'!AY22</f>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="29">
+        <f>'Fluxo de pagamentos'!AZ22</f>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="29">
+        <f>'Fluxo de pagamentos'!BA22</f>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="29">
+        <f>'Fluxo de pagamentos'!BB22</f>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="29">
+        <f>'Fluxo de pagamentos'!BC22</f>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="29">
+        <f>'Fluxo de pagamentos'!BD22</f>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="29">
+        <f>'Fluxo de pagamentos'!BE22</f>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="29">
+        <f>'Fluxo de pagamentos'!BF22</f>
+        <v>0</v>
+      </c>
+      <c r="BA4" s="29">
+        <f>'Fluxo de pagamentos'!BG22</f>
+        <v>0</v>
+      </c>
+      <c r="BB4" s="30">
+        <f>SUM(E4:BA4)</f>
+        <v>28762280.73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="str">
+        <f>'Fluxo de pagamentos'!C26</f>
+        <v>FTTx - Portas Iluminadas</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="40">
+        <f>'Fluxo de pagamentos'!J26</f>
+        <v>11239020</v>
+      </c>
+      <c r="E5" s="29">
+        <f>'Fluxo de pagamentos'!K26</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="29">
+        <f>'Fluxo de pagamentos'!L26</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="29">
+        <f>'Fluxo de pagamentos'!M26</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="29">
+        <f>'Fluxo de pagamentos'!N26</f>
+        <v>2809755</v>
+      </c>
+      <c r="I5" s="29">
+        <f>'Fluxo de pagamentos'!O26</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="29">
+        <f>'Fluxo de pagamentos'!P26</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="29">
+        <f>'Fluxo de pagamentos'!Q26</f>
+        <v>2809755</v>
+      </c>
+      <c r="L5" s="29">
+        <f>'Fluxo de pagamentos'!R26</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="29">
+        <f>'Fluxo de pagamentos'!S26</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="29">
+        <f>'Fluxo de pagamentos'!T26</f>
+        <v>2809755</v>
+      </c>
+      <c r="O5" s="29">
+        <f>'Fluxo de pagamentos'!U26</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="29">
+        <f>'Fluxo de pagamentos'!V26</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="29">
+        <f>'Fluxo de pagamentos'!W26</f>
+        <v>2809755</v>
+      </c>
+      <c r="R5" s="29">
+        <f>'Fluxo de pagamentos'!X26</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="29">
+        <f>'Fluxo de pagamentos'!Y26</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="29">
+        <f>'Fluxo de pagamentos'!Z26</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="29">
+        <f>'Fluxo de pagamentos'!AA26</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="29">
+        <f>'Fluxo de pagamentos'!AB26</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="29">
+        <f>'Fluxo de pagamentos'!AC26</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="29">
+        <f>'Fluxo de pagamentos'!AD26</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="29">
+        <f>'Fluxo de pagamentos'!AE26</f>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="29">
+        <f>'Fluxo de pagamentos'!AF26</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="29">
+        <f>'Fluxo de pagamentos'!AG26</f>
+        <v>0</v>
+      </c>
+      <c r="AB5" s="29">
+        <f>'Fluxo de pagamentos'!AH26</f>
+        <v>0</v>
+      </c>
+      <c r="AC5" s="29">
+        <f>'Fluxo de pagamentos'!AI26</f>
+        <v>0</v>
+      </c>
+      <c r="AD5" s="29">
+        <f>'Fluxo de pagamentos'!AJ26</f>
+        <v>0</v>
+      </c>
+      <c r="AE5" s="29">
+        <f>'Fluxo de pagamentos'!AK26</f>
+        <v>0</v>
+      </c>
+      <c r="AF5" s="29">
+        <f>'Fluxo de pagamentos'!AL26</f>
+        <v>0</v>
+      </c>
+      <c r="AG5" s="29">
+        <f>'Fluxo de pagamentos'!AM26</f>
+        <v>0</v>
+      </c>
+      <c r="AH5" s="29">
+        <f>'Fluxo de pagamentos'!AN26</f>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="29">
+        <f>'Fluxo de pagamentos'!AO26</f>
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="29">
+        <f>'Fluxo de pagamentos'!AP26</f>
+        <v>0</v>
+      </c>
+      <c r="AK5" s="29">
+        <f>'Fluxo de pagamentos'!AQ26</f>
+        <v>0</v>
+      </c>
+      <c r="AL5" s="29">
+        <f>'Fluxo de pagamentos'!AR26</f>
+        <v>0</v>
+      </c>
+      <c r="AM5" s="29">
+        <f>'Fluxo de pagamentos'!AS26</f>
+        <v>0</v>
+      </c>
+      <c r="AN5" s="29">
+        <f>'Fluxo de pagamentos'!AT26</f>
+        <v>0</v>
+      </c>
+      <c r="AO5" s="29">
+        <f>'Fluxo de pagamentos'!AU26</f>
+        <v>0</v>
+      </c>
+      <c r="AP5" s="29">
+        <f>'Fluxo de pagamentos'!AV26</f>
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="29">
+        <f>'Fluxo de pagamentos'!AW26</f>
+        <v>0</v>
+      </c>
+      <c r="AR5" s="29">
+        <f>'Fluxo de pagamentos'!AX26</f>
+        <v>0</v>
+      </c>
+      <c r="AS5" s="29">
+        <f>'Fluxo de pagamentos'!AY26</f>
+        <v>0</v>
+      </c>
+      <c r="AT5" s="29">
+        <f>'Fluxo de pagamentos'!AZ26</f>
+        <v>0</v>
+      </c>
+      <c r="AU5" s="29">
+        <f>'Fluxo de pagamentos'!BA26</f>
+        <v>0</v>
+      </c>
+      <c r="AV5" s="29">
+        <f>'Fluxo de pagamentos'!BB26</f>
+        <v>0</v>
+      </c>
+      <c r="AW5" s="29">
+        <f>'Fluxo de pagamentos'!BC26</f>
+        <v>0</v>
+      </c>
+      <c r="AX5" s="29">
+        <f>'Fluxo de pagamentos'!BD26</f>
+        <v>0</v>
+      </c>
+      <c r="AY5" s="29">
+        <f>'Fluxo de pagamentos'!BE26</f>
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="29">
+        <f>'Fluxo de pagamentos'!BF26</f>
+        <v>0</v>
+      </c>
+      <c r="BA5" s="29">
+        <f>'Fluxo de pagamentos'!BG26</f>
+        <v>0</v>
+      </c>
+      <c r="BB5" s="30">
+        <f>SUM(E5:BA5)</f>
+        <v>11239020</v>
+      </c>
+    </row>
+    <row r="6" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A6" s="39" t="str">
+        <f>'Fluxo de pagamentos'!C27</f>
+        <v>Setup</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="40">
+        <f>'Fluxo de pagamentos'!J27</f>
+        <v>44560980.313019089</v>
+      </c>
+      <c r="E6" s="29">
+        <f>'Fluxo de pagamentos'!K27</f>
+        <v>21432792.093905725</v>
+      </c>
+      <c r="F6" s="29">
+        <f>'Fluxo de pagamentos'!L27</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="29">
+        <f>'Fluxo de pagamentos'!M27</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="29">
+        <f>'Fluxo de pagamentos'!N27</f>
+        <v>957296.49000000022</v>
+      </c>
+      <c r="I6" s="29">
+        <f>'Fluxo de pagamentos'!O27</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="29">
+        <f>'Fluxo de pagamentos'!P27</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="29">
+        <f>'Fluxo de pagamentos'!Q27</f>
+        <v>806077.51999999955</v>
+      </c>
+      <c r="L6" s="29">
+        <f>'Fluxo de pagamentos'!R27</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="29">
+        <f>'Fluxo de pagamentos'!S27</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
+        <f>'Fluxo de pagamentos'!T27</f>
+        <v>1074859.7000000002</v>
+      </c>
+      <c r="O6" s="29">
+        <f>'Fluxo de pagamentos'!U27</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="29">
+        <f>'Fluxo de pagamentos'!V27</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="29">
+        <f>'Fluxo de pagamentos'!W27</f>
+        <v>1964872.5699999994</v>
+      </c>
+      <c r="R6" s="29">
+        <f>'Fluxo de pagamentos'!X27</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="29">
+        <f>'Fluxo de pagamentos'!Y27</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="29">
+        <f>'Fluxo de pagamentos'!Z27</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="29">
+        <f>'Fluxo de pagamentos'!AA27</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="29">
+        <f>'Fluxo de pagamentos'!AB27</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="29">
+        <f>'Fluxo de pagamentos'!AC27</f>
+        <v>0</v>
+      </c>
+      <c r="X6" s="29">
+        <f>'Fluxo de pagamentos'!AD27</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="29">
+        <f>'Fluxo de pagamentos'!AE27</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="29">
+        <f>'Fluxo de pagamentos'!AF27</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="29">
+        <f>'Fluxo de pagamentos'!AG27</f>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="29">
+        <f>'Fluxo de pagamentos'!AH27</f>
+        <v>0</v>
+      </c>
+      <c r="AC6" s="29">
+        <f>'Fluxo de pagamentos'!AI27</f>
+        <v>18325081.939113364</v>
+      </c>
+      <c r="AD6" s="29">
+        <f>'Fluxo de pagamentos'!AJ27</f>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="29">
+        <f>'Fluxo de pagamentos'!AK27</f>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="29">
+        <f>'Fluxo de pagamentos'!AL27</f>
+        <v>0</v>
+      </c>
+      <c r="AG6" s="29">
+        <f>'Fluxo de pagamentos'!AM27</f>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="29">
+        <f>'Fluxo de pagamentos'!AN27</f>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="29">
+        <f>'Fluxo de pagamentos'!AO27</f>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="29">
+        <f>'Fluxo de pagamentos'!AP27</f>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="29">
+        <f>'Fluxo de pagamentos'!AQ27</f>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="29">
+        <f>'Fluxo de pagamentos'!AR27</f>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="29">
+        <f>'Fluxo de pagamentos'!AS27</f>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="29">
+        <f>'Fluxo de pagamentos'!AT27</f>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="29">
+        <f>'Fluxo de pagamentos'!AU27</f>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="29">
+        <f>'Fluxo de pagamentos'!AV27</f>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="29">
+        <f>'Fluxo de pagamentos'!AW27</f>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="29">
+        <f>'Fluxo de pagamentos'!AX27</f>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="29">
+        <f>'Fluxo de pagamentos'!AY27</f>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="29">
+        <f>'Fluxo de pagamentos'!AZ27</f>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="29">
+        <f>'Fluxo de pagamentos'!BA27</f>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="29">
+        <f>'Fluxo de pagamentos'!BB27</f>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="29">
+        <f>'Fluxo de pagamentos'!BC27</f>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="29">
+        <f>'Fluxo de pagamentos'!BD27</f>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="29">
+        <f>'Fluxo de pagamentos'!BE27</f>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="29">
+        <f>'Fluxo de pagamentos'!BF27</f>
+        <v>0</v>
+      </c>
+      <c r="BA6" s="29">
+        <f>'Fluxo de pagamentos'!BG27</f>
+        <v>0</v>
+      </c>
+      <c r="BB6" s="30">
+        <f>SUM(E6:BA6)</f>
+        <v>44560980.313019089</v>
+      </c>
+    </row>
+    <row r="7" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A7" s="39" t="str">
+        <f>'Fluxo de pagamentos'!C28</f>
+        <v>Serviço Suporte N3</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="40">
+        <f>'Fluxo de pagamentos'!J28</f>
+        <v>3242640</v>
+      </c>
+      <c r="E7" s="29">
+        <f>'Fluxo de pagamentos'!K28</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="29">
+        <f>'Fluxo de pagamentos'!L28</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="29">
+        <f>'Fluxo de pagamentos'!M28</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="29">
+        <f>'Fluxo de pagamentos'!N28</f>
+        <v>810660</v>
+      </c>
+      <c r="I7" s="29">
+        <f>'Fluxo de pagamentos'!O28</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="29">
+        <f>'Fluxo de pagamentos'!P28</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="29">
+        <f>'Fluxo de pagamentos'!Q28</f>
+        <v>810660</v>
+      </c>
+      <c r="L7" s="29">
+        <f>'Fluxo de pagamentos'!R28</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="29">
+        <f>'Fluxo de pagamentos'!S28</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
+        <f>'Fluxo de pagamentos'!T28</f>
+        <v>810660</v>
+      </c>
+      <c r="O7" s="29">
+        <f>'Fluxo de pagamentos'!U28</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="29">
+        <f>'Fluxo de pagamentos'!V28</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="29">
+        <f>'Fluxo de pagamentos'!W28</f>
+        <v>810660</v>
+      </c>
+      <c r="R7" s="29">
+        <f>'Fluxo de pagamentos'!X28</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="29">
+        <f>'Fluxo de pagamentos'!Y28</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="29">
+        <f>'Fluxo de pagamentos'!Z28</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="29">
+        <f>'Fluxo de pagamentos'!AA28</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="29">
+        <f>'Fluxo de pagamentos'!AB28</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="29">
+        <f>'Fluxo de pagamentos'!AC28</f>
+        <v>0</v>
+      </c>
+      <c r="X7" s="29">
+        <f>'Fluxo de pagamentos'!AD28</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="29">
+        <f>'Fluxo de pagamentos'!AE28</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="29">
+        <f>'Fluxo de pagamentos'!AF28</f>
+        <v>0</v>
+      </c>
+      <c r="AA7" s="29">
+        <f>'Fluxo de pagamentos'!AG28</f>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="29">
+        <f>'Fluxo de pagamentos'!AH28</f>
+        <v>0</v>
+      </c>
+      <c r="AC7" s="29">
+        <f>'Fluxo de pagamentos'!AI28</f>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="29">
+        <f>'Fluxo de pagamentos'!AJ28</f>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="29">
+        <f>'Fluxo de pagamentos'!AK28</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="29">
+        <f>'Fluxo de pagamentos'!AL28</f>
+        <v>0</v>
+      </c>
+      <c r="AG7" s="29">
+        <f>'Fluxo de pagamentos'!AM28</f>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="29">
+        <f>'Fluxo de pagamentos'!AN28</f>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="29">
+        <f>'Fluxo de pagamentos'!AO28</f>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="29">
+        <f>'Fluxo de pagamentos'!AP28</f>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="29">
+        <f>'Fluxo de pagamentos'!AQ28</f>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="29">
+        <f>'Fluxo de pagamentos'!AR28</f>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="29">
+        <f>'Fluxo de pagamentos'!AS28</f>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="29">
+        <f>'Fluxo de pagamentos'!AT28</f>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="29">
+        <f>'Fluxo de pagamentos'!AU28</f>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="29">
+        <f>'Fluxo de pagamentos'!AV28</f>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="29">
+        <f>'Fluxo de pagamentos'!AW28</f>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="29">
+        <f>'Fluxo de pagamentos'!AX28</f>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="29">
+        <f>'Fluxo de pagamentos'!AY28</f>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="29">
+        <f>'Fluxo de pagamentos'!AZ28</f>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="29">
+        <f>'Fluxo de pagamentos'!BA28</f>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="29">
+        <f>'Fluxo de pagamentos'!BB28</f>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="29">
+        <f>'Fluxo de pagamentos'!BC28</f>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="29">
+        <f>'Fluxo de pagamentos'!BD28</f>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="29">
+        <f>'Fluxo de pagamentos'!BE28</f>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="29">
+        <f>'Fluxo de pagamentos'!BF28</f>
+        <v>0</v>
+      </c>
+      <c r="BA7" s="29">
+        <f>'Fluxo de pagamentos'!BG28</f>
+        <v>0</v>
+      </c>
+      <c r="BB7" s="30">
+        <f>SUM(E7:BA7)</f>
+        <v>3242640</v>
+      </c>
+    </row>
+    <row r="8" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A8" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="40">
+        <f>SUM(D5:D7)</f>
+        <v>59042640.313019089</v>
+      </c>
+      <c r="E8" s="29">
+        <f>SUM(E5:E7)</f>
+        <v>21432792.093905725</v>
+      </c>
+      <c r="F8" s="29">
+        <f>SUM(F5:F7)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="29">
+        <f>SUM(G5:G7)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="29">
+        <f>SUM(H5:H7)</f>
+        <v>4577711.49</v>
+      </c>
+      <c r="I8" s="29">
+        <f>SUM(I5:I7)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="29">
+        <f>SUM(J5:J7)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="29">
+        <f>SUM(K5:K7)</f>
+        <v>4426492.5199999996</v>
+      </c>
+      <c r="L8" s="29">
+        <f>SUM(L5:L7)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="29">
+        <f>SUM(M5:M7)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
+        <f>SUM(N5:N7)</f>
+        <v>4695274.7</v>
+      </c>
+      <c r="O8" s="29">
+        <f>SUM(O5:O7)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="29">
+        <f>SUM(P5:P7)</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="29">
+        <f>SUM(Q5:Q7)</f>
+        <v>5585287.5699999994</v>
+      </c>
+      <c r="R8" s="29">
+        <f>SUM(R5:R7)</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="29">
+        <f>SUM(S5:S7)</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="29">
+        <f>SUM(T5:T7)</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="29">
+        <f>SUM(U5:U7)</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="29">
+        <f>SUM(V5:V7)</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="29">
+        <f>SUM(W5:W7)</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="29">
+        <f>SUM(X5:X7)</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="29">
+        <f>SUM(Y5:Y7)</f>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="29">
+        <f>SUM(Z5:Z7)</f>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="29">
+        <f>SUM(AA5:AA7)</f>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="29">
+        <f>SUM(AB5:AB7)</f>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="29">
+        <f>SUM(AC5:AC7)</f>
+        <v>18325081.939113364</v>
+      </c>
+      <c r="AD8" s="29">
+        <f>SUM(AD5:AD7)</f>
+        <v>0</v>
+      </c>
+      <c r="AE8" s="29">
+        <f>SUM(AE5:AE7)</f>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="29">
+        <f>SUM(AF5:AF7)</f>
+        <v>0</v>
+      </c>
+      <c r="AG8" s="29">
+        <f>SUM(AG5:AG7)</f>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="29">
+        <f>SUM(AH5:AH7)</f>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="29">
+        <f>SUM(AI5:AI7)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="29">
+        <f>SUM(AJ5:AJ7)</f>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="29">
+        <f>SUM(AK5:AK7)</f>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="29">
+        <f>SUM(AL5:AL7)</f>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="29">
+        <f>SUM(AM5:AM7)</f>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="29">
+        <f>SUM(AN5:AN7)</f>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="29">
+        <f>SUM(AO5:AO7)</f>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="29">
+        <f>SUM(AP5:AP7)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="29">
+        <f>SUM(AQ5:AQ7)</f>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="29">
+        <f>SUM(AR5:AR7)</f>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="29">
+        <f>SUM(AS5:AS7)</f>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="29">
+        <f>SUM(AT5:AT7)</f>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="29">
+        <f>SUM(AU5:AU7)</f>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="29">
+        <f>SUM(AV5:AV7)</f>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="29">
+        <f>SUM(AW5:AW7)</f>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="29">
+        <f>SUM(AX5:AX7)</f>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="29">
+        <f>SUM(AY5:AY7)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="29">
+        <f>SUM(AZ5:AZ7)</f>
+        <v>0</v>
+      </c>
+      <c r="BA8" s="29">
+        <f>SUM(BA5:BA7)</f>
+        <v>0</v>
+      </c>
+      <c r="BB8" s="29">
+        <f>SUM(BB5:BB7)</f>
+        <v>59042640.313019089</v>
+      </c>
+    </row>
+    <row r="9" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A9" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40">
+        <f>SUM(D3:D7)</f>
+        <v>165300000</v>
+      </c>
+      <c r="E9" s="29">
+        <f>SUM(E3:E7)</f>
+        <v>66119999.999999993</v>
+      </c>
+      <c r="F9" s="29">
+        <f>SUM(F3:F7)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="29">
+        <f>SUM(G3:G7)</f>
+        <v>772015.09</v>
+      </c>
+      <c r="H9" s="29">
+        <f>SUM(H3:H7)</f>
+        <v>5429734.9100000001</v>
+      </c>
+      <c r="I9" s="29">
+        <f>SUM(I3:I7)</f>
+        <v>772015.09</v>
+      </c>
+      <c r="J9" s="29">
+        <f>SUM(J3:J7)</f>
+        <v>540113.11</v>
+      </c>
+      <c r="K9" s="29">
+        <f>SUM(K3:K7)</f>
+        <v>4886621.7999999989</v>
+      </c>
+      <c r="L9" s="29">
+        <f>SUM(L3:L7)</f>
+        <v>537811.52</v>
+      </c>
+      <c r="M9" s="29">
+        <f>SUM(M3:M7)</f>
+        <v>443632.36</v>
+      </c>
+      <c r="N9" s="29">
+        <f>SUM(N3:N7)</f>
+        <v>5217306.12</v>
+      </c>
+      <c r="O9" s="29">
+        <f>SUM(O3:O7)</f>
+        <v>204484.7</v>
+      </c>
+      <c r="P9" s="29">
+        <f>SUM(P3:P7)</f>
+        <v>204493.03</v>
+      </c>
+      <c r="Q9" s="29">
+        <f>SUM(Q3:Q7)</f>
+        <v>5789772.2699999996</v>
+      </c>
+      <c r="R9" s="29">
+        <f>SUM(R3:R7)</f>
+        <v>204493.03</v>
+      </c>
+      <c r="S9" s="29">
+        <f>SUM(S3:S7)</f>
+        <v>201801.96</v>
+      </c>
+      <c r="T9" s="29">
+        <f>SUM(T3:T7)</f>
+        <v>201810.33</v>
+      </c>
+      <c r="U9" s="29">
+        <f>SUM(U3:U7)</f>
+        <v>85143.59</v>
+      </c>
+      <c r="V9" s="29">
+        <f>SUM(V3:V7)</f>
+        <v>85143.59</v>
+      </c>
+      <c r="W9" s="29">
+        <f>SUM(W3:W7)</f>
+        <v>82669.48000000001</v>
+      </c>
+      <c r="X9" s="29">
+        <f>SUM(X3:X7)</f>
+        <v>80301.69</v>
+      </c>
+      <c r="Y9" s="29">
+        <f>SUM(Y3:Y7)</f>
+        <v>80301.69</v>
+      </c>
+      <c r="Z9" s="29">
+        <f>SUM(Z3:Z7)</f>
+        <v>80301.69</v>
+      </c>
+      <c r="AA9" s="29">
+        <f>SUM(AA3:AA7)</f>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="29">
+        <f>SUM(AB3:AB7)</f>
+        <v>0</v>
+      </c>
+      <c r="AC9" s="29">
+        <f>SUM(AC3:AC7)</f>
+        <v>23690032.950000003</v>
+      </c>
+      <c r="AD9" s="29">
+        <f>SUM(AD3:AD7)</f>
+        <v>0</v>
+      </c>
+      <c r="AE9" s="29">
+        <f>SUM(AE3:AE7)</f>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="29">
+        <f>SUM(AF3:AF7)</f>
+        <v>0</v>
+      </c>
+      <c r="AG9" s="29">
+        <f>SUM(AG3:AG7)</f>
+        <v>0</v>
+      </c>
+      <c r="AH9" s="29">
+        <f>SUM(AH3:AH7)</f>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="29">
+        <f>SUM(AI3:AI7)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="29">
+        <f>SUM(AJ3:AJ7)</f>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="29">
+        <f>SUM(AK3:AK7)</f>
+        <v>0</v>
+      </c>
+      <c r="AL9" s="29">
+        <f>SUM(AL3:AL7)</f>
+        <v>0</v>
+      </c>
+      <c r="AM9" s="29">
+        <f>SUM(AM3:AM7)</f>
+        <v>0</v>
+      </c>
+      <c r="AN9" s="29">
+        <f>SUM(AN3:AN7)</f>
+        <v>0</v>
+      </c>
+      <c r="AO9" s="29">
+        <f>SUM(AO3:AO7)</f>
+        <v>24795000</v>
+      </c>
+      <c r="AP9" s="29">
+        <f>SUM(AP3:AP7)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="29">
+        <f>SUM(AQ3:AQ7)</f>
+        <v>0</v>
+      </c>
+      <c r="AR9" s="29">
+        <f>SUM(AR3:AR7)</f>
+        <v>0</v>
+      </c>
+      <c r="AS9" s="29">
+        <f>SUM(AS3:AS7)</f>
+        <v>0</v>
+      </c>
+      <c r="AT9" s="29">
+        <f>SUM(AT3:AT7)</f>
+        <v>0</v>
+      </c>
+      <c r="AU9" s="29">
+        <f>SUM(AU3:AU7)</f>
+        <v>0</v>
+      </c>
+      <c r="AV9" s="29">
+        <f>SUM(AV3:AV7)</f>
+        <v>0</v>
+      </c>
+      <c r="AW9" s="29">
+        <f>SUM(AW3:AW7)</f>
+        <v>0</v>
+      </c>
+      <c r="AX9" s="29">
+        <f>SUM(AX3:AX7)</f>
+        <v>0</v>
+      </c>
+      <c r="AY9" s="29">
+        <f>SUM(AY3:AY7)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="29">
+        <f>SUM(AZ3:AZ7)</f>
+        <v>0</v>
+      </c>
+      <c r="BA9" s="29">
+        <f>SUM(BA3:BA7)</f>
+        <v>24795000</v>
+      </c>
+      <c r="BB9" s="30">
+        <f>SUM(E9:BA9)</f>
+        <v>165300000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="29"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="29"/>
+      <c r="AC10" s="29"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="29"/>
+      <c r="AF10" s="29"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="29"/>
+      <c r="AI10" s="29"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="29"/>
+      <c r="AL10" s="29"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="29"/>
+      <c r="AO10" s="29"/>
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="29"/>
+      <c r="AR10" s="29"/>
+      <c r="AS10" s="29"/>
+      <c r="AT10" s="29"/>
+      <c r="AU10" s="29"/>
+      <c r="AV10" s="29"/>
+      <c r="AW10" s="29"/>
+      <c r="AX10" s="29"/>
+      <c r="AY10" s="29"/>
+      <c r="AZ10" s="29"/>
+      <c r="BA10" s="29"/>
+      <c r="BB10" s="29"/>
+    </row>
+    <row r="11" spans="1:82" s="33" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="M11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="P11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="R11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="S11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="T11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="U11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="V11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="W11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="X11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AU11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AV11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AY11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AZ11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="BA11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="BB11" s="32"/>
+    </row>
+    <row r="12" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="D12" s="30"/>
+      <c r="E12" s="28">
+        <v>46230</v>
+      </c>
+      <c r="F12" s="28">
+        <v>46244</v>
+      </c>
+      <c r="G12" s="28">
+        <v>46275</v>
+      </c>
+      <c r="H12" s="28">
+        <v>46305</v>
+      </c>
+      <c r="I12" s="28">
+        <v>46336</v>
+      </c>
+      <c r="J12" s="28">
+        <v>46366</v>
+      </c>
+      <c r="K12" s="28">
+        <v>46397</v>
+      </c>
+      <c r="L12" s="28">
+        <v>46428</v>
+      </c>
+      <c r="M12" s="28">
+        <v>46456</v>
+      </c>
+      <c r="N12" s="28">
+        <v>46487</v>
+      </c>
+      <c r="O12" s="28">
+        <v>46517</v>
+      </c>
+      <c r="P12" s="28">
+        <v>46548</v>
+      </c>
+      <c r="Q12" s="28">
+        <v>46578</v>
+      </c>
+      <c r="R12" s="28">
+        <v>46609</v>
+      </c>
+      <c r="S12" s="28">
+        <v>46640</v>
+      </c>
+      <c r="T12" s="28">
+        <v>46670</v>
+      </c>
+      <c r="U12" s="28">
+        <v>46701</v>
+      </c>
+      <c r="V12" s="28">
+        <v>46731</v>
+      </c>
+      <c r="W12" s="28">
+        <v>46762</v>
+      </c>
+      <c r="X12" s="28">
+        <v>46793</v>
+      </c>
+      <c r="Y12" s="28">
+        <v>46822</v>
+      </c>
+      <c r="Z12" s="28">
+        <v>46853</v>
+      </c>
+      <c r="AA12" s="28">
+        <v>46883</v>
+      </c>
+      <c r="AB12" s="28">
+        <v>46914</v>
+      </c>
+      <c r="AC12" s="28">
+        <v>46944</v>
+      </c>
+      <c r="AD12" s="28">
+        <v>46975</v>
+      </c>
+      <c r="AE12" s="28">
+        <v>47006</v>
+      </c>
+      <c r="AF12" s="28">
+        <v>47036</v>
+      </c>
+      <c r="AG12" s="28">
+        <v>47067</v>
+      </c>
+      <c r="AH12" s="28">
+        <v>47097</v>
+      </c>
+      <c r="AI12" s="28">
+        <v>47128</v>
+      </c>
+      <c r="AJ12" s="28">
+        <v>47159</v>
+      </c>
+      <c r="AK12" s="28">
+        <v>47187</v>
+      </c>
+      <c r="AL12" s="28">
+        <v>47218</v>
+      </c>
+      <c r="AM12" s="28">
+        <v>47248</v>
+      </c>
+      <c r="AN12" s="28">
+        <v>47279</v>
+      </c>
+      <c r="AO12" s="28">
+        <v>47309</v>
+      </c>
+      <c r="AP12" s="28">
+        <v>47340</v>
+      </c>
+      <c r="AQ12" s="28">
+        <v>47371</v>
+      </c>
+      <c r="AR12" s="28">
+        <v>47401</v>
+      </c>
+      <c r="AS12" s="28">
+        <v>47432</v>
+      </c>
+      <c r="AT12" s="28">
+        <v>47462</v>
+      </c>
+      <c r="AU12" s="28">
+        <v>47493</v>
+      </c>
+      <c r="AV12" s="28">
+        <v>47524</v>
+      </c>
+      <c r="AW12" s="28">
+        <v>47552</v>
+      </c>
+      <c r="AX12" s="28">
+        <v>47583</v>
+      </c>
+      <c r="AY12" s="28">
+        <v>47613</v>
+      </c>
+      <c r="AZ12" s="28">
+        <v>47644</v>
+      </c>
+      <c r="BA12" s="28">
+        <v>47674</v>
+      </c>
+      <c r="BB12" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC12" s="28"/>
+      <c r="BD12" s="28"/>
+      <c r="BE12" s="28"/>
+      <c r="BF12" s="28"/>
+      <c r="BG12" s="28"/>
+      <c r="BH12" s="28"/>
+      <c r="BI12" s="28"/>
+      <c r="BJ12" s="28"/>
+      <c r="BK12" s="28"/>
+      <c r="BL12" s="28"/>
+      <c r="BM12" s="28"/>
+      <c r="BN12" s="28"/>
+      <c r="BO12" s="28"/>
+      <c r="BP12" s="28"/>
+      <c r="BQ12" s="28"/>
+      <c r="BR12" s="28"/>
+      <c r="BS12" s="28"/>
+      <c r="BT12" s="28"/>
+      <c r="BU12" s="28"/>
+      <c r="BV12" s="28"/>
+      <c r="BW12" s="28"/>
+      <c r="BX12" s="28"/>
+      <c r="BY12" s="28"/>
+      <c r="BZ12" s="28"/>
+      <c r="CA12" s="28"/>
+      <c r="CB12" s="28"/>
+      <c r="CC12" s="28"/>
+      <c r="CD12" s="28"/>
+    </row>
+    <row r="13" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="32">
+        <f>'Fluxo de pagamentos'!J5</f>
+        <v>42649550.918097198</v>
+      </c>
+      <c r="E13" s="32">
+        <f>'Fluxo de pagamentos'!K5</f>
+        <v>8362181.3736455785</v>
+      </c>
+      <c r="F13" s="32">
+        <f>'Fluxo de pagamentos'!L5</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="32">
+        <f>'Fluxo de pagamentos'!M5</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="32">
+        <f>'Fluxo de pagamentos'!N5</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="32">
+        <f>'Fluxo de pagamentos'!O5</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="32">
+        <f>'Fluxo de pagamentos'!P5</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="32">
+        <f>'Fluxo de pagamentos'!Q5</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="32">
+        <f>'Fluxo de pagamentos'!R5</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="32">
+        <f>'Fluxo de pagamentos'!S5</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="32">
+        <f>'Fluxo de pagamentos'!T5</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="32">
+        <f>'Fluxo de pagamentos'!U5</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="32">
+        <f>'Fluxo de pagamentos'!V5</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="32">
+        <f>'Fluxo de pagamentos'!W5</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="32">
+        <f>'Fluxo de pagamentos'!X5</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="32">
+        <f>'Fluxo de pagamentos'!Y5</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="32">
+        <f>'Fluxo de pagamentos'!Z5</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="32">
+        <f>'Fluxo de pagamentos'!AA5</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="32">
+        <f>'Fluxo de pagamentos'!AB5</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="32">
+        <f>'Fluxo de pagamentos'!AC5</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="32">
+        <f>'Fluxo de pagamentos'!AD5</f>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="32">
+        <f>'Fluxo de pagamentos'!AE5</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="32">
+        <f>'Fluxo de pagamentos'!AF5</f>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="32">
+        <f>'Fluxo de pagamentos'!AG5</f>
+        <v>0</v>
+      </c>
+      <c r="AB13" s="32">
+        <f>'Fluxo de pagamentos'!AH5</f>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="32">
+        <f>'Fluxo de pagamentos'!AI5</f>
+        <v>3048542.4358633407</v>
+      </c>
+      <c r="AD13" s="32">
+        <f>'Fluxo de pagamentos'!AJ5</f>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="32">
+        <f>'Fluxo de pagamentos'!AK5</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="32">
+        <f>'Fluxo de pagamentos'!AL5</f>
+        <v>0</v>
+      </c>
+      <c r="AG13" s="32">
+        <f>'Fluxo de pagamentos'!AM5</f>
+        <v>0</v>
+      </c>
+      <c r="AH13" s="32">
+        <f>'Fluxo de pagamentos'!AN5</f>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="32">
+        <f>'Fluxo de pagamentos'!AO5</f>
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="32">
+        <f>'Fluxo de pagamentos'!AP5</f>
+        <v>0</v>
+      </c>
+      <c r="AK13" s="32">
+        <f>'Fluxo de pagamentos'!AQ5</f>
+        <v>0</v>
+      </c>
+      <c r="AL13" s="32">
+        <f>'Fluxo de pagamentos'!AR5</f>
+        <v>0</v>
+      </c>
+      <c r="AM13" s="32">
+        <f>'Fluxo de pagamentos'!AS5</f>
+        <v>0</v>
+      </c>
+      <c r="AN13" s="32">
+        <f>'Fluxo de pagamentos'!AT5</f>
+        <v>0</v>
+      </c>
+      <c r="AO13" s="32">
+        <f>'Fluxo de pagamentos'!AU5</f>
+        <v>15619413.554294141</v>
+      </c>
+      <c r="AP13" s="32">
+        <f>'Fluxo de pagamentos'!AV5</f>
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="32">
+        <f>'Fluxo de pagamentos'!AW5</f>
+        <v>0</v>
+      </c>
+      <c r="AR13" s="32">
+        <f>'Fluxo de pagamentos'!AX5</f>
+        <v>0</v>
+      </c>
+      <c r="AS13" s="32">
+        <f>'Fluxo de pagamentos'!AY5</f>
+        <v>0</v>
+      </c>
+      <c r="AT13" s="32">
+        <f>'Fluxo de pagamentos'!AZ5</f>
+        <v>0</v>
+      </c>
+      <c r="AU13" s="32">
+        <f>'Fluxo de pagamentos'!BA5</f>
+        <v>0</v>
+      </c>
+      <c r="AV13" s="32">
+        <f>'Fluxo de pagamentos'!BB5</f>
+        <v>0</v>
+      </c>
+      <c r="AW13" s="32">
+        <f>'Fluxo de pagamentos'!BC5</f>
+        <v>0</v>
+      </c>
+      <c r="AX13" s="32">
+        <f>'Fluxo de pagamentos'!BD5</f>
+        <v>0</v>
+      </c>
+      <c r="AY13" s="32">
+        <f>'Fluxo de pagamentos'!BE5</f>
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="32">
+        <f>'Fluxo de pagamentos'!BF5</f>
+        <v>0</v>
+      </c>
+      <c r="BA13" s="32">
+        <f>'Fluxo de pagamentos'!BG5</f>
+        <v>15619413.554294141</v>
+      </c>
+      <c r="BB13" s="41">
+        <f>SUM(E13:BA13)</f>
+        <v>42649550.918097198</v>
+      </c>
+      <c r="BC13" s="41"/>
+      <c r="BD13" s="42"/>
+      <c r="BE13" s="43"/>
+      <c r="BF13" s="43"/>
+      <c r="BG13" s="43"/>
+      <c r="BH13" s="43"/>
+      <c r="BI13" s="43"/>
+      <c r="BJ13" s="43"/>
+      <c r="BK13" s="43"/>
+      <c r="BL13" s="43"/>
+      <c r="BM13" s="43"/>
+      <c r="BN13" s="43"/>
+      <c r="BO13" s="43"/>
+      <c r="BP13" s="43"/>
+      <c r="BQ13" s="43"/>
+      <c r="BR13" s="43"/>
+      <c r="BS13" s="43"/>
+      <c r="BT13" s="43"/>
+      <c r="BU13" s="43"/>
+      <c r="BV13" s="43"/>
+      <c r="BW13" s="43"/>
+      <c r="BX13" s="43"/>
+      <c r="BY13" s="43"/>
+      <c r="BZ13" s="43"/>
+      <c r="CA13" s="43"/>
+      <c r="CB13" s="43"/>
+      <c r="CC13" s="43"/>
+      <c r="CD13" s="43"/>
+    </row>
+    <row r="14" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="32">
+        <f>('Fluxo de pagamentos'!J7+'Fluxo de pagamentos'!J8)*64.7%</f>
+        <v>7488507.898190001</v>
+      </c>
+      <c r="E14" s="32">
+        <f>('Fluxo de pagamentos'!K7+'Fluxo de pagamentos'!K8)*64.7%</f>
+        <v>1941000</v>
+      </c>
+      <c r="F14" s="32">
+        <f>('Fluxo de pagamentos'!L7+'Fluxo de pagamentos'!L8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="32">
+        <f>('Fluxo de pagamentos'!M7+'Fluxo de pagamentos'!M8)*64.7%</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="H14" s="32">
+        <f>('Fluxo de pagamentos'!N7+'Fluxo de pagamentos'!N8)*64.7%</f>
+        <v>551259.15273999993</v>
+      </c>
+      <c r="I14" s="32">
+        <f>('Fluxo de pagamentos'!O7+'Fluxo de pagamentos'!O8)*64.7%</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="J14" s="32">
+        <f>('Fluxo de pagamentos'!P7+'Fluxo de pagamentos'!P8)*64.7%</f>
+        <v>349453.18216999999</v>
+      </c>
+      <c r="K14" s="32">
+        <f>('Fluxo de pagamentos'!Q7+'Fluxo de pagamentos'!Q8)*64.7%</f>
+        <v>297703.64415999997</v>
+      </c>
+      <c r="L14" s="32">
+        <f>('Fluxo de pagamentos'!R7+'Fluxo de pagamentos'!R8)*64.7%</f>
+        <v>347964.05344000005</v>
+      </c>
+      <c r="M14" s="32">
+        <f>('Fluxo de pagamentos'!S7+'Fluxo de pagamentos'!S8)*64.7%</f>
+        <v>287030.13692000002</v>
+      </c>
+      <c r="N14" s="32">
+        <f>('Fluxo de pagamentos'!T7+'Fluxo de pagamentos'!T8)*64.7%</f>
+        <v>337754.32874000003</v>
+      </c>
+      <c r="O14" s="32">
+        <f>('Fluxo de pagamentos'!U7+'Fluxo de pagamentos'!U8)*64.7%</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="P14" s="32">
+        <f>('Fluxo de pagamentos'!V7+'Fluxo de pagamentos'!V8)*64.7%</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="Q14" s="32">
+        <f>('Fluxo de pagamentos'!W7+'Fluxo de pagamentos'!W8)*64.7%</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="R14" s="32">
+        <f>('Fluxo de pagamentos'!X7+'Fluxo de pagamentos'!X8)*64.7%</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="S14" s="32">
+        <f>('Fluxo de pagamentos'!Y7+'Fluxo de pagamentos'!Y8)*64.7%</f>
+        <v>130565.86812</v>
+      </c>
+      <c r="T14" s="32">
+        <f>('Fluxo de pagamentos'!Z7+'Fluxo de pagamentos'!Z8)*64.7%</f>
+        <v>130571.28350999999</v>
+      </c>
+      <c r="U14" s="32">
+        <f>('Fluxo de pagamentos'!AA7+'Fluxo de pagamentos'!AA8)*64.7%</f>
+        <v>55087.902730000002</v>
+      </c>
+      <c r="V14" s="32">
+        <f>('Fluxo de pagamentos'!AB7+'Fluxo de pagamentos'!AB8)*64.7%</f>
+        <v>55087.902730000002</v>
+      </c>
+      <c r="W14" s="32">
+        <f>('Fluxo de pagamentos'!AC7+'Fluxo de pagamentos'!AC8)*64.7%</f>
+        <v>53487.153560000006</v>
+      </c>
+      <c r="X14" s="32">
+        <f>('Fluxo de pagamentos'!AD7+'Fluxo de pagamentos'!AD8)*64.7%</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="Y14" s="32">
+        <f>('Fluxo de pagamentos'!AE7+'Fluxo de pagamentos'!AE8)*64.7%</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="Z14" s="32">
+        <f>('Fluxo de pagamentos'!AF7+'Fluxo de pagamentos'!AF8)*64.7%</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="AA14" s="32">
+        <f>('Fluxo de pagamentos'!AG7+'Fluxo de pagamentos'!AG8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="32">
+        <f>('Fluxo de pagamentos'!AH7+'Fluxo de pagamentos'!AH8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="32">
+        <f>('Fluxo de pagamentos'!AI7+'Fluxo de pagamentos'!AI8)*64.7%</f>
+        <v>422491</v>
+      </c>
+      <c r="AD14" s="32">
+        <f>('Fluxo de pagamentos'!AJ7+'Fluxo de pagamentos'!AJ8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AE14" s="32">
+        <f>('Fluxo de pagamentos'!AK7+'Fluxo de pagamentos'!AK8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="32">
+        <f>('Fluxo de pagamentos'!AL7+'Fluxo de pagamentos'!AL8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AG14" s="32">
+        <f>('Fluxo de pagamentos'!AM7+'Fluxo de pagamentos'!AM8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AH14" s="32">
+        <f>('Fluxo de pagamentos'!AN7+'Fluxo de pagamentos'!AN8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AI14" s="32">
+        <f>('Fluxo de pagamentos'!AO7+'Fluxo de pagamentos'!AO8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="32">
+        <f>('Fluxo de pagamentos'!AP7+'Fluxo de pagamentos'!AP8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AK14" s="32">
+        <f>('Fluxo de pagamentos'!AQ7+'Fluxo de pagamentos'!AQ8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AL14" s="32">
+        <f>('Fluxo de pagamentos'!AR7+'Fluxo de pagamentos'!AR8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AM14" s="32">
+        <f>('Fluxo de pagamentos'!AS7+'Fluxo de pagamentos'!AS8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="32">
+        <f>('Fluxo de pagamentos'!AT7+'Fluxo de pagamentos'!AT8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AO14" s="32">
+        <f>('Fluxo de pagamentos'!AU7+'Fluxo de pagamentos'!AU8)*64.7%</f>
+        <v>422491</v>
+      </c>
+      <c r="AP14" s="32">
+        <f>('Fluxo de pagamentos'!AV7+'Fluxo de pagamentos'!AV8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="32">
+        <f>('Fluxo de pagamentos'!AW7+'Fluxo de pagamentos'!AW8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AR14" s="32">
+        <f>('Fluxo de pagamentos'!AX7+'Fluxo de pagamentos'!AX8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AS14" s="32">
+        <f>('Fluxo de pagamentos'!AY7+'Fluxo de pagamentos'!AY8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AT14" s="32">
+        <f>('Fluxo de pagamentos'!AZ7+'Fluxo de pagamentos'!AZ8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AU14" s="32">
+        <f>('Fluxo de pagamentos'!BA7+'Fluxo de pagamentos'!BA8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AV14" s="32">
+        <f>('Fluxo de pagamentos'!BB7+'Fluxo de pagamentos'!BB8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AW14" s="32">
+        <f>('Fluxo de pagamentos'!BC7+'Fluxo de pagamentos'!BC8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AX14" s="32">
+        <f>('Fluxo de pagamentos'!BD7+'Fluxo de pagamentos'!BD8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AY14" s="32">
+        <f>('Fluxo de pagamentos'!BE7+'Fluxo de pagamentos'!BE8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="32">
+        <f>('Fluxo de pagamentos'!BF7+'Fluxo de pagamentos'!BF8)*64.7%</f>
+        <v>0</v>
+      </c>
+      <c r="BA14" s="32">
+        <f>('Fluxo de pagamentos'!BG7+'Fluxo de pagamentos'!BG8)*64.7%</f>
+        <v>422491</v>
+      </c>
+      <c r="BB14" s="41">
+        <f>SUM(E14:BA14)</f>
+        <v>7488507.898190002</v>
+      </c>
+      <c r="BC14" s="41"/>
+      <c r="BD14" s="42"/>
+      <c r="BE14" s="43"/>
+      <c r="BF14" s="43"/>
+      <c r="BG14" s="43"/>
+      <c r="BH14" s="43"/>
+      <c r="BI14" s="43"/>
+      <c r="BJ14" s="43"/>
+      <c r="BK14" s="43"/>
+      <c r="BL14" s="43"/>
+      <c r="BM14" s="43"/>
+      <c r="BN14" s="43"/>
+      <c r="BO14" s="43"/>
+      <c r="BP14" s="43"/>
+      <c r="BQ14" s="43"/>
+      <c r="BR14" s="43"/>
+      <c r="BS14" s="43"/>
+      <c r="BT14" s="43"/>
+      <c r="BU14" s="43"/>
+      <c r="BV14" s="43"/>
+      <c r="BW14" s="43"/>
+      <c r="BX14" s="43"/>
+      <c r="BY14" s="43"/>
+      <c r="BZ14" s="43"/>
+      <c r="CA14" s="43"/>
+      <c r="CB14" s="43"/>
+      <c r="CC14" s="43"/>
+      <c r="CD14" s="43"/>
+    </row>
+    <row r="15" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="32">
+        <f>SUM(D13:D14)</f>
+        <v>50138058.816287197</v>
+      </c>
+      <c r="E15" s="32">
+        <f>SUM(E13:E14)</f>
+        <v>10303181.373645578</v>
+      </c>
+      <c r="F15" s="32">
+        <f>SUM(F13:F14)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="32">
+        <f>SUM(G13:G14)</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="H15" s="32">
+        <f>SUM(H13:H14)</f>
+        <v>551259.15273999993</v>
+      </c>
+      <c r="I15" s="32">
+        <f>SUM(I13:I14)</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="J15" s="32">
+        <f>SUM(J13:J14)</f>
+        <v>349453.18216999999</v>
+      </c>
+      <c r="K15" s="32">
+        <f>SUM(K13:K14)</f>
+        <v>297703.64415999997</v>
+      </c>
+      <c r="L15" s="32">
+        <f>SUM(L13:L14)</f>
+        <v>347964.05344000005</v>
+      </c>
+      <c r="M15" s="32">
+        <f>SUM(M13:M14)</f>
+        <v>287030.13692000002</v>
+      </c>
+      <c r="N15" s="32">
+        <f>SUM(N13:N14)</f>
+        <v>337754.32874000003</v>
+      </c>
+      <c r="O15" s="32">
+        <f>SUM(O13:O14)</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="P15" s="32">
+        <f>SUM(P13:P14)</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="Q15" s="32">
+        <f>SUM(Q13:Q14)</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="R15" s="32">
+        <f>SUM(R13:R14)</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="S15" s="32">
+        <f>SUM(S13:S14)</f>
+        <v>130565.86812</v>
+      </c>
+      <c r="T15" s="32">
+        <f>SUM(T13:T14)</f>
+        <v>130571.28350999999</v>
+      </c>
+      <c r="U15" s="32">
+        <f>SUM(U13:U14)</f>
+        <v>55087.902730000002</v>
+      </c>
+      <c r="V15" s="32">
+        <f>SUM(V13:V14)</f>
+        <v>55087.902730000002</v>
+      </c>
+      <c r="W15" s="32">
+        <f>SUM(W13:W14)</f>
+        <v>53487.153560000006</v>
+      </c>
+      <c r="X15" s="32">
+        <f>SUM(X13:X14)</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="Y15" s="32">
+        <f>SUM(Y13:Y14)</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="Z15" s="32">
+        <f>SUM(Z13:Z14)</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="AA15" s="32">
+        <f>SUM(AA13:AA14)</f>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="32">
+        <f>SUM(AB13:AB14)</f>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="32">
+        <f>SUM(AC13:AC14)</f>
+        <v>3471033.4358633407</v>
+      </c>
+      <c r="AD15" s="32">
+        <f>SUM(AD13:AD14)</f>
+        <v>0</v>
+      </c>
+      <c r="AE15" s="32">
+        <f>SUM(AE13:AE14)</f>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="32">
+        <f>SUM(AF13:AF14)</f>
+        <v>0</v>
+      </c>
+      <c r="AG15" s="32">
+        <f>SUM(AG13:AG14)</f>
+        <v>0</v>
+      </c>
+      <c r="AH15" s="32">
+        <f>SUM(AH13:AH14)</f>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="32">
+        <f>SUM(AI13:AI14)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="32">
+        <f>SUM(AJ13:AJ14)</f>
+        <v>0</v>
+      </c>
+      <c r="AK15" s="32">
+        <f>SUM(AK13:AK14)</f>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="32">
+        <f>SUM(AL13:AL14)</f>
+        <v>0</v>
+      </c>
+      <c r="AM15" s="32">
+        <f>SUM(AM13:AM14)</f>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="32">
+        <f>SUM(AN13:AN14)</f>
+        <v>0</v>
+      </c>
+      <c r="AO15" s="32">
+        <f>SUM(AO13:AO14)</f>
+        <v>16041904.554294141</v>
+      </c>
+      <c r="AP15" s="32">
+        <f>SUM(AP13:AP14)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="32">
+        <f>SUM(AQ13:AQ14)</f>
+        <v>0</v>
+      </c>
+      <c r="AR15" s="32">
+        <f>SUM(AR13:AR14)</f>
+        <v>0</v>
+      </c>
+      <c r="AS15" s="32">
+        <f>SUM(AS13:AS14)</f>
+        <v>0</v>
+      </c>
+      <c r="AT15" s="32">
+        <f>SUM(AT13:AT14)</f>
+        <v>0</v>
+      </c>
+      <c r="AU15" s="32">
+        <f>SUM(AU13:AU14)</f>
+        <v>0</v>
+      </c>
+      <c r="AV15" s="32">
+        <f>SUM(AV13:AV14)</f>
+        <v>0</v>
+      </c>
+      <c r="AW15" s="32">
+        <f>SUM(AW13:AW14)</f>
+        <v>0</v>
+      </c>
+      <c r="AX15" s="32">
+        <f>SUM(AX13:AX14)</f>
+        <v>0</v>
+      </c>
+      <c r="AY15" s="32">
+        <f>SUM(AY13:AY14)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="32">
+        <f>SUM(AZ13:AZ14)</f>
+        <v>0</v>
+      </c>
+      <c r="BA15" s="32">
+        <f>SUM(BA13:BA14)</f>
+        <v>16041904.554294141</v>
+      </c>
+      <c r="BB15" s="41">
+        <f>SUM(E15:BA15)</f>
+        <v>50138058.816287197</v>
+      </c>
+      <c r="BC15" s="41"/>
+      <c r="BD15" s="42"/>
+      <c r="BE15" s="43"/>
+      <c r="BF15" s="43"/>
+      <c r="BG15" s="43"/>
+      <c r="BH15" s="43"/>
+      <c r="BI15" s="43"/>
+      <c r="BJ15" s="43"/>
+      <c r="BK15" s="43"/>
+      <c r="BL15" s="43"/>
+      <c r="BM15" s="43"/>
+      <c r="BN15" s="43"/>
+      <c r="BO15" s="43"/>
+      <c r="BP15" s="43"/>
+      <c r="BQ15" s="43"/>
+      <c r="BR15" s="43"/>
+      <c r="BS15" s="43"/>
+      <c r="BT15" s="43"/>
+      <c r="BU15" s="43"/>
+      <c r="BV15" s="43"/>
+      <c r="BW15" s="43"/>
+      <c r="BX15" s="43"/>
+      <c r="BY15" s="43"/>
+      <c r="BZ15" s="43"/>
+      <c r="CA15" s="43"/>
+      <c r="CB15" s="43"/>
+      <c r="CC15" s="43"/>
+      <c r="CD15" s="43"/>
+    </row>
+    <row r="16" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="32">
+        <f>'Fluxo de pagamentos'!J6</f>
+        <v>23271327.268883705</v>
+      </c>
+      <c r="E16" s="32">
+        <f>'Fluxo de pagamentos'!K6</f>
+        <v>4562745.8024486918</v>
+      </c>
+      <c r="F16" s="32">
+        <f>'Fluxo de pagamentos'!L6</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="32">
+        <f>'Fluxo de pagamentos'!M6</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="32">
+        <f>'Fluxo de pagamentos'!N6</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="32">
+        <f>'Fluxo de pagamentos'!O6</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="32">
+        <f>'Fluxo de pagamentos'!P6</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="32">
+        <f>'Fluxo de pagamentos'!Q6</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="32">
+        <f>'Fluxo de pagamentos'!R6</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="32">
+        <f>'Fluxo de pagamentos'!S6</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="32">
+        <f>'Fluxo de pagamentos'!T6</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="32">
+        <f>'Fluxo de pagamentos'!U6</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="32">
+        <f>'Fluxo de pagamentos'!V6</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="32">
+        <f>'Fluxo de pagamentos'!W6</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="32">
+        <f>'Fluxo de pagamentos'!X6</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="32">
+        <f>'Fluxo de pagamentos'!Y6</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="32">
+        <f>'Fluxo de pagamentos'!Z6</f>
+        <v>0</v>
+      </c>
+      <c r="U16" s="32">
+        <f>'Fluxo de pagamentos'!AA6</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="32">
+        <f>'Fluxo de pagamentos'!AB6</f>
+        <v>0</v>
+      </c>
+      <c r="W16" s="32">
+        <f>'Fluxo de pagamentos'!AC6</f>
+        <v>0</v>
+      </c>
+      <c r="X16" s="32">
+        <f>'Fluxo de pagamentos'!AD6</f>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="32">
+        <f>'Fluxo de pagamentos'!AE6</f>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="32">
+        <f>'Fluxo de pagamentos'!AF6</f>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="32">
+        <f>'Fluxo de pagamentos'!AG6</f>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="32">
+        <f>'Fluxo de pagamentos'!AH6</f>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="32">
+        <f>'Fluxo de pagamentos'!AI6</f>
+        <v>1663408.5750232993</v>
+      </c>
+      <c r="AD16" s="32">
+        <f>'Fluxo de pagamentos'!AJ6</f>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="32">
+        <f>'Fluxo de pagamentos'!AK6</f>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="32">
+        <f>'Fluxo de pagamentos'!AL6</f>
+        <v>0</v>
+      </c>
+      <c r="AG16" s="32">
+        <f>'Fluxo de pagamentos'!AM6</f>
+        <v>0</v>
+      </c>
+      <c r="AH16" s="32">
+        <f>'Fluxo de pagamentos'!AN6</f>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="32">
+        <f>'Fluxo de pagamentos'!AO6</f>
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="32">
+        <f>'Fluxo de pagamentos'!AP6</f>
+        <v>0</v>
+      </c>
+      <c r="AK16" s="32">
+        <f>'Fluxo de pagamentos'!AQ6</f>
+        <v>0</v>
+      </c>
+      <c r="AL16" s="32">
+        <f>'Fluxo de pagamentos'!AR6</f>
+        <v>0</v>
+      </c>
+      <c r="AM16" s="32">
+        <f>'Fluxo de pagamentos'!AS6</f>
+        <v>0</v>
+      </c>
+      <c r="AN16" s="32">
+        <f>'Fluxo de pagamentos'!AT6</f>
+        <v>0</v>
+      </c>
+      <c r="AO16" s="32">
+        <f>'Fluxo de pagamentos'!AU6</f>
+        <v>8522586.4457058571</v>
+      </c>
+      <c r="AP16" s="32">
+        <f>'Fluxo de pagamentos'!AV6</f>
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="32">
+        <f>'Fluxo de pagamentos'!AW6</f>
+        <v>0</v>
+      </c>
+      <c r="AR16" s="32">
+        <f>'Fluxo de pagamentos'!AX6</f>
+        <v>0</v>
+      </c>
+      <c r="AS16" s="32">
+        <f>'Fluxo de pagamentos'!AY6</f>
+        <v>0</v>
+      </c>
+      <c r="AT16" s="32">
+        <f>'Fluxo de pagamentos'!AZ6</f>
+        <v>0</v>
+      </c>
+      <c r="AU16" s="32">
+        <f>'Fluxo de pagamentos'!BA6</f>
+        <v>0</v>
+      </c>
+      <c r="AV16" s="32">
+        <f>'Fluxo de pagamentos'!BB6</f>
+        <v>0</v>
+      </c>
+      <c r="AW16" s="32">
+        <f>'Fluxo de pagamentos'!BC6</f>
+        <v>0</v>
+      </c>
+      <c r="AX16" s="32">
+        <f>'Fluxo de pagamentos'!BD6</f>
+        <v>0</v>
+      </c>
+      <c r="AY16" s="32">
+        <f>'Fluxo de pagamentos'!BE6</f>
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="32">
+        <f>'Fluxo de pagamentos'!BF6</f>
+        <v>0</v>
+      </c>
+      <c r="BA16" s="32">
+        <f>'Fluxo de pagamentos'!BG6</f>
+        <v>8522586.4457058571</v>
+      </c>
+      <c r="BB16" s="41">
+        <f>SUM(E16:BA16)</f>
+        <v>23271327.268883705</v>
+      </c>
+      <c r="BC16" s="43"/>
+      <c r="BD16" s="42"/>
+      <c r="BE16" s="43"/>
+      <c r="BF16" s="43"/>
+      <c r="BG16" s="43"/>
+      <c r="BH16" s="43"/>
+      <c r="BI16" s="43"/>
+      <c r="BJ16" s="43"/>
+      <c r="BK16" s="43"/>
+      <c r="BL16" s="43"/>
+      <c r="BM16" s="43"/>
+      <c r="BN16" s="43"/>
+      <c r="BO16" s="43"/>
+      <c r="BP16" s="43"/>
+      <c r="BQ16" s="43"/>
+      <c r="BR16" s="43"/>
+      <c r="BS16" s="43"/>
+      <c r="BT16" s="43"/>
+      <c r="BU16" s="43"/>
+      <c r="BV16" s="43"/>
+      <c r="BW16" s="43"/>
+      <c r="BX16" s="43"/>
+      <c r="BY16" s="43"/>
+      <c r="BZ16" s="43"/>
+      <c r="CA16" s="43"/>
+      <c r="CB16" s="43"/>
+      <c r="CC16" s="43"/>
+      <c r="CD16" s="43"/>
+    </row>
+    <row r="17" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="32">
+        <f>('Fluxo de pagamentos'!J7+'Fluxo de pagamentos'!J8)*35.3%</f>
+        <v>4085692.8718100004</v>
+      </c>
+      <c r="E17" s="32">
+        <f>('Fluxo de pagamentos'!K7+'Fluxo de pagamentos'!K8)*35.3%</f>
+        <v>1059000</v>
+      </c>
+      <c r="F17" s="32">
+        <f>('Fluxo de pagamentos'!L7+'Fluxo de pagamentos'!L8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="32">
+        <f>('Fluxo de pagamentos'!M7+'Fluxo de pagamentos'!M8)*35.3%</f>
+        <v>272521.32676999999</v>
+      </c>
+      <c r="H17" s="32">
+        <f>('Fluxo de pagamentos'!N7+'Fluxo de pagamentos'!N8)*35.3%</f>
+        <v>300764.26725999994</v>
+      </c>
+      <c r="I17" s="32">
+        <f>('Fluxo de pagamentos'!O7+'Fluxo de pagamentos'!O8)*35.3%</f>
+        <v>272521.32676999999</v>
+      </c>
+      <c r="J17" s="32">
+        <f>('Fluxo de pagamentos'!P7+'Fluxo de pagamentos'!P8)*35.3%</f>
+        <v>190659.92782999997</v>
+      </c>
+      <c r="K17" s="32">
+        <f>('Fluxo de pagamentos'!Q7+'Fluxo de pagamentos'!Q8)*35.3%</f>
+        <v>162425.63583999997</v>
+      </c>
+      <c r="L17" s="32">
+        <f>('Fluxo de pagamentos'!R7+'Fluxo de pagamentos'!R8)*35.3%</f>
+        <v>189847.46656</v>
+      </c>
+      <c r="M17" s="32">
+        <f>('Fluxo de pagamentos'!S7+'Fluxo de pagamentos'!S8)*35.3%</f>
+        <v>156602.22308</v>
+      </c>
+      <c r="N17" s="32">
+        <f>('Fluxo de pagamentos'!T7+'Fluxo de pagamentos'!T8)*35.3%</f>
+        <v>184277.09125999999</v>
+      </c>
+      <c r="O17" s="32">
+        <f>('Fluxo de pagamentos'!U7+'Fluxo de pagamentos'!U8)*35.3%</f>
+        <v>72183.099100000007</v>
+      </c>
+      <c r="P17" s="32">
+        <f>('Fluxo de pagamentos'!V7+'Fluxo de pagamentos'!V8)*35.3%</f>
+        <v>72186.03959</v>
+      </c>
+      <c r="Q17" s="32">
+        <f>('Fluxo de pagamentos'!W7+'Fluxo de pagamentos'!W8)*35.3%</f>
+        <v>72183.099100000007</v>
+      </c>
+      <c r="R17" s="32">
+        <f>('Fluxo de pagamentos'!X7+'Fluxo de pagamentos'!X8)*35.3%</f>
+        <v>72186.03959</v>
+      </c>
+      <c r="S17" s="32">
+        <f>('Fluxo de pagamentos'!Y7+'Fluxo de pagamentos'!Y8)*35.3%</f>
+        <v>71236.091879999993</v>
+      </c>
+      <c r="T17" s="32">
+        <f>('Fluxo de pagamentos'!Z7+'Fluxo de pagamentos'!Z8)*35.3%</f>
+        <v>71239.046489999993</v>
+      </c>
+      <c r="U17" s="32">
+        <f>('Fluxo de pagamentos'!AA7+'Fluxo de pagamentos'!AA8)*35.3%</f>
+        <v>30055.687269999999</v>
+      </c>
+      <c r="V17" s="32">
+        <f>('Fluxo de pagamentos'!AB7+'Fluxo de pagamentos'!AB8)*35.3%</f>
+        <v>30055.687269999999</v>
+      </c>
+      <c r="W17" s="32">
+        <f>('Fluxo de pagamentos'!AC7+'Fluxo de pagamentos'!AC8)*35.3%</f>
+        <v>29182.326440000001</v>
+      </c>
+      <c r="X17" s="32">
+        <f>('Fluxo de pagamentos'!AD7+'Fluxo de pagamentos'!AD8)*35.3%</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="Y17" s="32">
+        <f>('Fluxo de pagamentos'!AE7+'Fluxo de pagamentos'!AE8)*35.3%</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="Z17" s="32">
+        <f>('Fluxo de pagamentos'!AF7+'Fluxo de pagamentos'!AF8)*35.3%</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="AA17" s="32">
+        <f>('Fluxo de pagamentos'!AG7+'Fluxo de pagamentos'!AG8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="32">
+        <f>('Fluxo de pagamentos'!AH7+'Fluxo de pagamentos'!AH8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="32">
+        <f>('Fluxo de pagamentos'!AI7+'Fluxo de pagamentos'!AI8)*35.3%</f>
+        <v>230509</v>
+      </c>
+      <c r="AD17" s="32">
+        <f>('Fluxo de pagamentos'!AJ7+'Fluxo de pagamentos'!AJ8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="32">
+        <f>('Fluxo de pagamentos'!AK7+'Fluxo de pagamentos'!AK8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="32">
+        <f>('Fluxo de pagamentos'!AL7+'Fluxo de pagamentos'!AL8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="32">
+        <f>('Fluxo de pagamentos'!AM7+'Fluxo de pagamentos'!AM8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="32">
+        <f>('Fluxo de pagamentos'!AN7+'Fluxo de pagamentos'!AN8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="32">
+        <f>('Fluxo de pagamentos'!AO7+'Fluxo de pagamentos'!AO8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="32">
+        <f>('Fluxo de pagamentos'!AP7+'Fluxo de pagamentos'!AP8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="32">
+        <f>('Fluxo de pagamentos'!AQ7+'Fluxo de pagamentos'!AQ8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AL17" s="32">
+        <f>('Fluxo de pagamentos'!AR7+'Fluxo de pagamentos'!AR8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AM17" s="32">
+        <f>('Fluxo de pagamentos'!AS7+'Fluxo de pagamentos'!AS8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AN17" s="32">
+        <f>('Fluxo de pagamentos'!AT7+'Fluxo de pagamentos'!AT8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AO17" s="32">
+        <f>('Fluxo de pagamentos'!AU7+'Fluxo de pagamentos'!AU8)*35.3%</f>
+        <v>230509</v>
+      </c>
+      <c r="AP17" s="32">
+        <f>('Fluxo de pagamentos'!AV7+'Fluxo de pagamentos'!AV8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="32">
+        <f>('Fluxo de pagamentos'!AW7+'Fluxo de pagamentos'!AW8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AR17" s="32">
+        <f>('Fluxo de pagamentos'!AX7+'Fluxo de pagamentos'!AX8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AS17" s="32">
+        <f>('Fluxo de pagamentos'!AY7+'Fluxo de pagamentos'!AY8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AT17" s="32">
+        <f>('Fluxo de pagamentos'!AZ7+'Fluxo de pagamentos'!AZ8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AU17" s="32">
+        <f>('Fluxo de pagamentos'!BA7+'Fluxo de pagamentos'!BA8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AV17" s="32">
+        <f>('Fluxo de pagamentos'!BB7+'Fluxo de pagamentos'!BB8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AW17" s="32">
+        <f>('Fluxo de pagamentos'!BC7+'Fluxo de pagamentos'!BC8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AX17" s="32">
+        <f>('Fluxo de pagamentos'!BD7+'Fluxo de pagamentos'!BD8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AY17" s="32">
+        <f>('Fluxo de pagamentos'!BE7+'Fluxo de pagamentos'!BE8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="32">
+        <f>('Fluxo de pagamentos'!BF7+'Fluxo de pagamentos'!BF8)*35.3%</f>
+        <v>0</v>
+      </c>
+      <c r="BA17" s="32">
+        <f>('Fluxo de pagamentos'!BG7+'Fluxo de pagamentos'!BG8)*35.3%</f>
+        <v>230509</v>
+      </c>
+      <c r="BB17" s="41">
+        <f>SUM(E17:BA17)</f>
+        <v>4085692.8718100009</v>
+      </c>
+      <c r="BC17" s="43"/>
+      <c r="BD17" s="42"/>
+      <c r="BE17" s="43"/>
+      <c r="BF17" s="43"/>
+      <c r="BG17" s="43"/>
+      <c r="BH17" s="43"/>
+      <c r="BI17" s="43"/>
+      <c r="BJ17" s="43"/>
+      <c r="BK17" s="43"/>
+      <c r="BL17" s="43"/>
+      <c r="BM17" s="43"/>
+      <c r="BN17" s="43"/>
+      <c r="BO17" s="43"/>
+      <c r="BP17" s="43"/>
+      <c r="BQ17" s="43"/>
+      <c r="BR17" s="43"/>
+      <c r="BS17" s="43"/>
+      <c r="BT17" s="43"/>
+      <c r="BU17" s="43"/>
+      <c r="BV17" s="43"/>
+      <c r="BW17" s="43"/>
+      <c r="BX17" s="43"/>
+      <c r="BY17" s="43"/>
+      <c r="BZ17" s="43"/>
+      <c r="CA17" s="43"/>
+      <c r="CB17" s="43"/>
+      <c r="CC17" s="43"/>
+      <c r="CD17" s="43"/>
+    </row>
+    <row r="18" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="32">
+        <f>SUM(D16:D17)</f>
+        <v>27357020.140693706</v>
+      </c>
+      <c r="E18" s="32">
+        <f>SUM(E16:E17)</f>
+        <v>5621745.8024486918</v>
+      </c>
+      <c r="F18" s="32">
+        <f>SUM(F16:F17)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="32">
+        <f>SUM(G16:G17)</f>
+        <v>272521.32676999999</v>
+      </c>
+      <c r="H18" s="32">
+        <f>SUM(H16:H17)</f>
+        <v>300764.26725999994</v>
+      </c>
+      <c r="I18" s="32">
+        <f>SUM(I16:I17)</f>
+        <v>272521.32676999999</v>
+      </c>
+      <c r="J18" s="32">
+        <f>SUM(J16:J17)</f>
+        <v>190659.92782999997</v>
+      </c>
+      <c r="K18" s="32">
+        <f>SUM(K16:K17)</f>
+        <v>162425.63583999997</v>
+      </c>
+      <c r="L18" s="32">
+        <f>SUM(L16:L17)</f>
+        <v>189847.46656</v>
+      </c>
+      <c r="M18" s="32">
+        <f>SUM(M16:M17)</f>
+        <v>156602.22308</v>
+      </c>
+      <c r="N18" s="32">
+        <f>SUM(N16:N17)</f>
+        <v>184277.09125999999</v>
+      </c>
+      <c r="O18" s="32">
+        <f>SUM(O16:O17)</f>
+        <v>72183.099100000007</v>
+      </c>
+      <c r="P18" s="32">
+        <f>SUM(P16:P17)</f>
+        <v>72186.03959</v>
+      </c>
+      <c r="Q18" s="32">
+        <f>SUM(Q16:Q17)</f>
+        <v>72183.099100000007</v>
+      </c>
+      <c r="R18" s="32">
+        <f>SUM(R16:R17)</f>
+        <v>72186.03959</v>
+      </c>
+      <c r="S18" s="32">
+        <f>SUM(S16:S17)</f>
+        <v>71236.091879999993</v>
+      </c>
+      <c r="T18" s="32">
+        <f>SUM(T16:T17)</f>
+        <v>71239.046489999993</v>
+      </c>
+      <c r="U18" s="32">
+        <f>SUM(U16:U17)</f>
+        <v>30055.687269999999</v>
+      </c>
+      <c r="V18" s="32">
+        <f>SUM(V16:V17)</f>
+        <v>30055.687269999999</v>
+      </c>
+      <c r="W18" s="32">
+        <f>SUM(W16:W17)</f>
+        <v>29182.326440000001</v>
+      </c>
+      <c r="X18" s="32">
+        <f>SUM(X16:X17)</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="Y18" s="32">
+        <f>SUM(Y16:Y17)</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="Z18" s="32">
+        <f>SUM(Z16:Z17)</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="AA18" s="32">
+        <f>SUM(AA16:AA17)</f>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="32">
+        <f>SUM(AB16:AB17)</f>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="32">
+        <f>SUM(AC16:AC17)</f>
+        <v>1893917.5750232993</v>
+      </c>
+      <c r="AD18" s="32">
+        <f>SUM(AD16:AD17)</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="32">
+        <f>SUM(AE16:AE17)</f>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="32">
+        <f>SUM(AF16:AF17)</f>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="32">
+        <f>SUM(AG16:AG17)</f>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="32">
+        <f>SUM(AH16:AH17)</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="32">
+        <f>SUM(AI16:AI17)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="32">
+        <f>SUM(AJ16:AJ17)</f>
+        <v>0</v>
+      </c>
+      <c r="AK18" s="32">
+        <f>SUM(AK16:AK17)</f>
+        <v>0</v>
+      </c>
+      <c r="AL18" s="32">
+        <f>SUM(AL16:AL17)</f>
+        <v>0</v>
+      </c>
+      <c r="AM18" s="32">
+        <f>SUM(AM16:AM17)</f>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="32">
+        <f>SUM(AN16:AN17)</f>
+        <v>0</v>
+      </c>
+      <c r="AO18" s="32">
+        <f>SUM(AO16:AO17)</f>
+        <v>8753095.4457058571</v>
+      </c>
+      <c r="AP18" s="32">
+        <f>SUM(AP16:AP17)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="32">
+        <f>SUM(AQ16:AQ17)</f>
+        <v>0</v>
+      </c>
+      <c r="AR18" s="32">
+        <f>SUM(AR16:AR17)</f>
+        <v>0</v>
+      </c>
+      <c r="AS18" s="32">
+        <f>SUM(AS16:AS17)</f>
+        <v>0</v>
+      </c>
+      <c r="AT18" s="32">
+        <f>SUM(AT16:AT17)</f>
+        <v>0</v>
+      </c>
+      <c r="AU18" s="32">
+        <f>SUM(AU16:AU17)</f>
+        <v>0</v>
+      </c>
+      <c r="AV18" s="32">
+        <f>SUM(AV16:AV17)</f>
+        <v>0</v>
+      </c>
+      <c r="AW18" s="32">
+        <f>SUM(AW16:AW17)</f>
+        <v>0</v>
+      </c>
+      <c r="AX18" s="32">
+        <f>SUM(AX16:AX17)</f>
+        <v>0</v>
+      </c>
+      <c r="AY18" s="32">
+        <f>SUM(AY16:AY17)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="32">
+        <f>SUM(AZ16:AZ17)</f>
+        <v>0</v>
+      </c>
+      <c r="BA18" s="32">
+        <f>SUM(BA16:BA17)</f>
+        <v>8753095.4457058571</v>
+      </c>
+      <c r="BB18" s="41">
+        <f>SUM(E18:BA18)</f>
+        <v>27357020.140693706</v>
+      </c>
+      <c r="BC18" s="43"/>
+      <c r="BD18" s="42"/>
+      <c r="BE18" s="43"/>
+      <c r="BF18" s="43"/>
+      <c r="BG18" s="43"/>
+      <c r="BH18" s="43"/>
+      <c r="BI18" s="43"/>
+      <c r="BJ18" s="43"/>
+      <c r="BK18" s="43"/>
+      <c r="BL18" s="43"/>
+      <c r="BM18" s="43"/>
+      <c r="BN18" s="43"/>
+      <c r="BO18" s="43"/>
+      <c r="BP18" s="43"/>
+      <c r="BQ18" s="43"/>
+      <c r="BR18" s="43"/>
+      <c r="BS18" s="43"/>
+      <c r="BT18" s="43"/>
+      <c r="BU18" s="43"/>
+      <c r="BV18" s="43"/>
+      <c r="BW18" s="43"/>
+      <c r="BX18" s="43"/>
+      <c r="BY18" s="43"/>
+      <c r="BZ18" s="43"/>
+      <c r="CA18" s="43"/>
+      <c r="CB18" s="43"/>
+      <c r="CC18" s="43"/>
+      <c r="CD18" s="43"/>
+    </row>
+    <row r="19" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A19" t="str">
+        <f>A4</f>
+        <v>Cessão Imobilizado</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="30">
+        <f>D4</f>
+        <v>28762280.73</v>
+      </c>
+      <c r="E19" s="30">
+        <f>D19</f>
+        <v>28762280.73</v>
+      </c>
+      <c r="F19" s="30">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="30">
+        <f>G4</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="30">
+        <f>H4</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="30">
+        <f>I4</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="30">
+        <f>J4</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="30">
+        <f>K4</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="30">
+        <f>L4</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="30">
+        <f>M4</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="30">
+        <f>N4</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="30">
+        <f>O4</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="30">
+        <f>P4</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="30">
+        <f>Q4</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="30">
+        <f>R4</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="30">
+        <f>S4</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="30">
+        <f>T4</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="30">
+        <f>U4</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="30">
+        <f>V4</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="30">
+        <f>W4</f>
+        <v>0</v>
+      </c>
+      <c r="X19" s="30">
+        <f>X4</f>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="30">
+        <f>Y4</f>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="30">
+        <f>Z4</f>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="30">
+        <f>AA4</f>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="30">
+        <f>AB4</f>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="30">
+        <f>AC4</f>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="30">
+        <f>AD4</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="30">
+        <f>AE4</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="30">
+        <f>AF4</f>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="30">
+        <f>AG4</f>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="30">
+        <f>AH4</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="30">
+        <f>AI4</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="30">
+        <f>AJ4</f>
+        <v>0</v>
+      </c>
+      <c r="AK19" s="30">
+        <f>AK4</f>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="30">
+        <f>AL4</f>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="30">
+        <f>AM4</f>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="30">
+        <f>AN4</f>
+        <v>0</v>
+      </c>
+      <c r="AO19" s="30">
+        <f>AO4</f>
+        <v>0</v>
+      </c>
+      <c r="AP19" s="30">
+        <f>AP4</f>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="30">
+        <f>AQ4</f>
+        <v>0</v>
+      </c>
+      <c r="AR19" s="30">
+        <f>AR4</f>
+        <v>0</v>
+      </c>
+      <c r="AS19" s="30">
+        <f>AS4</f>
+        <v>0</v>
+      </c>
+      <c r="AT19" s="30">
+        <f>AT4</f>
+        <v>0</v>
+      </c>
+      <c r="AU19" s="30">
+        <f>AU4</f>
+        <v>0</v>
+      </c>
+      <c r="AV19" s="30">
+        <f>AV4</f>
+        <v>0</v>
+      </c>
+      <c r="AW19" s="30">
+        <f>AW4</f>
+        <v>0</v>
+      </c>
+      <c r="AX19" s="30">
+        <f>AX4</f>
+        <v>0</v>
+      </c>
+      <c r="AY19" s="30">
+        <f>AY4</f>
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="30">
+        <f>AZ4</f>
+        <v>0</v>
+      </c>
+      <c r="BA19" s="30">
+        <f>BA4</f>
+        <v>0</v>
+      </c>
+      <c r="BB19" s="30">
+        <f>SUM(E19:BA19)</f>
+        <v>28762280.73</v>
+      </c>
+      <c r="BC19" s="28"/>
+      <c r="BD19" s="28"/>
+      <c r="BE19" s="28"/>
+      <c r="BF19" s="28"/>
+      <c r="BG19" s="28"/>
+      <c r="BH19" s="28"/>
+      <c r="BI19" s="28"/>
+      <c r="BJ19" s="28"/>
+      <c r="BK19" s="28"/>
+      <c r="BL19" s="28"/>
+      <c r="BM19" s="28"/>
+      <c r="BN19" s="28"/>
+      <c r="BO19" s="28"/>
+      <c r="BP19" s="28"/>
+      <c r="BQ19" s="28"/>
+      <c r="BR19" s="28"/>
+      <c r="BS19" s="28"/>
+      <c r="BT19" s="28"/>
+      <c r="BU19" s="28"/>
+      <c r="BV19" s="28"/>
+      <c r="BW19" s="28"/>
+      <c r="BX19" s="28"/>
+      <c r="BY19" s="28"/>
+      <c r="BZ19" s="28"/>
+      <c r="CA19" s="28"/>
+      <c r="CB19" s="28"/>
+      <c r="CC19" s="28"/>
+      <c r="CD19" s="28"/>
+    </row>
+    <row r="20" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A20" t="str">
+        <f>A5</f>
+        <v>FTTx - Portas Iluminadas</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="29">
+        <f>D5</f>
+        <v>11239020</v>
+      </c>
+      <c r="E20" s="29">
+        <f>'Fluxo de pagamentos'!K36</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="29">
+        <f>'Fluxo de pagamentos'!L36</f>
+        <v>936585</v>
+      </c>
+      <c r="G20" s="29">
+        <f>'Fluxo de pagamentos'!M36</f>
+        <v>936585</v>
+      </c>
+      <c r="H20" s="29">
+        <f>'Fluxo de pagamentos'!N36</f>
+        <v>936585</v>
+      </c>
+      <c r="I20" s="29">
+        <f>'Fluxo de pagamentos'!O36</f>
+        <v>936585</v>
+      </c>
+      <c r="J20" s="29">
+        <f>'Fluxo de pagamentos'!P36</f>
+        <v>936585</v>
+      </c>
+      <c r="K20" s="29">
+        <f>'Fluxo de pagamentos'!Q36</f>
+        <v>936585</v>
+      </c>
+      <c r="L20" s="29">
+        <f>'Fluxo de pagamentos'!R36</f>
+        <v>936585</v>
+      </c>
+      <c r="M20" s="29">
+        <f>'Fluxo de pagamentos'!S36</f>
+        <v>936585</v>
+      </c>
+      <c r="N20" s="29">
+        <f>'Fluxo de pagamentos'!T36</f>
+        <v>936585</v>
+      </c>
+      <c r="O20" s="29">
+        <f>'Fluxo de pagamentos'!U36</f>
+        <v>936585</v>
+      </c>
+      <c r="P20" s="29">
+        <f>'Fluxo de pagamentos'!V36</f>
+        <v>936585</v>
+      </c>
+      <c r="Q20" s="29">
+        <f>'Fluxo de pagamentos'!W36</f>
+        <v>936585</v>
+      </c>
+      <c r="R20" s="29">
+        <f>'Fluxo de pagamentos'!X36</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="29">
+        <f>'Fluxo de pagamentos'!Y36</f>
+        <v>0</v>
+      </c>
+      <c r="T20" s="29">
+        <f>'Fluxo de pagamentos'!Z36</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="29">
+        <f>'Fluxo de pagamentos'!AA36</f>
+        <v>0</v>
+      </c>
+      <c r="V20" s="29">
+        <f>'Fluxo de pagamentos'!AB36</f>
+        <v>0</v>
+      </c>
+      <c r="W20" s="29">
+        <f>'Fluxo de pagamentos'!AC36</f>
+        <v>0</v>
+      </c>
+      <c r="X20" s="29">
+        <f>'Fluxo de pagamentos'!AD36</f>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="29">
+        <f>'Fluxo de pagamentos'!AE36</f>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="29">
+        <f>'Fluxo de pagamentos'!AF36</f>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="29">
+        <f>'Fluxo de pagamentos'!AG36</f>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="29">
+        <f>'Fluxo de pagamentos'!AH36</f>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="29">
+        <f>'Fluxo de pagamentos'!AI36</f>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="29">
+        <f>'Fluxo de pagamentos'!AJ36</f>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="29">
+        <f>'Fluxo de pagamentos'!AK36</f>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="29">
+        <f>'Fluxo de pagamentos'!AL36</f>
+        <v>0</v>
+      </c>
+      <c r="AG20" s="29">
+        <f>'Fluxo de pagamentos'!AM36</f>
+        <v>0</v>
+      </c>
+      <c r="AH20" s="29">
+        <f>'Fluxo de pagamentos'!AN36</f>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="29">
+        <f>'Fluxo de pagamentos'!AO36</f>
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="29">
+        <f>'Fluxo de pagamentos'!AP36</f>
+        <v>0</v>
+      </c>
+      <c r="AK20" s="29">
+        <f>'Fluxo de pagamentos'!AQ36</f>
+        <v>0</v>
+      </c>
+      <c r="AL20" s="29">
+        <f>'Fluxo de pagamentos'!AR36</f>
+        <v>0</v>
+      </c>
+      <c r="AM20" s="29">
+        <f>'Fluxo de pagamentos'!AS36</f>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="29">
+        <f>'Fluxo de pagamentos'!AT36</f>
+        <v>0</v>
+      </c>
+      <c r="AO20" s="29">
+        <f>'Fluxo de pagamentos'!AU36</f>
+        <v>0</v>
+      </c>
+      <c r="AP20" s="29">
+        <f>'Fluxo de pagamentos'!AV36</f>
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="29">
+        <f>'Fluxo de pagamentos'!AW36</f>
+        <v>0</v>
+      </c>
+      <c r="AR20" s="29">
+        <f>'Fluxo de pagamentos'!AX36</f>
+        <v>0</v>
+      </c>
+      <c r="AS20" s="29">
+        <f>'Fluxo de pagamentos'!AY36</f>
+        <v>0</v>
+      </c>
+      <c r="AT20" s="29">
+        <f>'Fluxo de pagamentos'!AZ36</f>
+        <v>0</v>
+      </c>
+      <c r="AU20" s="29">
+        <f>'Fluxo de pagamentos'!BA36</f>
+        <v>0</v>
+      </c>
+      <c r="AV20" s="29">
+        <f>'Fluxo de pagamentos'!BB36</f>
+        <v>0</v>
+      </c>
+      <c r="AW20" s="29">
+        <f>'Fluxo de pagamentos'!BC36</f>
+        <v>0</v>
+      </c>
+      <c r="AX20" s="29">
+        <f>'Fluxo de pagamentos'!BD36</f>
+        <v>0</v>
+      </c>
+      <c r="AY20" s="29">
+        <f>'Fluxo de pagamentos'!BE36</f>
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="29">
+        <f>'Fluxo de pagamentos'!BF36</f>
+        <v>0</v>
+      </c>
+      <c r="BA20" s="29">
+        <f>'Fluxo de pagamentos'!BG36</f>
+        <v>0</v>
+      </c>
+      <c r="BB20" s="30">
+        <f>SUM(E20:BA20)</f>
+        <v>11239020</v>
+      </c>
+    </row>
+    <row r="21" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A21" t="str">
+        <f>A6</f>
+        <v>Setup</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="29">
+        <f>D6</f>
+        <v>44560980.313019089</v>
+      </c>
+      <c r="E21" s="29">
+        <f>'Fluxo de pagamentos'!K37</f>
+        <v>21432792.093905725</v>
+      </c>
+      <c r="F21" s="29">
+        <f>'Fluxo de pagamentos'!L37</f>
+        <v>319098.83000000007</v>
+      </c>
+      <c r="G21" s="29">
+        <f>'Fluxo de pagamentos'!M37</f>
+        <v>319098.83000000007</v>
+      </c>
+      <c r="H21" s="29">
+        <f>'Fluxo de pagamentos'!N37</f>
+        <v>319098.83000000007</v>
+      </c>
+      <c r="I21" s="29">
+        <f>'Fluxo de pagamentos'!O37</f>
+        <v>268692.50666666654</v>
+      </c>
+      <c r="J21" s="29">
+        <f>'Fluxo de pagamentos'!P37</f>
+        <v>268692.50666666654</v>
+      </c>
+      <c r="K21" s="29">
+        <f>'Fluxo de pagamentos'!Q37</f>
+        <v>268692.50666666654</v>
+      </c>
+      <c r="L21" s="29">
+        <f>'Fluxo de pagamentos'!R37</f>
+        <v>358286.56666666671</v>
+      </c>
+      <c r="M21" s="29">
+        <f>'Fluxo de pagamentos'!S37</f>
+        <v>358286.56666666671</v>
+      </c>
+      <c r="N21" s="29">
+        <f>'Fluxo de pagamentos'!T37</f>
+        <v>358286.56666666671</v>
+      </c>
+      <c r="O21" s="29">
+        <f>'Fluxo de pagamentos'!U37</f>
+        <v>654957.52333333308</v>
+      </c>
+      <c r="P21" s="29">
+        <f>'Fluxo de pagamentos'!V37</f>
+        <v>654957.52333333308</v>
+      </c>
+      <c r="Q21" s="29">
+        <f>'Fluxo de pagamentos'!W37</f>
+        <v>654957.52333333308</v>
+      </c>
+      <c r="R21" s="29">
+        <f>'Fluxo de pagamentos'!X37</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="29">
+        <f>'Fluxo de pagamentos'!Y37</f>
+        <v>0</v>
+      </c>
+      <c r="T21" s="29">
+        <f>'Fluxo de pagamentos'!Z37</f>
+        <v>0</v>
+      </c>
+      <c r="U21" s="29">
+        <f>'Fluxo de pagamentos'!AA37</f>
+        <v>0</v>
+      </c>
+      <c r="V21" s="29">
+        <f>'Fluxo de pagamentos'!AB37</f>
+        <v>0</v>
+      </c>
+      <c r="W21" s="29">
+        <f>'Fluxo de pagamentos'!AC37</f>
+        <v>0</v>
+      </c>
+      <c r="X21" s="29">
+        <f>'Fluxo de pagamentos'!AD37</f>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="29">
+        <f>'Fluxo de pagamentos'!AE37</f>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="29">
+        <f>'Fluxo de pagamentos'!AF37</f>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="29">
+        <f>'Fluxo de pagamentos'!AG37</f>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="29">
+        <f>'Fluxo de pagamentos'!AH37</f>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="29">
+        <f>'Fluxo de pagamentos'!AI37</f>
+        <v>18325081.939113364</v>
+      </c>
+      <c r="AD21" s="29">
+        <f>'Fluxo de pagamentos'!AJ37</f>
+        <v>0</v>
+      </c>
+      <c r="AE21" s="29">
+        <f>'Fluxo de pagamentos'!AK37</f>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="29">
+        <f>'Fluxo de pagamentos'!AL37</f>
+        <v>0</v>
+      </c>
+      <c r="AG21" s="29">
+        <f>'Fluxo de pagamentos'!AM37</f>
+        <v>0</v>
+      </c>
+      <c r="AH21" s="29">
+        <f>'Fluxo de pagamentos'!AN37</f>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="29">
+        <f>'Fluxo de pagamentos'!AO37</f>
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="29">
+        <f>'Fluxo de pagamentos'!AP37</f>
+        <v>0</v>
+      </c>
+      <c r="AK21" s="29">
+        <f>'Fluxo de pagamentos'!AQ37</f>
+        <v>0</v>
+      </c>
+      <c r="AL21" s="29">
+        <f>'Fluxo de pagamentos'!AR37</f>
+        <v>0</v>
+      </c>
+      <c r="AM21" s="29">
+        <f>'Fluxo de pagamentos'!AS37</f>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="29">
+        <f>'Fluxo de pagamentos'!AT37</f>
+        <v>0</v>
+      </c>
+      <c r="AO21" s="29">
+        <f>'Fluxo de pagamentos'!AU37</f>
+        <v>0</v>
+      </c>
+      <c r="AP21" s="29">
+        <f>'Fluxo de pagamentos'!AV37</f>
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="29">
+        <f>'Fluxo de pagamentos'!AW37</f>
+        <v>0</v>
+      </c>
+      <c r="AR21" s="29">
+        <f>'Fluxo de pagamentos'!AX37</f>
+        <v>0</v>
+      </c>
+      <c r="AS21" s="29">
+        <f>'Fluxo de pagamentos'!AY37</f>
+        <v>0</v>
+      </c>
+      <c r="AT21" s="29">
+        <f>'Fluxo de pagamentos'!AZ37</f>
+        <v>0</v>
+      </c>
+      <c r="AU21" s="29">
+        <f>'Fluxo de pagamentos'!BA37</f>
+        <v>0</v>
+      </c>
+      <c r="AV21" s="29">
+        <f>'Fluxo de pagamentos'!BB37</f>
+        <v>0</v>
+      </c>
+      <c r="AW21" s="29">
+        <f>'Fluxo de pagamentos'!BC37</f>
+        <v>0</v>
+      </c>
+      <c r="AX21" s="29">
+        <f>'Fluxo de pagamentos'!BD37</f>
+        <v>0</v>
+      </c>
+      <c r="AY21" s="29">
+        <f>'Fluxo de pagamentos'!BE37</f>
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="29">
+        <f>'Fluxo de pagamentos'!BF37</f>
+        <v>0</v>
+      </c>
+      <c r="BA21" s="29">
+        <f>'Fluxo de pagamentos'!BG37</f>
+        <v>0</v>
+      </c>
+      <c r="BB21" s="30">
+        <f>SUM(E21:BA21)</f>
+        <v>44560980.313019082</v>
+      </c>
+      <c r="BC21" s="30">
+        <f>BB6-BB21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>A7</f>
+        <v>Serviço Suporte N3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="29">
+        <f>D7</f>
+        <v>3242640</v>
+      </c>
+      <c r="E22" s="29">
+        <f>'Fluxo de pagamentos'!K38</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="29">
+        <f>'Fluxo de pagamentos'!L38</f>
+        <v>270220</v>
+      </c>
+      <c r="G22" s="29">
+        <f>'Fluxo de pagamentos'!M38</f>
+        <v>270220</v>
+      </c>
+      <c r="H22" s="29">
+        <f>'Fluxo de pagamentos'!N38</f>
+        <v>270220</v>
+      </c>
+      <c r="I22" s="29">
+        <f>'Fluxo de pagamentos'!O38</f>
+        <v>270220</v>
+      </c>
+      <c r="J22" s="29">
+        <f>'Fluxo de pagamentos'!P38</f>
+        <v>270220</v>
+      </c>
+      <c r="K22" s="29">
+        <f>'Fluxo de pagamentos'!Q38</f>
+        <v>270220</v>
+      </c>
+      <c r="L22" s="29">
+        <f>'Fluxo de pagamentos'!R38</f>
+        <v>270220</v>
+      </c>
+      <c r="M22" s="29">
+        <f>'Fluxo de pagamentos'!S38</f>
+        <v>270220</v>
+      </c>
+      <c r="N22" s="29">
+        <f>'Fluxo de pagamentos'!T38</f>
+        <v>270220</v>
+      </c>
+      <c r="O22" s="29">
+        <f>'Fluxo de pagamentos'!U38</f>
+        <v>270220</v>
+      </c>
+      <c r="P22" s="29">
+        <f>'Fluxo de pagamentos'!V38</f>
+        <v>270220</v>
+      </c>
+      <c r="Q22" s="29">
+        <f>'Fluxo de pagamentos'!W38</f>
+        <v>270220</v>
+      </c>
+      <c r="R22" s="29">
+        <f>'Fluxo de pagamentos'!X38</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="29">
+        <f>'Fluxo de pagamentos'!Y38</f>
+        <v>0</v>
+      </c>
+      <c r="T22" s="29">
+        <f>'Fluxo de pagamentos'!Z38</f>
+        <v>0</v>
+      </c>
+      <c r="U22" s="29">
+        <f>'Fluxo de pagamentos'!AA38</f>
+        <v>0</v>
+      </c>
+      <c r="V22" s="29">
+        <f>'Fluxo de pagamentos'!AB38</f>
+        <v>0</v>
+      </c>
+      <c r="W22" s="29">
+        <f>'Fluxo de pagamentos'!AC38</f>
+        <v>0</v>
+      </c>
+      <c r="X22" s="29">
+        <f>'Fluxo de pagamentos'!AD38</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="29">
+        <f>'Fluxo de pagamentos'!AE38</f>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="29">
+        <f>'Fluxo de pagamentos'!AF38</f>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="29">
+        <f>'Fluxo de pagamentos'!AG38</f>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="29">
+        <f>'Fluxo de pagamentos'!AH38</f>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="29">
+        <f>'Fluxo de pagamentos'!AI38</f>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="29">
+        <f>'Fluxo de pagamentos'!AJ38</f>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="29">
+        <f>'Fluxo de pagamentos'!AK38</f>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="29">
+        <f>'Fluxo de pagamentos'!AL38</f>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="29">
+        <f>'Fluxo de pagamentos'!AM38</f>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="29">
+        <f>'Fluxo de pagamentos'!AN38</f>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="29">
+        <f>'Fluxo de pagamentos'!AO38</f>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="29">
+        <f>'Fluxo de pagamentos'!AP38</f>
+        <v>0</v>
+      </c>
+      <c r="AK22" s="29">
+        <f>'Fluxo de pagamentos'!AQ38</f>
+        <v>0</v>
+      </c>
+      <c r="AL22" s="29">
+        <f>'Fluxo de pagamentos'!AR38</f>
+        <v>0</v>
+      </c>
+      <c r="AM22" s="29">
+        <f>'Fluxo de pagamentos'!AS38</f>
+        <v>0</v>
+      </c>
+      <c r="AN22" s="29">
+        <f>'Fluxo de pagamentos'!AT38</f>
+        <v>0</v>
+      </c>
+      <c r="AO22" s="29">
+        <f>'Fluxo de pagamentos'!AU38</f>
+        <v>0</v>
+      </c>
+      <c r="AP22" s="29">
+        <f>'Fluxo de pagamentos'!AV38</f>
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="29">
+        <f>'Fluxo de pagamentos'!AW38</f>
+        <v>0</v>
+      </c>
+      <c r="AR22" s="29">
+        <f>'Fluxo de pagamentos'!AX38</f>
+        <v>0</v>
+      </c>
+      <c r="AS22" s="29">
+        <f>'Fluxo de pagamentos'!AY38</f>
+        <v>0</v>
+      </c>
+      <c r="AT22" s="29">
+        <f>'Fluxo de pagamentos'!AZ38</f>
+        <v>0</v>
+      </c>
+      <c r="AU22" s="29">
+        <f>'Fluxo de pagamentos'!BA38</f>
+        <v>0</v>
+      </c>
+      <c r="AV22" s="29">
+        <f>'Fluxo de pagamentos'!BB38</f>
+        <v>0</v>
+      </c>
+      <c r="AW22" s="29">
+        <f>'Fluxo de pagamentos'!BC38</f>
+        <v>0</v>
+      </c>
+      <c r="AX22" s="29">
+        <f>'Fluxo de pagamentos'!BD38</f>
+        <v>0</v>
+      </c>
+      <c r="AY22" s="29">
+        <f>'Fluxo de pagamentos'!BE38</f>
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="29">
+        <f>'Fluxo de pagamentos'!BF38</f>
+        <v>0</v>
+      </c>
+      <c r="BA22" s="29">
+        <f>'Fluxo de pagamentos'!BG38</f>
+        <v>0</v>
+      </c>
+      <c r="BB22" s="30">
+        <f>SUM(E22:BA22)</f>
+        <v>3242640</v>
+      </c>
+    </row>
+    <row r="23" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="29">
+        <f>SUM(D20:D22)</f>
+        <v>59042640.313019089</v>
+      </c>
+      <c r="E23" s="29">
+        <f>SUM(E20:E22)</f>
+        <v>21432792.093905725</v>
+      </c>
+      <c r="F23" s="29">
+        <f>SUM(F20:F22)</f>
+        <v>1525903.83</v>
+      </c>
+      <c r="G23" s="29">
+        <f>SUM(G20:G22)</f>
+        <v>1525903.83</v>
+      </c>
+      <c r="H23" s="29">
+        <f>SUM(H20:H22)</f>
+        <v>1525903.83</v>
+      </c>
+      <c r="I23" s="29">
+        <f>SUM(I20:I22)</f>
+        <v>1475497.5066666666</v>
+      </c>
+      <c r="J23" s="29">
+        <f>SUM(J20:J22)</f>
+        <v>1475497.5066666666</v>
+      </c>
+      <c r="K23" s="29">
+        <f>SUM(K20:K22)</f>
+        <v>1475497.5066666666</v>
+      </c>
+      <c r="L23" s="29">
+        <f>SUM(L20:L22)</f>
+        <v>1565091.5666666667</v>
+      </c>
+      <c r="M23" s="29">
+        <f>SUM(M20:M22)</f>
+        <v>1565091.5666666667</v>
+      </c>
+      <c r="N23" s="29">
+        <f>SUM(N20:N22)</f>
+        <v>1565091.5666666667</v>
+      </c>
+      <c r="O23" s="29">
+        <f>SUM(O20:O22)</f>
+        <v>1861762.523333333</v>
+      </c>
+      <c r="P23" s="29">
+        <f>SUM(P20:P22)</f>
+        <v>1861762.523333333</v>
+      </c>
+      <c r="Q23" s="29">
+        <f>SUM(Q20:Q22)</f>
+        <v>1861762.523333333</v>
+      </c>
+      <c r="R23" s="29">
+        <f>SUM(R20:R22)</f>
+        <v>0</v>
+      </c>
+      <c r="S23" s="29">
+        <f>SUM(S20:S22)</f>
+        <v>0</v>
+      </c>
+      <c r="T23" s="29">
+        <f>SUM(T20:T22)</f>
+        <v>0</v>
+      </c>
+      <c r="U23" s="29">
+        <f>SUM(U20:U22)</f>
+        <v>0</v>
+      </c>
+      <c r="V23" s="29">
+        <f>SUM(V20:V22)</f>
+        <v>0</v>
+      </c>
+      <c r="W23" s="29">
+        <f>SUM(W20:W22)</f>
+        <v>0</v>
+      </c>
+      <c r="X23" s="29">
+        <f>SUM(X20:X22)</f>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="29">
+        <f>SUM(Y20:Y22)</f>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="29">
+        <f>SUM(Z20:Z22)</f>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="29">
+        <f>SUM(AA20:AA22)</f>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="29">
+        <f>SUM(AB20:AB22)</f>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="29">
+        <f>SUM(AC20:AC22)</f>
+        <v>18325081.939113364</v>
+      </c>
+      <c r="AD23" s="29">
+        <f>SUM(AD20:AD22)</f>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="29">
+        <f>SUM(AE20:AE22)</f>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="29">
+        <f>SUM(AF20:AF22)</f>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="29">
+        <f>SUM(AG20:AG22)</f>
+        <v>0</v>
+      </c>
+      <c r="AH23" s="29">
+        <f>SUM(AH20:AH22)</f>
+        <v>0</v>
+      </c>
+      <c r="AI23" s="29">
+        <f>SUM(AI20:AI22)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="29">
+        <f>SUM(AJ20:AJ22)</f>
+        <v>0</v>
+      </c>
+      <c r="AK23" s="29">
+        <f>SUM(AK20:AK22)</f>
+        <v>0</v>
+      </c>
+      <c r="AL23" s="29">
+        <f>SUM(AL20:AL22)</f>
+        <v>0</v>
+      </c>
+      <c r="AM23" s="29">
+        <f>SUM(AM20:AM22)</f>
+        <v>0</v>
+      </c>
+      <c r="AN23" s="29">
+        <f>SUM(AN20:AN22)</f>
+        <v>0</v>
+      </c>
+      <c r="AO23" s="29">
+        <f>SUM(AO20:AO22)</f>
+        <v>0</v>
+      </c>
+      <c r="AP23" s="29">
+        <f>SUM(AP20:AP22)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="29">
+        <f>SUM(AQ20:AQ22)</f>
+        <v>0</v>
+      </c>
+      <c r="AR23" s="29">
+        <f>SUM(AR20:AR22)</f>
+        <v>0</v>
+      </c>
+      <c r="AS23" s="29">
+        <f>SUM(AS20:AS22)</f>
+        <v>0</v>
+      </c>
+      <c r="AT23" s="29">
+        <f>SUM(AT20:AT22)</f>
+        <v>0</v>
+      </c>
+      <c r="AU23" s="29">
+        <f>SUM(AU20:AU22)</f>
+        <v>0</v>
+      </c>
+      <c r="AV23" s="29">
+        <f>SUM(AV20:AV22)</f>
+        <v>0</v>
+      </c>
+      <c r="AW23" s="29">
+        <f>SUM(AW20:AW22)</f>
+        <v>0</v>
+      </c>
+      <c r="AX23" s="29">
+        <f>SUM(AX20:AX22)</f>
+        <v>0</v>
+      </c>
+      <c r="AY23" s="29">
+        <f>SUM(AY20:AY22)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="29">
+        <f>SUM(AZ20:AZ22)</f>
+        <v>0</v>
+      </c>
+      <c r="BA23" s="29">
+        <f>SUM(BA20:BA22)</f>
+        <v>0</v>
+      </c>
+      <c r="BB23" s="29">
+        <f>SUM(BB20:BB22)</f>
+        <v>59042640.313019082</v>
+      </c>
+    </row>
+    <row r="24" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="29">
+        <f>SUM(D13:D22)</f>
+        <v>242795078.95698088</v>
+      </c>
+      <c r="E24" s="29">
+        <f>SUM(E20:E22)</f>
+        <v>21432792.093905725</v>
+      </c>
+      <c r="F24" s="29">
+        <f>SUM(F20:F22)</f>
+        <v>1525903.83</v>
+      </c>
+      <c r="G24" s="29">
+        <f>SUM(G20:G22)</f>
+        <v>1525903.83</v>
+      </c>
+      <c r="H24" s="29">
+        <f>SUM(H20:H22)</f>
+        <v>1525903.83</v>
+      </c>
+      <c r="I24" s="29">
+        <f>SUM(I20:I22)</f>
+        <v>1475497.5066666666</v>
+      </c>
+      <c r="J24" s="29">
+        <f>SUM(J20:J22)</f>
+        <v>1475497.5066666666</v>
+      </c>
+      <c r="K24" s="29">
+        <f>SUM(K20:K22)</f>
+        <v>1475497.5066666666</v>
+      </c>
+      <c r="L24" s="29">
+        <f>SUM(L20:L22)</f>
+        <v>1565091.5666666667</v>
+      </c>
+      <c r="M24" s="29">
+        <f>SUM(M20:M22)</f>
+        <v>1565091.5666666667</v>
+      </c>
+      <c r="N24" s="29">
+        <f>SUM(N20:N22)</f>
+        <v>1565091.5666666667</v>
+      </c>
+      <c r="O24" s="29">
+        <f>SUM(O20:O22)</f>
+        <v>1861762.523333333</v>
+      </c>
+      <c r="P24" s="29">
+        <f>SUM(P20:P22)</f>
+        <v>1861762.523333333</v>
+      </c>
+      <c r="Q24" s="29">
+        <f>SUM(Q20:Q22)</f>
+        <v>1861762.523333333</v>
+      </c>
+      <c r="R24" s="29">
+        <f>SUM(R20:R22)</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="29">
+        <f>SUM(S20:S22)</f>
+        <v>0</v>
+      </c>
+      <c r="T24" s="29">
+        <f>SUM(T20:T22)</f>
+        <v>0</v>
+      </c>
+      <c r="U24" s="29">
+        <f>SUM(U20:U22)</f>
+        <v>0</v>
+      </c>
+      <c r="V24" s="29">
+        <f>SUM(V20:V22)</f>
+        <v>0</v>
+      </c>
+      <c r="W24" s="29">
+        <f>SUM(W20:W22)</f>
+        <v>0</v>
+      </c>
+      <c r="X24" s="29">
+        <f>SUM(X20:X22)</f>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="29">
+        <f>SUM(Y20:Y22)</f>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="29">
+        <f>SUM(Z20:Z22)</f>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="29">
+        <f>SUM(AA20:AA22)</f>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="29">
+        <f>SUM(AB20:AB22)</f>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="29">
+        <f>SUM(AC20:AC22)</f>
+        <v>18325081.939113364</v>
+      </c>
+      <c r="AD24" s="29">
+        <f>SUM(AD20:AD22)</f>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="29">
+        <f>SUM(AE20:AE22)</f>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="29">
+        <f>SUM(AF20:AF22)</f>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="29">
+        <f>SUM(AG20:AG22)</f>
+        <v>0</v>
+      </c>
+      <c r="AH24" s="29">
+        <f>SUM(AH20:AH22)</f>
+        <v>0</v>
+      </c>
+      <c r="AI24" s="29">
+        <f>SUM(AI20:AI22)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="29">
+        <f>SUM(AJ20:AJ22)</f>
+        <v>0</v>
+      </c>
+      <c r="AK24" s="29">
+        <f>SUM(AK20:AK22)</f>
+        <v>0</v>
+      </c>
+      <c r="AL24" s="29">
+        <f>SUM(AL20:AL22)</f>
+        <v>0</v>
+      </c>
+      <c r="AM24" s="29">
+        <f>SUM(AM20:AM22)</f>
+        <v>0</v>
+      </c>
+      <c r="AN24" s="29">
+        <f>SUM(AN20:AN22)</f>
+        <v>0</v>
+      </c>
+      <c r="AO24" s="29">
+        <f>SUM(AO20:AO22)</f>
+        <v>0</v>
+      </c>
+      <c r="AP24" s="29">
+        <f>SUM(AP20:AP22)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="29">
+        <f>SUM(AQ20:AQ22)</f>
+        <v>0</v>
+      </c>
+      <c r="AR24" s="29">
+        <f>SUM(AR20:AR22)</f>
+        <v>0</v>
+      </c>
+      <c r="AS24" s="29">
+        <f>SUM(AS20:AS22)</f>
+        <v>0</v>
+      </c>
+      <c r="AT24" s="29">
+        <f>SUM(AT20:AT22)</f>
+        <v>0</v>
+      </c>
+      <c r="AU24" s="29">
+        <f>SUM(AU20:AU22)</f>
+        <v>0</v>
+      </c>
+      <c r="AV24" s="29">
+        <f>SUM(AV20:AV22)</f>
+        <v>0</v>
+      </c>
+      <c r="AW24" s="29">
+        <f>SUM(AW20:AW22)</f>
+        <v>0</v>
+      </c>
+      <c r="AX24" s="29">
+        <f>SUM(AX20:AX22)</f>
+        <v>0</v>
+      </c>
+      <c r="AY24" s="29">
+        <f>SUM(AY20:AY22)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ24" s="29">
+        <f>SUM(AZ20:AZ22)</f>
+        <v>0</v>
+      </c>
+      <c r="BA24" s="29">
+        <f>SUM(BA20:BA22)</f>
+        <v>0</v>
+      </c>
+      <c r="BB24" s="30">
+        <f>BB15+BB18+BB19+BB23</f>
+        <v>165300000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="29"/>
+      <c r="AA25" s="29"/>
+      <c r="AB25" s="29"/>
+      <c r="AC25" s="29"/>
+      <c r="AD25" s="29"/>
+      <c r="AE25" s="29"/>
+      <c r="AF25" s="29"/>
+      <c r="AG25" s="29"/>
+      <c r="AH25" s="29"/>
+      <c r="AI25" s="29"/>
+      <c r="AJ25" s="29"/>
+      <c r="AK25" s="29"/>
+      <c r="AL25" s="29"/>
+      <c r="AM25" s="29"/>
+      <c r="AN25" s="29"/>
+      <c r="AO25" s="29"/>
+      <c r="AP25" s="29"/>
+      <c r="AQ25" s="29"/>
+      <c r="AR25" s="29"/>
+      <c r="AS25" s="29"/>
+      <c r="AT25" s="29"/>
+      <c r="AU25" s="29"/>
+      <c r="AV25" s="29"/>
+      <c r="AW25" s="29"/>
+      <c r="AX25" s="29"/>
+      <c r="AY25" s="29"/>
+      <c r="AZ25" s="29"/>
+      <c r="BA25" s="29"/>
+      <c r="BB25" s="30"/>
+    </row>
+    <row r="26" spans="1:82" x14ac:dyDescent="0.2">
+      <c r="D26" s="30"/>
+    </row>
+    <row r="45" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E45" s="29"/>
+    </row>
+    <row r="48" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E48" s="29"/>
+    </row>
+    <row r="50" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E50" s="30"/>
+    </row>
+    <row r="51" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E51" s="30"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9218DFE5-209B-2241-8847-333DF7C258A2}">
+  <dimension ref="A2:W19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="18.1640625" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:23" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="N2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="R2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="U2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="V2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="W2" s="46" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="28">
+        <v>46295</v>
+      </c>
+      <c r="D3" s="28">
+        <v>46326</v>
+      </c>
+      <c r="E3" s="28">
+        <v>46356</v>
+      </c>
+      <c r="F3" s="28">
+        <v>46387</v>
+      </c>
+      <c r="G3" s="28">
+        <v>46418</v>
+      </c>
+      <c r="H3" s="28">
+        <v>46446</v>
+      </c>
+      <c r="I3" s="28">
+        <v>46477</v>
+      </c>
+      <c r="J3" s="28">
+        <v>46507</v>
+      </c>
+      <c r="K3" s="28">
+        <v>46538</v>
+      </c>
+      <c r="L3" s="28">
+        <v>46568</v>
+      </c>
+      <c r="M3" s="28">
+        <v>46599</v>
+      </c>
+      <c r="N3" s="28">
+        <v>46630</v>
+      </c>
+      <c r="O3" s="28">
+        <v>46660</v>
+      </c>
+      <c r="P3" s="28">
+        <v>46691</v>
+      </c>
+      <c r="Q3" s="28">
+        <v>46721</v>
+      </c>
+      <c r="R3" s="28">
+        <v>46752</v>
+      </c>
+      <c r="S3" s="28">
+        <v>46783</v>
+      </c>
+      <c r="T3" s="28">
+        <v>46812</v>
+      </c>
+      <c r="U3" s="28">
+        <v>46843</v>
+      </c>
+      <c r="V3" s="28">
+        <v>46873</v>
+      </c>
+      <c r="W3" s="46"/>
+    </row>
+    <row r="4" spans="1:23" s="33" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A4" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="32">
+        <f>'Fluxo de pagamentos'!M8</f>
+        <v>772015.09</v>
+      </c>
+      <c r="D4" s="32">
+        <f>'Fluxo de pagamentos'!N8</f>
+        <v>852023.41999999993</v>
+      </c>
+      <c r="E4" s="32">
+        <f>'Fluxo de pagamentos'!O8</f>
+        <v>772015.09</v>
+      </c>
+      <c r="F4" s="32">
+        <f>'Fluxo de pagamentos'!P8</f>
+        <v>540113.11</v>
+      </c>
+      <c r="G4" s="32">
+        <f>'Fluxo de pagamentos'!Q8</f>
+        <v>460129.27999999997</v>
+      </c>
+      <c r="H4" s="32">
+        <f>'Fluxo de pagamentos'!R8</f>
+        <v>537811.52</v>
+      </c>
+      <c r="I4" s="32">
+        <f>'Fluxo de pagamentos'!S8</f>
+        <v>443632.36</v>
+      </c>
+      <c r="J4" s="32">
+        <f>'Fluxo de pagamentos'!T8</f>
+        <v>522031.42</v>
+      </c>
+      <c r="K4" s="32">
+        <f>'Fluxo de pagamentos'!U8</f>
+        <v>204484.7</v>
+      </c>
+      <c r="L4" s="32">
+        <f>'Fluxo de pagamentos'!V8</f>
+        <v>204493.03</v>
+      </c>
+      <c r="M4" s="32">
+        <f>'Fluxo de pagamentos'!W8</f>
+        <v>204484.7</v>
+      </c>
+      <c r="N4" s="32">
+        <f>'Fluxo de pagamentos'!X8</f>
+        <v>204493.03</v>
+      </c>
+      <c r="O4" s="32">
+        <f>'Fluxo de pagamentos'!Y8</f>
+        <v>201801.96</v>
+      </c>
+      <c r="P4" s="32">
+        <f>'Fluxo de pagamentos'!Z8</f>
+        <v>201810.33</v>
+      </c>
+      <c r="Q4" s="32">
+        <f>'Fluxo de pagamentos'!AA8</f>
+        <v>85143.59</v>
+      </c>
+      <c r="R4" s="32">
+        <f>'Fluxo de pagamentos'!AB8</f>
+        <v>85143.59</v>
+      </c>
+      <c r="S4" s="32">
+        <f>'Fluxo de pagamentos'!AC8</f>
+        <v>82669.48000000001</v>
+      </c>
+      <c r="T4" s="32">
+        <f>'Fluxo de pagamentos'!AD8</f>
+        <v>80301.69</v>
+      </c>
+      <c r="U4" s="32">
+        <f>'Fluxo de pagamentos'!AE8</f>
+        <v>80301.69</v>
+      </c>
+      <c r="V4" s="32">
+        <f>'Fluxo de pagamentos'!AF8</f>
+        <v>80301.69</v>
+      </c>
+      <c r="W4" s="41">
+        <f>SUM(C4:V4)</f>
+        <v>6615200.7700000014</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="29">
+        <f>'Fluxo de pagamentos'!M9</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="29">
+        <f>'Fluxo de pagamentos'!N9</f>
+        <v>116666.66</v>
+      </c>
+      <c r="E5" s="29">
+        <f>'Fluxo de pagamentos'!O9</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="29">
+        <f>'Fluxo de pagamentos'!P9</f>
+        <v>116666.66</v>
+      </c>
+      <c r="G5" s="29">
+        <f>'Fluxo de pagamentos'!Q9</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="29">
+        <f>'Fluxo de pagamentos'!R9</f>
+        <v>116666.66</v>
+      </c>
+      <c r="I5" s="29">
+        <f>'Fluxo de pagamentos'!S9</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="29">
+        <f>'Fluxo de pagamentos'!T9</f>
+        <v>116666.66</v>
+      </c>
+      <c r="K5" s="29">
+        <f>'Fluxo de pagamentos'!U9</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="29">
+        <f>'Fluxo de pagamentos'!V9</f>
+        <v>116666.66</v>
+      </c>
+      <c r="M5" s="29">
+        <f>'Fluxo de pagamentos'!W9</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="29">
+        <f>'Fluxo de pagamentos'!X9</f>
+        <v>116666.66</v>
+      </c>
+      <c r="O5" s="29">
+        <f>'Fluxo de pagamentos'!Y9</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="29">
+        <f>'Fluxo de pagamentos'!Z9</f>
+        <v>116666.74</v>
+      </c>
+      <c r="Q5" s="29">
+        <f>'Fluxo de pagamentos'!AA9</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="29">
+        <f>'Fluxo de pagamentos'!AB9</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="29">
+        <f>'Fluxo de pagamentos'!AC9</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="29">
+        <f>'Fluxo de pagamentos'!AD9</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="29">
+        <f>'Fluxo de pagamentos'!AE9</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="29">
+        <f>'Fluxo de pagamentos'!AF9</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="30">
+        <f>SUM(C5:V5)</f>
+        <v>816666.70000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="29">
+        <f>'Fluxo de pagamentos'!M10</f>
+        <v>351670.07</v>
+      </c>
+      <c r="D6" s="29">
+        <f>'Fluxo de pagamentos'!N10</f>
+        <v>351670.07</v>
+      </c>
+      <c r="E6" s="29">
+        <f>'Fluxo de pagamentos'!O10</f>
+        <v>351670.07</v>
+      </c>
+      <c r="F6" s="29">
+        <f>'Fluxo de pagamentos'!P10</f>
+        <v>39759.760000000002</v>
+      </c>
+      <c r="G6" s="29">
+        <f>'Fluxo de pagamentos'!Q10</f>
+        <v>39784.26</v>
+      </c>
+      <c r="H6" s="29">
+        <f>'Fluxo de pagamentos'!R10</f>
+        <v>37458.17</v>
+      </c>
+      <c r="I6" s="29">
+        <f>'Fluxo de pagamentos'!S10</f>
+        <v>23287.34</v>
+      </c>
+      <c r="J6" s="29">
+        <f>'Fluxo de pagamentos'!T10</f>
+        <v>21678.07</v>
+      </c>
+      <c r="K6" s="29">
+        <f>'Fluxo de pagamentos'!U10</f>
+        <v>7524.68</v>
+      </c>
+      <c r="L6" s="29">
+        <f>'Fluxo de pagamentos'!V10</f>
+        <v>7524.68</v>
+      </c>
+      <c r="M6" s="29">
+        <f>'Fluxo de pagamentos'!W10</f>
+        <v>7524.68</v>
+      </c>
+      <c r="N6" s="29">
+        <f>'Fluxo de pagamentos'!X10</f>
+        <v>7524.68</v>
+      </c>
+      <c r="O6" s="29">
+        <f>'Fluxo de pagamentos'!Y10</f>
+        <v>4841.8999999999996</v>
+      </c>
+      <c r="P6" s="29">
+        <f>'Fluxo de pagamentos'!Z10</f>
+        <v>4841.8999999999996</v>
+      </c>
+      <c r="Q6" s="29">
+        <f>'Fluxo de pagamentos'!AA10</f>
+        <v>4841.8999999999996</v>
+      </c>
+      <c r="R6" s="29">
+        <f>'Fluxo de pagamentos'!AB10</f>
+        <v>4841.8999999999996</v>
+      </c>
+      <c r="S6" s="29">
+        <f>'Fluxo de pagamentos'!AC10</f>
+        <v>2367.79</v>
+      </c>
+      <c r="T6" s="29">
+        <f>'Fluxo de pagamentos'!AD10</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="29">
+        <f>'Fluxo de pagamentos'!AE10</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="29">
+        <f>'Fluxo de pagamentos'!AF10</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="30">
+        <f>SUM(C6:V6)</f>
+        <v>1268811.9199999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="29">
+        <f>'Fluxo de pagamentos'!M11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="D7" s="29">
+        <f>'Fluxo de pagamentos'!N11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="E7" s="29">
+        <f>'Fluxo de pagamentos'!O11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="F7" s="29">
+        <f>'Fluxo de pagamentos'!P11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="G7" s="29">
+        <f>'Fluxo de pagamentos'!Q11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="H7" s="29">
+        <f>'Fluxo de pagamentos'!R11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="I7" s="29">
+        <f>'Fluxo de pagamentos'!S11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="J7" s="29">
+        <f>'Fluxo de pagamentos'!T11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="K7" s="29">
+        <f>'Fluxo de pagamentos'!U11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="L7" s="29">
+        <f>'Fluxo de pagamentos'!V11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="M7" s="29">
+        <f>'Fluxo de pagamentos'!W11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="N7" s="29">
+        <f>'Fluxo de pagamentos'!X11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="O7" s="29">
+        <f>'Fluxo de pagamentos'!Y11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="P7" s="29">
+        <f>'Fluxo de pagamentos'!Z11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="Q7" s="29">
+        <f>'Fluxo de pagamentos'!AA11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="R7" s="29">
+        <f>'Fluxo de pagamentos'!AB11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="S7" s="29">
+        <f>'Fluxo de pagamentos'!AC11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="T7" s="29">
+        <f>'Fluxo de pagamentos'!AD11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="U7" s="29">
+        <f>'Fluxo de pagamentos'!AE11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="V7" s="29">
+        <f>'Fluxo de pagamentos'!AF11</f>
+        <v>1190.07</v>
+      </c>
+      <c r="W7" s="30">
+        <f>SUM(C7:V7)</f>
+        <v>23801.399999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="29">
+        <f>'Fluxo de pagamentos'!M12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="D8" s="29">
+        <f>'Fluxo de pagamentos'!N12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="E8" s="29">
+        <f>'Fluxo de pagamentos'!O12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="F8" s="29">
+        <f>'Fluxo de pagamentos'!P12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="G8" s="29">
+        <f>'Fluxo de pagamentos'!Q12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="H8" s="29">
+        <f>'Fluxo de pagamentos'!R12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="I8" s="29">
+        <f>'Fluxo de pagamentos'!S12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="J8" s="29">
+        <f>'Fluxo de pagamentos'!T12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="K8" s="29">
+        <f>'Fluxo de pagamentos'!U12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="L8" s="29">
+        <f>'Fluxo de pagamentos'!V12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="M8" s="29">
+        <f>'Fluxo de pagamentos'!W12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="N8" s="29">
+        <f>'Fluxo de pagamentos'!X12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="O8" s="29">
+        <f>'Fluxo de pagamentos'!Y12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="P8" s="29">
+        <f>'Fluxo de pagamentos'!Z12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="Q8" s="29">
+        <f>'Fluxo de pagamentos'!AA12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="R8" s="29">
+        <f>'Fluxo de pagamentos'!AB12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="S8" s="29">
+        <f>'Fluxo de pagamentos'!AC12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="T8" s="29">
+        <f>'Fluxo de pagamentos'!AD12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="U8" s="29">
+        <f>'Fluxo de pagamentos'!AE12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="V8" s="29">
+        <f>'Fluxo de pagamentos'!AF12</f>
+        <v>22376.07</v>
+      </c>
+      <c r="W8" s="30">
+        <f>SUM(C8:V8)</f>
+        <v>447521.40000000008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="29">
+        <f>'Fluxo de pagamentos'!M13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="D9" s="29">
+        <f>'Fluxo de pagamentos'!N13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="E9" s="29">
+        <f>'Fluxo de pagamentos'!O13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="F9" s="29">
+        <f>'Fluxo de pagamentos'!P13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="G9" s="29">
+        <f>'Fluxo de pagamentos'!Q13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="H9" s="29">
+        <f>'Fluxo de pagamentos'!R13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="I9" s="29">
+        <f>'Fluxo de pagamentos'!S13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="J9" s="29">
+        <f>'Fluxo de pagamentos'!T13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="K9" s="29">
+        <f>'Fluxo de pagamentos'!U13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="L9" s="29">
+        <f>'Fluxo de pagamentos'!V13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="M9" s="29">
+        <f>'Fluxo de pagamentos'!W13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="N9" s="29">
+        <f>'Fluxo de pagamentos'!X13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="O9" s="29">
+        <f>'Fluxo de pagamentos'!Y13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="P9" s="29">
+        <f>'Fluxo de pagamentos'!Z13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="Q9" s="29">
+        <f>'Fluxo de pagamentos'!AA13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="R9" s="29">
+        <f>'Fluxo de pagamentos'!AB13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="S9" s="29">
+        <f>'Fluxo de pagamentos'!AC13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="T9" s="29">
+        <f>'Fluxo de pagamentos'!AD13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="U9" s="29">
+        <f>'Fluxo de pagamentos'!AE13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="V9" s="29">
+        <f>'Fluxo de pagamentos'!AF13</f>
+        <v>10710.64</v>
+      </c>
+      <c r="W9" s="30">
+        <f>SUM(C9:V9)</f>
+        <v>214212.8000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="29">
+        <f>'Fluxo de pagamentos'!M14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="D10" s="29">
+        <f>'Fluxo de pagamentos'!N14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="E10" s="29">
+        <f>'Fluxo de pagamentos'!O14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="F10" s="29">
+        <f>'Fluxo de pagamentos'!P14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="G10" s="29">
+        <f>'Fluxo de pagamentos'!Q14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="H10" s="29">
+        <f>'Fluxo de pagamentos'!R14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="I10" s="29">
+        <f>'Fluxo de pagamentos'!S14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="J10" s="29">
+        <f>'Fluxo de pagamentos'!T14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="K10" s="29">
+        <f>'Fluxo de pagamentos'!U14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="L10" s="29">
+        <f>'Fluxo de pagamentos'!V14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="M10" s="29">
+        <f>'Fluxo de pagamentos'!W14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="N10" s="29">
+        <f>'Fluxo de pagamentos'!X14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="O10" s="29">
+        <f>'Fluxo de pagamentos'!Y14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="P10" s="29">
+        <f>'Fluxo de pagamentos'!Z14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="Q10" s="29">
+        <f>'Fluxo de pagamentos'!AA14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="R10" s="29">
+        <f>'Fluxo de pagamentos'!AB14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="S10" s="29">
+        <f>'Fluxo de pagamentos'!AC14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="T10" s="29">
+        <f>'Fluxo de pagamentos'!AD14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="U10" s="29">
+        <f>'Fluxo de pagamentos'!AE14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="V10" s="29">
+        <f>'Fluxo de pagamentos'!AF14</f>
+        <v>23648.84</v>
+      </c>
+      <c r="W10" s="30">
+        <f>SUM(C10:V10)</f>
+        <v>472976.80000000022</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="29">
+        <f>'Fluxo de pagamentos'!M15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="D11" s="29">
+        <f>'Fluxo de pagamentos'!N15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="E11" s="29">
+        <f>'Fluxo de pagamentos'!O15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="F11" s="29">
+        <f>'Fluxo de pagamentos'!P15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="G11" s="29">
+        <f>'Fluxo de pagamentos'!Q15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="H11" s="29">
+        <f>'Fluxo de pagamentos'!R15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="I11" s="29">
+        <f>'Fluxo de pagamentos'!S15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="J11" s="29">
+        <f>'Fluxo de pagamentos'!T15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="K11" s="29">
+        <f>'Fluxo de pagamentos'!U15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="L11" s="29">
+        <f>'Fluxo de pagamentos'!V15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="M11" s="29">
+        <f>'Fluxo de pagamentos'!W15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="N11" s="29">
+        <f>'Fluxo de pagamentos'!X15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="O11" s="29">
+        <f>'Fluxo de pagamentos'!Y15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="P11" s="29">
+        <f>'Fluxo de pagamentos'!Z15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="Q11" s="29">
+        <f>'Fluxo de pagamentos'!AA15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="R11" s="29">
+        <f>'Fluxo de pagamentos'!AB15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="S11" s="29">
+        <f>'Fluxo de pagamentos'!AC15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="T11" s="29">
+        <f>'Fluxo de pagamentos'!AD15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="U11" s="29">
+        <f>'Fluxo de pagamentos'!AE15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="V11" s="29">
+        <f>'Fluxo de pagamentos'!AF15</f>
+        <v>22376.07</v>
+      </c>
+      <c r="W11" s="30">
+        <f>SUM(C11:V11)</f>
+        <v>447521.40000000008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="29">
+        <f>'Fluxo de pagamentos'!M16</f>
+        <v>245737.9</v>
+      </c>
+      <c r="D12" s="29">
+        <f>'Fluxo de pagamentos'!N16</f>
+        <v>245737.9</v>
+      </c>
+      <c r="E12" s="29">
+        <f>'Fluxo de pagamentos'!O16</f>
+        <v>245737.9</v>
+      </c>
+      <c r="F12" s="29">
+        <f>'Fluxo de pagamentos'!P16</f>
+        <v>245737.9</v>
+      </c>
+      <c r="G12" s="29">
+        <f>'Fluxo de pagamentos'!Q16</f>
+        <v>245737.9</v>
+      </c>
+      <c r="H12" s="29">
+        <f>'Fluxo de pagamentos'!R16</f>
+        <v>245737.9</v>
+      </c>
+      <c r="I12" s="29">
+        <f>'Fluxo de pagamentos'!S16</f>
+        <v>245737.9</v>
+      </c>
+      <c r="J12" s="29">
+        <f>'Fluxo de pagamentos'!T16</f>
+        <v>245737.9</v>
+      </c>
+      <c r="K12" s="29">
+        <f>'Fluxo de pagamentos'!U16</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="29">
+        <f>'Fluxo de pagamentos'!V16</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="29">
+        <f>'Fluxo de pagamentos'!W16</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="29">
+        <f>'Fluxo de pagamentos'!X16</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="29">
+        <f>'Fluxo de pagamentos'!Y16</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="29">
+        <f>'Fluxo de pagamentos'!Z16</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="29">
+        <f>'Fluxo de pagamentos'!AA16</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="29">
+        <f>'Fluxo de pagamentos'!AB16</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="29">
+        <f>'Fluxo de pagamentos'!AC16</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="29">
+        <f>'Fluxo de pagamentos'!AD16</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="29">
+        <f>'Fluxo de pagamentos'!AE16</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="29">
+        <f>'Fluxo de pagamentos'!AF16</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="30">
+        <f>SUM(C12:V12)</f>
+        <v>1965903.1999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="29">
+        <f>'Fluxo de pagamentos'!M17</f>
+        <v>36658.33</v>
+      </c>
+      <c r="D13" s="29">
+        <f>'Fluxo de pagamentos'!N17</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="29">
+        <f>'Fluxo de pagamentos'!O17</f>
+        <v>36658.33</v>
+      </c>
+      <c r="F13" s="29">
+        <f>'Fluxo de pagamentos'!P17</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="29">
+        <f>'Fluxo de pagamentos'!Q17</f>
+        <v>36658.33</v>
+      </c>
+      <c r="H13" s="29">
+        <f>'Fluxo de pagamentos'!R17</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="29">
+        <f>'Fluxo de pagamentos'!S17</f>
+        <v>36658.33</v>
+      </c>
+      <c r="J13" s="29">
+        <f>'Fluxo de pagamentos'!T17</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="29">
+        <f>'Fluxo de pagamentos'!U17</f>
+        <v>116658.33</v>
+      </c>
+      <c r="L13" s="29">
+        <f>'Fluxo de pagamentos'!V17</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="29">
+        <f>'Fluxo de pagamentos'!W17</f>
+        <v>116658.33</v>
+      </c>
+      <c r="N13" s="29">
+        <f>'Fluxo de pagamentos'!X17</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="29">
+        <f>'Fluxo de pagamentos'!Y17</f>
+        <v>116658.37</v>
+      </c>
+      <c r="P13" s="29">
+        <f>'Fluxo de pagamentos'!Z17</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="29">
+        <f>'Fluxo de pagamentos'!AA17</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="29">
+        <f>'Fluxo de pagamentos'!AB17</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="29">
+        <f>'Fluxo de pagamentos'!AC17</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="29">
+        <f>'Fluxo de pagamentos'!AD17</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="29">
+        <f>'Fluxo de pagamentos'!AE17</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="29">
+        <f>'Fluxo de pagamentos'!AF17</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="30">
+        <f>SUM(C13:V13)</f>
+        <v>496608.35000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="29">
+        <f>'Fluxo de pagamentos'!M18</f>
+        <v>57647.1</v>
+      </c>
+      <c r="D14" s="29">
+        <f>'Fluxo de pagamentos'!N18</f>
+        <v>57647.1</v>
+      </c>
+      <c r="E14" s="29">
+        <f>'Fluxo de pagamentos'!O18</f>
+        <v>57647.1</v>
+      </c>
+      <c r="F14" s="29">
+        <f>'Fluxo de pagamentos'!P18</f>
+        <v>57647.1</v>
+      </c>
+      <c r="G14" s="29">
+        <f>'Fluxo de pagamentos'!Q18</f>
+        <v>57647.1</v>
+      </c>
+      <c r="H14" s="29">
+        <f>'Fluxo de pagamentos'!R18</f>
+        <v>57647.1</v>
+      </c>
+      <c r="I14" s="29">
+        <f>'Fluxo de pagamentos'!S18</f>
+        <v>57647.1</v>
+      </c>
+      <c r="J14" s="29">
+        <f>'Fluxo de pagamentos'!T18</f>
+        <v>57647.1</v>
+      </c>
+      <c r="K14" s="29">
+        <f>'Fluxo de pagamentos'!U18</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="29">
+        <f>'Fluxo de pagamentos'!V18</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="29">
+        <f>'Fluxo de pagamentos'!W18</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
+        <f>'Fluxo de pagamentos'!X18</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="29">
+        <f>'Fluxo de pagamentos'!Y18</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="29">
+        <f>'Fluxo de pagamentos'!Z18</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="29">
+        <f>'Fluxo de pagamentos'!AA18</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="29">
+        <f>'Fluxo de pagamentos'!AB18</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="29">
+        <f>'Fluxo de pagamentos'!AC18</f>
+        <v>0</v>
+      </c>
+      <c r="T14" s="29">
+        <f>'Fluxo de pagamentos'!AD18</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="29">
+        <f>'Fluxo de pagamentos'!AE18</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="29">
+        <f>'Fluxo de pagamentos'!AF18</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="30">
+        <f>SUM(C14:V14)</f>
+        <v>461176.79999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A15" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="47"/>
+      <c r="C15" s="29">
+        <f>C5+SUM(C7:C11)+C13</f>
+        <v>116960.02</v>
+      </c>
+      <c r="D15" s="29">
+        <f>D5+SUM(D7:D11)+D13</f>
+        <v>196968.35</v>
+      </c>
+      <c r="E15" s="29">
+        <f>E5+SUM(E7:E11)+E13</f>
+        <v>116960.02</v>
+      </c>
+      <c r="F15" s="29">
+        <f>F5+SUM(F7:F11)+F13</f>
+        <v>196968.35</v>
+      </c>
+      <c r="G15" s="29">
+        <f>G5+SUM(G7:G11)+G13</f>
+        <v>116960.02</v>
+      </c>
+      <c r="H15" s="29">
+        <f>H5+SUM(H7:H11)+H13</f>
+        <v>196968.35</v>
+      </c>
+      <c r="I15" s="29">
+        <f>I5+SUM(I7:I11)+I13</f>
+        <v>116960.02</v>
+      </c>
+      <c r="J15" s="29">
+        <f>J5+SUM(J7:J11)+J13</f>
+        <v>196968.35</v>
+      </c>
+      <c r="K15" s="29">
+        <f>K5+SUM(K7:K11)+K13</f>
+        <v>196960.02000000002</v>
+      </c>
+      <c r="L15" s="29">
+        <f>L5+SUM(L7:L11)+L13</f>
+        <v>196968.35</v>
+      </c>
+      <c r="M15" s="29">
+        <f>M5+SUM(M7:M11)+M13</f>
+        <v>196960.02000000002</v>
+      </c>
+      <c r="N15" s="29">
+        <f>N5+SUM(N7:N11)+N13</f>
+        <v>196968.35</v>
+      </c>
+      <c r="O15" s="29">
+        <f>O5+SUM(O7:O11)+O13</f>
+        <v>196960.06</v>
+      </c>
+      <c r="P15" s="29">
+        <f>P5+SUM(P7:P11)+P13</f>
+        <v>196968.43</v>
+      </c>
+      <c r="Q15" s="29">
+        <f>Q5+SUM(Q7:Q11)+Q13</f>
+        <v>80301.69</v>
+      </c>
+      <c r="R15" s="29">
+        <f>R5+SUM(R7:R11)+R13</f>
+        <v>80301.69</v>
+      </c>
+      <c r="S15" s="29">
+        <f>S5+SUM(S7:S11)+S13</f>
+        <v>80301.69</v>
+      </c>
+      <c r="T15" s="29">
+        <f>T5+SUM(T7:T11)+T13</f>
+        <v>80301.69</v>
+      </c>
+      <c r="U15" s="29">
+        <f>U5+SUM(U7:U11)+U13</f>
+        <v>80301.69</v>
+      </c>
+      <c r="V15" s="29">
+        <f>V5+SUM(V7:V11)+V13</f>
+        <v>80301.69</v>
+      </c>
+      <c r="W15" s="30">
+        <f>SUM(C15:V15)</f>
+        <v>2919308.85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A16" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="30">
+        <f>C6+C12+C14</f>
+        <v>655055.06999999995</v>
+      </c>
+      <c r="D16" s="30">
+        <f>D6+D12+D14</f>
+        <v>655055.06999999995</v>
+      </c>
+      <c r="E16" s="30">
+        <f>E6+E12+E14</f>
+        <v>655055.06999999995</v>
+      </c>
+      <c r="F16" s="30">
+        <f>F6+F12+F14</f>
+        <v>343144.75999999995</v>
+      </c>
+      <c r="G16" s="30">
+        <f>G6+G12+G14</f>
+        <v>343169.25999999995</v>
+      </c>
+      <c r="H16" s="30">
+        <f>H6+H12+H14</f>
+        <v>340843.17</v>
+      </c>
+      <c r="I16" s="30">
+        <f>I6+I12+I14</f>
+        <v>326672.33999999997</v>
+      </c>
+      <c r="J16" s="30">
+        <f>J6+J12+J14</f>
+        <v>325063.06999999995</v>
+      </c>
+      <c r="K16" s="30">
+        <f>K6+K12+K14</f>
+        <v>7524.68</v>
+      </c>
+      <c r="L16" s="30">
+        <f>L6+L12+L14</f>
+        <v>7524.68</v>
+      </c>
+      <c r="M16" s="30">
+        <f>M6+M12+M14</f>
+        <v>7524.68</v>
+      </c>
+      <c r="N16" s="30">
+        <f>N6+N12+N14</f>
+        <v>7524.68</v>
+      </c>
+      <c r="O16" s="30">
+        <f>O6+O12+O14</f>
+        <v>4841.8999999999996</v>
+      </c>
+      <c r="P16" s="30">
+        <f>P6+P12+P14</f>
+        <v>4841.8999999999996</v>
+      </c>
+      <c r="Q16" s="30">
+        <f>Q6+Q12+Q14</f>
+        <v>4841.8999999999996</v>
+      </c>
+      <c r="R16" s="30">
+        <f>R6+R12+R14</f>
+        <v>4841.8999999999996</v>
+      </c>
+      <c r="S16" s="30">
+        <f>S6+S12+S14</f>
+        <v>2367.79</v>
+      </c>
+      <c r="T16" s="30">
+        <f>T6+T12+T14</f>
+        <v>0</v>
+      </c>
+      <c r="U16" s="30">
+        <f>U6+U12+U14</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="30">
+        <f>V6+V12+V14</f>
+        <v>0</v>
+      </c>
+      <c r="W16" s="30">
+        <f>SUM(C16:V16)</f>
+        <v>3695891.9199999995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A17" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="48"/>
+      <c r="C17" s="30">
+        <f>C4*64.7%</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="D17" s="30">
+        <f>D4*64.7%</f>
+        <v>551259.15273999993</v>
+      </c>
+      <c r="E17" s="30">
+        <f>E4*64.7%</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="F17" s="30">
+        <f>F4*64.7%</f>
+        <v>349453.18216999999</v>
+      </c>
+      <c r="G17" s="30">
+        <f>G4*64.7%</f>
+        <v>297703.64415999997</v>
+      </c>
+      <c r="H17" s="30">
+        <f>H4*64.7%</f>
+        <v>347964.05344000005</v>
+      </c>
+      <c r="I17" s="30">
+        <f>I4*64.7%</f>
+        <v>287030.13692000002</v>
+      </c>
+      <c r="J17" s="30">
+        <f>J4*64.7%</f>
+        <v>337754.32874000003</v>
+      </c>
+      <c r="K17" s="30">
+        <f>K4*64.7%</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="L17" s="30">
+        <f>L4*64.7%</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="M17" s="30">
+        <f>M4*64.7%</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="N17" s="30">
+        <f>N4*64.7%</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="O17" s="30">
+        <f>O4*64.7%</f>
+        <v>130565.86812</v>
+      </c>
+      <c r="P17" s="30">
+        <f>P4*64.7%</f>
+        <v>130571.28350999999</v>
+      </c>
+      <c r="Q17" s="30">
+        <f>Q4*64.7%</f>
+        <v>55087.902730000002</v>
+      </c>
+      <c r="R17" s="30">
+        <f>R4*64.7%</f>
+        <v>55087.902730000002</v>
+      </c>
+      <c r="S17" s="30">
+        <f>S4*64.7%</f>
+        <v>53487.153560000006</v>
+      </c>
+      <c r="T17" s="30">
+        <f>T4*64.7%</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="U17" s="30">
+        <f>U4*64.7%</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="V17" s="30">
+        <f>V4*64.7%</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="W17" s="30">
+        <f>SUM(C17:V17)</f>
+        <v>4280034.8981900001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A18" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="48"/>
+      <c r="C18" s="30">
+        <f>C4*35.3%</f>
+        <v>272521.32676999999</v>
+      </c>
+      <c r="D18" s="30">
+        <f>D4*35.3%</f>
+        <v>300764.26725999994</v>
+      </c>
+      <c r="E18" s="30">
+        <f>E4*35.3%</f>
+        <v>272521.32676999999</v>
+      </c>
+      <c r="F18" s="30">
+        <f>F4*35.3%</f>
+        <v>190659.92782999997</v>
+      </c>
+      <c r="G18" s="30">
+        <f>G4*35.3%</f>
+        <v>162425.63583999997</v>
+      </c>
+      <c r="H18" s="30">
+        <f>H4*35.3%</f>
+        <v>189847.46656</v>
+      </c>
+      <c r="I18" s="30">
+        <f>I4*35.3%</f>
+        <v>156602.22308</v>
+      </c>
+      <c r="J18" s="30">
+        <f>J4*35.3%</f>
+        <v>184277.09125999999</v>
+      </c>
+      <c r="K18" s="30">
+        <f>K4*35.3%</f>
+        <v>72183.099100000007</v>
+      </c>
+      <c r="L18" s="30">
+        <f>L4*35.3%</f>
+        <v>72186.03959</v>
+      </c>
+      <c r="M18" s="30">
+        <f>M4*35.3%</f>
+        <v>72183.099100000007</v>
+      </c>
+      <c r="N18" s="30">
+        <f>N4*35.3%</f>
+        <v>72186.03959</v>
+      </c>
+      <c r="O18" s="30">
+        <f>O4*35.3%</f>
+        <v>71236.091879999993</v>
+      </c>
+      <c r="P18" s="30">
+        <f>P4*35.3%</f>
+        <v>71239.046489999993</v>
+      </c>
+      <c r="Q18" s="30">
+        <f>Q4*35.3%</f>
+        <v>30055.687269999999</v>
+      </c>
+      <c r="R18" s="30">
+        <f>R4*35.3%</f>
+        <v>30055.687269999999</v>
+      </c>
+      <c r="S18" s="30">
+        <f>S4*35.3%</f>
+        <v>29182.326440000001</v>
+      </c>
+      <c r="T18" s="30">
+        <f>T4*35.3%</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="U18" s="30">
+        <f>U4*35.3%</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="V18" s="30">
+        <f>V4*35.3%</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="W18" s="30">
+        <f>SUM(C18:V18)</f>
+        <v>2335165.8718099995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" s="33" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="49"/>
+      <c r="C19" s="41">
+        <f>C18-C15</f>
+        <v>155561.30676999997</v>
+      </c>
+      <c r="D19" s="41">
+        <f t="shared" ref="D19:V19" si="0">D18-D15</f>
+        <v>103795.91725999993</v>
+      </c>
+      <c r="E19" s="41">
+        <f t="shared" si="0"/>
+        <v>155561.30676999997</v>
+      </c>
+      <c r="F19" s="41">
+        <f t="shared" si="0"/>
+        <v>-6308.4221700000344</v>
+      </c>
+      <c r="G19" s="41">
+        <f t="shared" si="0"/>
+        <v>45465.615839999969</v>
+      </c>
+      <c r="H19" s="41">
+        <f t="shared" si="0"/>
+        <v>-7120.8834400000051</v>
+      </c>
+      <c r="I19" s="41">
+        <f t="shared" si="0"/>
+        <v>39642.203079999992</v>
+      </c>
+      <c r="J19" s="41">
+        <f t="shared" si="0"/>
+        <v>-12691.258740000019</v>
+      </c>
+      <c r="K19" s="41">
+        <f t="shared" si="0"/>
+        <v>-124776.92090000001</v>
+      </c>
+      <c r="L19" s="41">
+        <f t="shared" si="0"/>
+        <v>-124782.31041000001</v>
+      </c>
+      <c r="M19" s="41">
+        <f t="shared" si="0"/>
+        <v>-124776.92090000001</v>
+      </c>
+      <c r="N19" s="41">
+        <f t="shared" si="0"/>
+        <v>-124782.31041000001</v>
+      </c>
+      <c r="O19" s="41">
+        <f t="shared" si="0"/>
+        <v>-125723.96812000001</v>
+      </c>
+      <c r="P19" s="41">
+        <f t="shared" si="0"/>
+        <v>-125729.38351</v>
+      </c>
+      <c r="Q19" s="41">
+        <f t="shared" si="0"/>
+        <v>-50246.002730000007</v>
+      </c>
+      <c r="R19" s="41">
+        <f t="shared" si="0"/>
+        <v>-50246.002730000007</v>
+      </c>
+      <c r="S19" s="41">
+        <f t="shared" si="0"/>
+        <v>-51119.363559999998</v>
+      </c>
+      <c r="T19" s="41">
+        <f t="shared" si="0"/>
+        <v>-51955.193429999999</v>
+      </c>
+      <c r="U19" s="41">
+        <f t="shared" si="0"/>
+        <v>-51955.193429999999</v>
+      </c>
+      <c r="V19" s="41">
+        <f t="shared" si="0"/>
+        <v>-51955.193429999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A2:B3"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 

--- a/Anexo Fluxo de Pagamento Nio x Onitel.xlsx
+++ b/Anexo Fluxo de Pagamento Nio x Onitel.xlsx
@@ -8,14 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/silvio/Library/CloudStorage/GoogleDrive-eucastrosilvio@gmail.com/Meu Drive/1A Grupo Tigon Drive/Grupo Tigon Estratégico/Vtal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C7D73B-1E83-1E4E-B4BE-9D9F60D80936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D28D786-65CD-4A4E-9BEA-D6DD5A88C735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-140" yWindow="580" windowWidth="29040" windowHeight="15120" activeTab="2" xr2:uid="{64F40452-A3D8-4C49-BFF5-9F85CDF9315C}"/>
+    <workbookView xWindow="1760" yWindow="580" windowWidth="23840" windowHeight="15120" activeTab="2" xr2:uid="{64F40452-A3D8-4C49-BFF5-9F85CDF9315C}"/>
   </bookViews>
   <sheets>
     <sheet name="Fluxo de pagamentos" sheetId="5" r:id="rId1"/>
     <sheet name="Resumo Fluxo de Pagamentos" sheetId="6" r:id="rId2"/>
-    <sheet name="Escrow" sheetId="7" r:id="rId3"/>
+    <sheet name="Escrow e IT Serviços" sheetId="7" r:id="rId3"/>
+    <sheet name="Variação Monetária Telecom" sheetId="19" r:id="rId4"/>
+    <sheet name="Variação Monetária Serviços" sheetId="18" r:id="rId5"/>
+    <sheet name="Suporte Técnico N3 Serviços" sheetId="16" r:id="rId6"/>
+    <sheet name="FTTx Onitel Telecom" sheetId="17" r:id="rId7"/>
+    <sheet name="Setup Onitel Serviços" sheetId="15" r:id="rId8"/>
+    <sheet name="Imobilizado Onitel Telecom" sheetId="13" r:id="rId9"/>
+    <sheet name="Carteira Conta Or Onitel Serviç" sheetId="12" r:id="rId10"/>
+    <sheet name="Carteira Escrow Onitel Serviços" sheetId="22" r:id="rId11"/>
+    <sheet name="Carteira BB Onitel Serviços" sheetId="11" r:id="rId12"/>
+    <sheet name="Carteira Escrow Onitel Telecom " sheetId="20" r:id="rId13"/>
+    <sheet name="Carteira Conta e Ordem Telecom" sheetId="10" r:id="rId14"/>
+    <sheet name="Carteira BB Onitel Telecom" sheetId="8" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="187">
   <si>
     <t>Total</t>
   </si>
@@ -346,23 +358,309 @@
     <t>Valor  dos Recursos Parte Onitel Serviços: 35,3%</t>
   </si>
   <si>
-    <t>Saldo que a Onitel Telecom deverá repassar para a Onitel Seriços</t>
+    <t>Campo no Kamino</t>
+  </si>
+  <si>
+    <t>Informação</t>
+  </si>
+  <si>
+    <t>Entrada</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Conta Financeira</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Pagador/Cliente</t>
+  </si>
+  <si>
+    <t>Nio</t>
+  </si>
+  <si>
+    <t>Histórico</t>
+  </si>
+  <si>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>Contrato de Cessão, planilha do fluxo e comprovante do pagamento efetuado pela Nio</t>
+  </si>
+  <si>
+    <t>Código Contábil</t>
+  </si>
+  <si>
+    <t>Recebimento da Carteira Onitel Telecom  –  Valor pago pela Nio diretamente na Conta Banco do Brasil da  Telecom</t>
+  </si>
+  <si>
+    <t>Liquidação parcial do preço da Carteira de Clientes mediante pagamento na Conta BB Onitel Telecom</t>
+  </si>
+  <si>
+    <t>1.02.02.001 - Pagamentos por Conta e Ordem -  Nio</t>
+  </si>
+  <si>
+    <t>3.07.02 - Venda de Carteira de Clientes</t>
+  </si>
+  <si>
+    <t>Recebimento da Carteira Onitel Telecom  –  Valor pago pela Nio por Conta e Ordem à IT Investimentos / Lançamento 1</t>
+  </si>
+  <si>
+    <t>Liquidação parcial do preço da Carteira de Clientes mediante pagamento pela Nio por Conta e Ordem à IT Investimentos</t>
+  </si>
+  <si>
+    <t>Saída</t>
+  </si>
+  <si>
+    <t>Pagamento da Comissão à IT Investimentos – Valor pago pela Nio por Conta e Ordem à IT Investimentos /               Lançamento 2</t>
+  </si>
+  <si>
+    <t>4.03.01.027 - Despesas com Consultorias</t>
+  </si>
+  <si>
+    <t>Pagamento da NF da IT Investimentos efetuado pela Nio por conta e ordem da Onitel Telecom</t>
+  </si>
+  <si>
+    <t>NF emitida pela IT e comprovante do pagamento realizado pela Nio</t>
+  </si>
+  <si>
+    <t>1.01.02.003.002 Banco do Brasil - Onitel Serviços - Ag 4275-7	Cc47908-X</t>
+  </si>
+  <si>
+    <t>1.01.02.002.001 Banco do Brasil - Onitel Telecom -  Ag 3411-8 Cc 47907-1</t>
+  </si>
+  <si>
+    <t>Liquidação parcial do preço da Carteira de Clientes mediante pagamento na Conta BB Onitel Serviços</t>
+  </si>
+  <si>
+    <t>Onitel Serviços - Pagamento da Comissão à IT Investimentos – Valor pago pela Nio por Conta e Ordem à IT Investimentos / Lançamento 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recebimento da Carteira Onitel Serviços  –  Valor pago pela Nio por Conta e Ordem à IT Investimentos /                   Lançamento 1</t>
+  </si>
+  <si>
+    <t>Recebimento da Carteira Onitel Serviços  –  Valor pago pela Nio diretamente na Conta Banco do Brasil da  Serviços</t>
+  </si>
+  <si>
+    <t>Pagamento da NF da IT Investimentos efetuado pela Nio por conta e ordem da Onitel Serviços</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recebimento Venda Imobilizado Onitel Telecom  –  Valor pago pela Nio para Conta BB Onitel Telecom</t>
+  </si>
+  <si>
+    <t>3.06.02 - Receita de Venda de Imobilizado</t>
+  </si>
+  <si>
+    <t>Recebimento de Venda de Imobilizado conforme NF nº 353955 mediante pagamento pela Nio para BB Onitel Telecom</t>
+  </si>
+  <si>
+    <t>Contrato de Cessão, planilha do fluxo e comprovante do pagamento efetuado pela Nio e NF nº 353955</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recebimento Set-up/Migração FTTx Onitel Serviços  –  Valor pago pela Nio para Conta BB Onitel Serviços</t>
+  </si>
+  <si>
+    <t>3.03.01.005 — Receita Serviço Instalação/Desinstalação</t>
+  </si>
+  <si>
+    <t>Recebimento de Venda de Imobilizado conforme NFS-e
+ nº 11171 mediante pagamento pela Nio para BB Onitel Serviços</t>
+  </si>
+  <si>
+    <t>Contrato de Cessão, planilha do fluxo e comprovante do pagamento efetuado pela Nio e NF-e  nº 11171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03.01.006 — Receitas Aluguel de Portas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato de Cessão, planilha do fluxo e comprovante do pagamento efetuado pela Nio e NF nº </t>
+  </si>
+  <si>
+    <t>Recebimento Portas Iluminadas FTTX / Aluguel de Portas Mensal Onitel Telecom - conforme fluxo de pagamentos</t>
+  </si>
+  <si>
+    <t>Data Emissão NF</t>
+  </si>
+  <si>
+    <t>Data Recebimento</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>Prestação de Serviço de SCM por 12 meses com emissão de NF de Telecomunicações</t>
+  </si>
+  <si>
+    <t>3.03.03.001 — Receita Suporte Técnico N3</t>
+  </si>
+  <si>
+    <t>Prestação mensal de serviços a emitir NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prestação mensal de serviços a emitir NF		</t>
+  </si>
+  <si>
+    <t>Previsão de Faturamento Mensal sem Glosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recebimento Suporte Técnico N3 Onitel Serviços  –  Valor a Pagar pela Nio para Conta BB Onitel Serviços -  12 Parcelas Mensais</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recebimento Portas Iluminadas FTTX / Aluguel de Portas Onitel Telecom  –  Valor a pagar pela Nio para Conta BB Onitel Telecom - 12 Parcelas Mensais</t>
+  </si>
+  <si>
+    <t>Conforme fluxo de pagamento mensal - observar se haverá Glosa</t>
+  </si>
+  <si>
+    <t>Contrato de Cessão, planilha do fluxo e comprovante do pagamento efetuado pela Nio e NF</t>
+  </si>
+  <si>
+    <t>Recebimento Serviço Suporte Técnico N3 - conforme fluxo de pagamentos</t>
+  </si>
+  <si>
+    <t>Conforme Tabela de Fluxo de Pagamentos</t>
+  </si>
+  <si>
+    <t>3.05.05 - Receita - Variações Monetárias Ativas</t>
+  </si>
+  <si>
+    <t>Deverá ser calculado no mês do pagamento conforme contrato - IPCA + 5%aa sobre saldo devedor</t>
+  </si>
+  <si>
+    <t>Recebimento de Receita - Variações Monetárias Ativas  Onitel Serviços - Nio</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>* Observação</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Na data de Recebimento dos valores conforme o fluxo de pagamentos abaixo, deverá ser calculado atualização monetária sobre o saldo devedor de todos as Rubricas. O valor deverá ser lançado segregado do valor de qualquer das Rubricas, mesmo que a Nio faça o pagamento em uma única transferência. Deverá ser lançado como Receita de Variação Monetária</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01.02.002.001 Banco do Brasil - Onitel Telecom -  Ag 3411-8 Cc 47907-1		</t>
+  </si>
+  <si>
+    <t>Onitel Serviços Recebimento Receita - Variações Monetárias Ativas –  Valor pago pela Nio para Conta BB Onitel Serviços</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* Observação: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Repetir esses lançamentos mensalmente, nas datas e valores conforme tabela abaixo:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Data </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recebimento Carteira de Cliente Onitel Telecom - Depósitos da Nio na Conta Escrow  - 20  Parcelas Mensais com Valores Variáveis Conforme Tabela  Abaixo.</t>
+  </si>
+  <si>
+    <t>1.01.02.002.009 - Conta Escrow Onitel Telecom</t>
+  </si>
+  <si>
+    <t>Liquidação parcial do preço da Carteira de Clientes mediante pagamento pela Nio por Conta e Ordem à Conta Escrow</t>
+  </si>
+  <si>
+    <t>Contrato de Cessão, planilha do fluxo e comprovante de transferência efetuado pela Nio na Conta Escrow</t>
+  </si>
+  <si>
+    <t>Repetir os lançamentos conforme as transferências para a Conta Escrow previstas para as datas e valores na tabela abaixo</t>
+  </si>
+  <si>
+    <t>Conforme Tabela abaixo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme Tabela abaixo	</t>
+  </si>
+  <si>
+    <t>Conforme tabela abaixo</t>
+  </si>
+  <si>
+    <t>Liquidação parcial do preço da Carteira de Clientes mediante pagamento pelaOnitel Telecom referente a Valores que a Nio depositou na  Conta Escrow Onitel Telecom</t>
+  </si>
+  <si>
+    <t>Contrato de Cessão, planilha do fluxo e comprovante de transferência efetuado pela Onitel Telecom</t>
+  </si>
+  <si>
+    <t>Repetir os lançamentos conforme as transferências previstas para as datas e valores na tabela abaixo</t>
+  </si>
+  <si>
+    <t>Tabela de Data e Valores - Pagamento a Credores Onitel Serviços</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recebimento Carteira de Cliente Onitel Serviços - Valores que a Nio depositou na  Conta Escrow Onitel Telecom /Parte Onitel Serviços - 20  Parcelas Mensais com Valores Variáveis Conforme Tabela  Abaixo.</t>
+  </si>
+  <si>
+    <t>Soma dos Valores Carteira de Clientes -  Parte Onitel Serviços</t>
+  </si>
+  <si>
+    <t>Telecom</t>
+  </si>
+  <si>
+    <t>Serviços</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Investimentos </t>
+  </si>
+  <si>
+    <t>Soma Valores Connectx</t>
+  </si>
+  <si>
+    <t>Tabela de Data e Valores - Pagamento a Credores Onitel Telecom - Conta Escrow</t>
+  </si>
+  <si>
+    <t>Tabela de Datas e Valores Recebidos - Carteira de Clientes -  Onitel Telecom na Conta Escrow Onitel Telecom</t>
+  </si>
+  <si>
+    <t>Tabela de Datas e Valores Recebidos - Carteira de Clientes -  Onitel Serviços na Conta Escrow Onitel Telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabela de Valores Recebidos  - Carteira de Clientes  à IT Investimentos </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Onitel Telecom Recebimento Receita - Variações Monetárias Ativas –  Valor pago pela Nio para Conta BB Onitel Telecom</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0_);\(#,##0\);&quot;-&quot;_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0_)%;\(#,##0.0%\);&quot;-&quot;\%_)"/>
     <numFmt numFmtId="166" formatCode="#,##0.000000000000_);\(#,##0.000000000000\);&quot;-&quot;_)"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="0.000%"/>
+    <numFmt numFmtId="169" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,6 +721,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -450,7 +783,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -506,6 +839,85 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -514,7 +926,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -591,7 +1003,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -600,8 +1012,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -610,10 +1028,169 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6598,12 +7175,1496 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C597DB66-A48C-A849-9E26-78748DF260AC}">
+  <dimension ref="A2:C29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" customWidth="1"/>
+    <col min="3" max="3" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+    </row>
+    <row r="3" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="66"/>
+    </row>
+    <row r="4" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="69"/>
+    </row>
+    <row r="5" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="70">
+        <v>46230</v>
+      </c>
+      <c r="C5" s="72"/>
+    </row>
+    <row r="6" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="69"/>
+    </row>
+    <row r="7" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="69"/>
+    </row>
+    <row r="8" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="67">
+        <v>141</v>
+      </c>
+      <c r="C8" s="69"/>
+    </row>
+    <row r="9" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="82">
+        <v>1059000</v>
+      </c>
+      <c r="C9" s="84"/>
+    </row>
+    <row r="10" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="69"/>
+    </row>
+    <row r="11" spans="1:3" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="69"/>
+    </row>
+    <row r="12" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="69"/>
+    </row>
+    <row r="14" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+    </row>
+    <row r="15" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="66"/>
+    </row>
+    <row r="16" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="69"/>
+    </row>
+    <row r="17" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="70">
+        <v>46240</v>
+      </c>
+      <c r="C17" s="72"/>
+    </row>
+    <row r="18" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="69"/>
+    </row>
+    <row r="19" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="69"/>
+    </row>
+    <row r="20" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="67">
+        <v>1431</v>
+      </c>
+      <c r="C20" s="69"/>
+    </row>
+    <row r="21" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="82">
+        <v>1059000</v>
+      </c>
+      <c r="C21" s="84"/>
+    </row>
+    <row r="22" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="69"/>
+    </row>
+    <row r="23" spans="1:3" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="69"/>
+    </row>
+    <row r="24" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="69"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="94" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="95"/>
+      <c r="C25" s="96"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="89" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26" s="90" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="91"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="75">
+        <v>46965</v>
+      </c>
+      <c r="B27" s="40">
+        <v>230509</v>
+      </c>
+      <c r="C27" s="92"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="75">
+        <v>47330</v>
+      </c>
+      <c r="B28" s="40">
+        <v>230509</v>
+      </c>
+      <c r="C28" s="92"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="75">
+        <v>47695</v>
+      </c>
+      <c r="B29" s="40">
+        <v>230509</v>
+      </c>
+      <c r="C29" s="92"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B7:C7"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58742BAA-5F5B-0348-B8E2-5A205844A13E}">
+  <dimension ref="A2:G36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" customWidth="1"/>
+    <col min="3" max="3" width="57.5" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="91.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" ht="47" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+    </row>
+    <row r="3" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="66"/>
+    </row>
+    <row r="4" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="69"/>
+    </row>
+    <row r="5" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="70" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="72"/>
+    </row>
+    <row r="6" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="69"/>
+    </row>
+    <row r="7" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="69"/>
+    </row>
+    <row r="8" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="67">
+        <v>141</v>
+      </c>
+      <c r="C8" s="69"/>
+    </row>
+    <row r="9" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="84"/>
+    </row>
+    <row r="10" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="69"/>
+    </row>
+    <row r="11" spans="1:7" s="33" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="69"/>
+    </row>
+    <row r="12" spans="1:7" s="33" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="69"/>
+    </row>
+    <row r="13" spans="1:7" s="33" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="78"/>
+    </row>
+    <row r="14" spans="1:7" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="98" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="98"/>
+      <c r="C14" s="105"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="106"/>
+    </row>
+    <row r="16" spans="1:7" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="81">
+        <v>46295</v>
+      </c>
+      <c r="B16" s="79">
+        <f>'Escrow e IT Serviços'!C18</f>
+        <v>272521.32676999999</v>
+      </c>
+      <c r="C16" s="106"/>
+    </row>
+    <row r="17" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="81">
+        <v>46326</v>
+      </c>
+      <c r="B17" s="79">
+        <f>'Escrow e IT Serviços'!D18</f>
+        <v>300764.26725999994</v>
+      </c>
+      <c r="C17" s="106"/>
+    </row>
+    <row r="18" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="81">
+        <v>46356</v>
+      </c>
+      <c r="B18" s="79">
+        <f>'Escrow e IT Serviços'!E18</f>
+        <v>272521.32676999999</v>
+      </c>
+      <c r="C18" s="106"/>
+    </row>
+    <row r="19" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="81">
+        <v>46387</v>
+      </c>
+      <c r="B19" s="79">
+        <f>'Escrow e IT Serviços'!F18</f>
+        <v>190659.92782999997</v>
+      </c>
+      <c r="C19" s="106"/>
+    </row>
+    <row r="20" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="81">
+        <v>46418</v>
+      </c>
+      <c r="B20" s="79">
+        <f>'Escrow e IT Serviços'!G18</f>
+        <v>162425.63583999997</v>
+      </c>
+      <c r="C20" s="106"/>
+    </row>
+    <row r="21" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="81">
+        <v>46446</v>
+      </c>
+      <c r="B21" s="79">
+        <f>'Escrow e IT Serviços'!H18</f>
+        <v>189847.46656</v>
+      </c>
+      <c r="C21" s="106"/>
+    </row>
+    <row r="22" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="81">
+        <v>46477</v>
+      </c>
+      <c r="B22" s="79">
+        <f>'Escrow e IT Serviços'!I18</f>
+        <v>156602.22308</v>
+      </c>
+      <c r="C22" s="106"/>
+    </row>
+    <row r="23" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="81">
+        <v>46507</v>
+      </c>
+      <c r="B23" s="79">
+        <f>'Escrow e IT Serviços'!J18</f>
+        <v>184277.09125999999</v>
+      </c>
+      <c r="C23" s="106"/>
+    </row>
+    <row r="24" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="81">
+        <v>46538</v>
+      </c>
+      <c r="B24" s="79">
+        <f>'Escrow e IT Serviços'!K18</f>
+        <v>72183.099100000007</v>
+      </c>
+      <c r="C24" s="106"/>
+    </row>
+    <row r="25" spans="1:3" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="81">
+        <v>46568</v>
+      </c>
+      <c r="B25" s="79">
+        <f>'Escrow e IT Serviços'!L18</f>
+        <v>72186.03959</v>
+      </c>
+      <c r="C25" s="106"/>
+    </row>
+    <row r="26" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="81">
+        <v>46599</v>
+      </c>
+      <c r="B26" s="79">
+        <f>'Escrow e IT Serviços'!M18</f>
+        <v>72183.099100000007</v>
+      </c>
+      <c r="C26" s="106"/>
+    </row>
+    <row r="27" spans="1:3" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="81">
+        <v>46630</v>
+      </c>
+      <c r="B27" s="79">
+        <f>'Escrow e IT Serviços'!N18</f>
+        <v>72186.03959</v>
+      </c>
+      <c r="C27" s="106"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="81">
+        <v>46660</v>
+      </c>
+      <c r="B28" s="79">
+        <f>'Escrow e IT Serviços'!O18</f>
+        <v>71236.091879999993</v>
+      </c>
+      <c r="C28" s="106"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="81">
+        <v>46691</v>
+      </c>
+      <c r="B29" s="79">
+        <f>'Escrow e IT Serviços'!P18</f>
+        <v>71239.046489999993</v>
+      </c>
+      <c r="C29" s="106"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="81">
+        <v>46721</v>
+      </c>
+      <c r="B30" s="79">
+        <f>'Escrow e IT Serviços'!Q18</f>
+        <v>30055.687269999999</v>
+      </c>
+      <c r="C30" s="106"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="81">
+        <v>46752</v>
+      </c>
+      <c r="B31" s="79">
+        <f>'Escrow e IT Serviços'!R18</f>
+        <v>30055.687269999999</v>
+      </c>
+      <c r="C31" s="106"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="81">
+        <v>46783</v>
+      </c>
+      <c r="B32" s="79">
+        <f>'Escrow e IT Serviços'!S18</f>
+        <v>29182.326440000001</v>
+      </c>
+      <c r="C32" s="106"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="81">
+        <v>46812</v>
+      </c>
+      <c r="B33" s="79">
+        <f>'Escrow e IT Serviços'!T18</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="C33" s="106"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="81">
+        <v>46843</v>
+      </c>
+      <c r="B34" s="79">
+        <f>'Escrow e IT Serviços'!U18</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="C34" s="106"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="81">
+        <v>46873</v>
+      </c>
+      <c r="B35" s="79">
+        <f>'Escrow e IT Serviços'!V18</f>
+        <v>28346.496569999999</v>
+      </c>
+      <c r="C35" s="106"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="97">
+        <f>SUM(B16:B35)</f>
+        <v>2335165.8718099995</v>
+      </c>
+      <c r="C36" s="106"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:C36"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA901DFA-CA6F-9747-B7B3-00C050365193}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="59"/>
+    </row>
+    <row r="2" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="54">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="56">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="55">
+        <v>4562745.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D5EEE07-E1C1-944D-850C-E5FDC004171F}">
+  <dimension ref="A2:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" customWidth="1"/>
+    <col min="3" max="3" width="57.5" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+    </row>
+    <row r="3" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="66"/>
+    </row>
+    <row r="4" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="69"/>
+    </row>
+    <row r="5" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="70" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="72"/>
+    </row>
+    <row r="6" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="69"/>
+    </row>
+    <row r="7" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="69"/>
+    </row>
+    <row r="8" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="67">
+        <v>141</v>
+      </c>
+      <c r="C8" s="69"/>
+    </row>
+    <row r="9" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="84"/>
+    </row>
+    <row r="10" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="69"/>
+    </row>
+    <row r="11" spans="1:3" s="33" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="69"/>
+    </row>
+    <row r="12" spans="1:3" s="33" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="69"/>
+    </row>
+    <row r="13" spans="1:3" s="33" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="78"/>
+    </row>
+    <row r="14" spans="1:3" s="33" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="98" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" s="98"/>
+      <c r="C14" s="61"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="62"/>
+    </row>
+    <row r="16" spans="1:3" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="81">
+        <v>46295</v>
+      </c>
+      <c r="B16" s="79">
+        <f>'Escrow e IT Serviços'!C17</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="C16" s="80"/>
+    </row>
+    <row r="17" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="81">
+        <v>46326</v>
+      </c>
+      <c r="B17" s="79">
+        <f>'Escrow e IT Serviços'!D17</f>
+        <v>551259.15273999993</v>
+      </c>
+      <c r="C17" s="80"/>
+    </row>
+    <row r="18" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="81">
+        <v>46356</v>
+      </c>
+      <c r="B18" s="79">
+        <f>'Escrow e IT Serviços'!E17</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="C18" s="80"/>
+    </row>
+    <row r="19" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="81">
+        <v>46387</v>
+      </c>
+      <c r="B19" s="79">
+        <f>'Escrow e IT Serviços'!F17</f>
+        <v>349453.18216999999</v>
+      </c>
+      <c r="C19" s="80"/>
+    </row>
+    <row r="20" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="81">
+        <v>46418</v>
+      </c>
+      <c r="B20" s="79">
+        <f>'Escrow e IT Serviços'!G17</f>
+        <v>297703.64415999997</v>
+      </c>
+      <c r="C20" s="80"/>
+    </row>
+    <row r="21" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="81">
+        <v>46446</v>
+      </c>
+      <c r="B21" s="79">
+        <f>'Escrow e IT Serviços'!H17</f>
+        <v>347964.05344000005</v>
+      </c>
+      <c r="C21" s="80"/>
+    </row>
+    <row r="22" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="81">
+        <v>46477</v>
+      </c>
+      <c r="B22" s="79">
+        <f>'Escrow e IT Serviços'!I17</f>
+        <v>287030.13692000002</v>
+      </c>
+      <c r="C22" s="80"/>
+    </row>
+    <row r="23" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="81">
+        <v>46507</v>
+      </c>
+      <c r="B23" s="79">
+        <f>'Escrow e IT Serviços'!J17</f>
+        <v>337754.32874000003</v>
+      </c>
+      <c r="C23" s="80"/>
+    </row>
+    <row r="24" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="81">
+        <v>46538</v>
+      </c>
+      <c r="B24" s="79">
+        <f>'Escrow e IT Serviços'!K17</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="C24" s="80"/>
+    </row>
+    <row r="25" spans="1:3" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="81">
+        <v>46568</v>
+      </c>
+      <c r="B25" s="79">
+        <f>'Escrow e IT Serviços'!L17</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="C25" s="80"/>
+    </row>
+    <row r="26" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="81">
+        <v>46599</v>
+      </c>
+      <c r="B26" s="79">
+        <f>'Escrow e IT Serviços'!M17</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="C26" s="80"/>
+    </row>
+    <row r="27" spans="1:3" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="81">
+        <v>46630</v>
+      </c>
+      <c r="B27" s="79">
+        <f>'Escrow e IT Serviços'!N17</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="C27" s="80"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="81">
+        <v>46660</v>
+      </c>
+      <c r="B28" s="79">
+        <f>'Escrow e IT Serviços'!O17</f>
+        <v>130565.86812</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="81">
+        <v>46691</v>
+      </c>
+      <c r="B29" s="79">
+        <f>'Escrow e IT Serviços'!P17</f>
+        <v>130571.28350999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="81">
+        <v>46721</v>
+      </c>
+      <c r="B30" s="79">
+        <f>'Escrow e IT Serviços'!Q17</f>
+        <v>55087.902730000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="81">
+        <v>46752</v>
+      </c>
+      <c r="B31" s="79">
+        <f>'Escrow e IT Serviços'!R17</f>
+        <v>55087.902730000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="81">
+        <v>46783</v>
+      </c>
+      <c r="B32" s="79">
+        <f>'Escrow e IT Serviços'!S17</f>
+        <v>53487.153560000006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="81">
+        <v>46812</v>
+      </c>
+      <c r="B33" s="79">
+        <f>'Escrow e IT Serviços'!T17</f>
+        <v>51955.193430000007</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="81">
+        <v>46843</v>
+      </c>
+      <c r="B34" s="79">
+        <f>'Escrow e IT Serviços'!U17</f>
+        <v>51955.193430000007</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="81">
+        <v>46873</v>
+      </c>
+      <c r="B35" s="79">
+        <f>'Escrow e IT Serviços'!V17</f>
+        <v>51955.193430000007</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="97">
+        <f>SUM(B16:B35)</f>
+        <v>4280034.8981900001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406E3ADB-306E-094D-B889-19B5630806C9}">
+  <dimension ref="A2:C29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" customWidth="1"/>
+    <col min="3" max="3" width="61.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+    </row>
+    <row r="3" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="66"/>
+    </row>
+    <row r="4" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="69"/>
+    </row>
+    <row r="5" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="70">
+        <v>46230</v>
+      </c>
+      <c r="C5" s="72"/>
+    </row>
+    <row r="6" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="69"/>
+    </row>
+    <row r="7" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="69"/>
+    </row>
+    <row r="8" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="67">
+        <v>141</v>
+      </c>
+      <c r="C8" s="69"/>
+    </row>
+    <row r="9" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="82">
+        <v>1941000</v>
+      </c>
+      <c r="C9" s="84"/>
+    </row>
+    <row r="10" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="69"/>
+    </row>
+    <row r="11" spans="1:3" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="69"/>
+    </row>
+    <row r="12" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="69"/>
+    </row>
+    <row r="14" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+    </row>
+    <row r="15" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="66"/>
+    </row>
+    <row r="16" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="69"/>
+    </row>
+    <row r="17" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="70">
+        <v>46240</v>
+      </c>
+      <c r="C17" s="72"/>
+    </row>
+    <row r="18" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="69"/>
+    </row>
+    <row r="19" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="69"/>
+    </row>
+    <row r="20" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="67">
+        <v>1431</v>
+      </c>
+      <c r="C20" s="69"/>
+    </row>
+    <row r="21" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="82">
+        <v>1941000</v>
+      </c>
+      <c r="C21" s="84"/>
+    </row>
+    <row r="22" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="69"/>
+    </row>
+    <row r="23" spans="1:3" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="69"/>
+    </row>
+    <row r="24" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="69"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="94" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="95"/>
+      <c r="C25" s="96"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="89" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26" s="90" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="91"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="75">
+        <v>46965</v>
+      </c>
+      <c r="B27" s="40">
+        <v>422491</v>
+      </c>
+      <c r="C27" s="92"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="75">
+        <v>47330</v>
+      </c>
+      <c r="B28" s="40">
+        <v>422491</v>
+      </c>
+      <c r="C28" s="92"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="75">
+        <v>47695</v>
+      </c>
+      <c r="B29" s="40">
+        <v>422491</v>
+      </c>
+      <c r="C29" s="92"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B10:C10"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E55E88B-747D-9041-86CA-C549C5044782}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="59"/>
+    </row>
+    <row r="2" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="54">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="56">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="55">
+        <v>8362181.3700000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9126A784-1C98-9F45-AB74-8C05D98CDB5F}">
   <dimension ref="A1:CD51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -6620,8 +8681,7 @@
     <col min="41" max="41" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="42" max="52" width="11" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="55" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -8055,207 +10115,207 @@
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
       <c r="D8" s="40">
-        <f>SUM(D5:D7)</f>
+        <f t="shared" ref="D8:AI8" si="0">SUM(D5:D7)</f>
         <v>59042640.313019089</v>
       </c>
       <c r="E8" s="29">
-        <f>SUM(E5:E7)</f>
+        <f t="shared" si="0"/>
         <v>21432792.093905725</v>
       </c>
       <c r="F8" s="29">
-        <f>SUM(F5:F7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G8" s="29">
-        <f>SUM(G5:G7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H8" s="29">
-        <f>SUM(H5:H7)</f>
+        <f t="shared" si="0"/>
         <v>4577711.49</v>
       </c>
       <c r="I8" s="29">
-        <f>SUM(I5:I7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J8" s="29">
-        <f>SUM(J5:J7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K8" s="29">
-        <f>SUM(K5:K7)</f>
+        <f t="shared" si="0"/>
         <v>4426492.5199999996</v>
       </c>
       <c r="L8" s="29">
-        <f>SUM(L5:L7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M8" s="29">
-        <f>SUM(M5:M7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N8" s="29">
-        <f>SUM(N5:N7)</f>
+        <f t="shared" si="0"/>
         <v>4695274.7</v>
       </c>
       <c r="O8" s="29">
-        <f>SUM(O5:O7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P8" s="29">
-        <f>SUM(P5:P7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q8" s="29">
-        <f>SUM(Q5:Q7)</f>
+        <f t="shared" si="0"/>
         <v>5585287.5699999994</v>
       </c>
       <c r="R8" s="29">
-        <f>SUM(R5:R7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S8" s="29">
-        <f>SUM(S5:S7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T8" s="29">
-        <f>SUM(T5:T7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U8" s="29">
-        <f>SUM(U5:U7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V8" s="29">
-        <f>SUM(V5:V7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W8" s="29">
-        <f>SUM(W5:W7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X8" s="29">
-        <f>SUM(X5:X7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y8" s="29">
-        <f>SUM(Y5:Y7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z8" s="29">
-        <f>SUM(Z5:Z7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA8" s="29">
-        <f>SUM(AA5:AA7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB8" s="29">
-        <f>SUM(AB5:AB7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC8" s="29">
-        <f>SUM(AC5:AC7)</f>
+        <f t="shared" si="0"/>
         <v>18325081.939113364</v>
       </c>
       <c r="AD8" s="29">
-        <f>SUM(AD5:AD7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE8" s="29">
-        <f>SUM(AE5:AE7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF8" s="29">
-        <f>SUM(AF5:AF7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG8" s="29">
-        <f>SUM(AG5:AG7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH8" s="29">
-        <f>SUM(AH5:AH7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AI8" s="29">
-        <f>SUM(AI5:AI7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ8" s="29">
-        <f>SUM(AJ5:AJ7)</f>
+        <f t="shared" ref="AJ8:BO8" si="1">SUM(AJ5:AJ7)</f>
         <v>0</v>
       </c>
       <c r="AK8" s="29">
-        <f>SUM(AK5:AK7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AL8" s="29">
-        <f>SUM(AL5:AL7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AM8" s="29">
-        <f>SUM(AM5:AM7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AN8" s="29">
-        <f>SUM(AN5:AN7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AO8" s="29">
-        <f>SUM(AO5:AO7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AP8" s="29">
-        <f>SUM(AP5:AP7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AQ8" s="29">
-        <f>SUM(AQ5:AQ7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AR8" s="29">
-        <f>SUM(AR5:AR7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AS8" s="29">
-        <f>SUM(AS5:AS7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AT8" s="29">
-        <f>SUM(AT5:AT7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AU8" s="29">
-        <f>SUM(AU5:AU7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AV8" s="29">
-        <f>SUM(AV5:AV7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AW8" s="29">
-        <f>SUM(AW5:AW7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX8" s="29">
-        <f>SUM(AX5:AX7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AY8" s="29">
-        <f>SUM(AY5:AY7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AZ8" s="29">
-        <f>SUM(AZ5:AZ7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BA8" s="29">
-        <f>SUM(BA5:BA7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BB8" s="29">
-        <f>SUM(BB5:BB7)</f>
+        <f t="shared" si="1"/>
         <v>59042640.313019089</v>
       </c>
     </row>
@@ -8266,203 +10326,203 @@
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
       <c r="D9" s="40">
-        <f>SUM(D3:D7)</f>
+        <f t="shared" ref="D9:AI9" si="2">SUM(D3:D7)</f>
         <v>165300000</v>
       </c>
       <c r="E9" s="29">
-        <f>SUM(E3:E7)</f>
+        <f t="shared" si="2"/>
         <v>66119999.999999993</v>
       </c>
       <c r="F9" s="29">
-        <f>SUM(F3:F7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G9" s="29">
-        <f>SUM(G3:G7)</f>
+        <f t="shared" si="2"/>
         <v>772015.09</v>
       </c>
       <c r="H9" s="29">
-        <f>SUM(H3:H7)</f>
+        <f t="shared" si="2"/>
         <v>5429734.9100000001</v>
       </c>
       <c r="I9" s="29">
-        <f>SUM(I3:I7)</f>
+        <f t="shared" si="2"/>
         <v>772015.09</v>
       </c>
       <c r="J9" s="29">
-        <f>SUM(J3:J7)</f>
+        <f t="shared" si="2"/>
         <v>540113.11</v>
       </c>
       <c r="K9" s="29">
-        <f>SUM(K3:K7)</f>
+        <f t="shared" si="2"/>
         <v>4886621.7999999989</v>
       </c>
       <c r="L9" s="29">
-        <f>SUM(L3:L7)</f>
+        <f t="shared" si="2"/>
         <v>537811.52</v>
       </c>
       <c r="M9" s="29">
-        <f>SUM(M3:M7)</f>
+        <f t="shared" si="2"/>
         <v>443632.36</v>
       </c>
       <c r="N9" s="29">
-        <f>SUM(N3:N7)</f>
+        <f t="shared" si="2"/>
         <v>5217306.12</v>
       </c>
       <c r="O9" s="29">
-        <f>SUM(O3:O7)</f>
+        <f t="shared" si="2"/>
         <v>204484.7</v>
       </c>
       <c r="P9" s="29">
-        <f>SUM(P3:P7)</f>
+        <f t="shared" si="2"/>
         <v>204493.03</v>
       </c>
       <c r="Q9" s="29">
-        <f>SUM(Q3:Q7)</f>
+        <f t="shared" si="2"/>
         <v>5789772.2699999996</v>
       </c>
       <c r="R9" s="29">
-        <f>SUM(R3:R7)</f>
+        <f t="shared" si="2"/>
         <v>204493.03</v>
       </c>
       <c r="S9" s="29">
-        <f>SUM(S3:S7)</f>
+        <f t="shared" si="2"/>
         <v>201801.96</v>
       </c>
       <c r="T9" s="29">
-        <f>SUM(T3:T7)</f>
+        <f t="shared" si="2"/>
         <v>201810.33</v>
       </c>
       <c r="U9" s="29">
-        <f>SUM(U3:U7)</f>
+        <f t="shared" si="2"/>
         <v>85143.59</v>
       </c>
       <c r="V9" s="29">
-        <f>SUM(V3:V7)</f>
+        <f t="shared" si="2"/>
         <v>85143.59</v>
       </c>
       <c r="W9" s="29">
-        <f>SUM(W3:W7)</f>
+        <f t="shared" si="2"/>
         <v>82669.48000000001</v>
       </c>
       <c r="X9" s="29">
-        <f>SUM(X3:X7)</f>
+        <f t="shared" si="2"/>
         <v>80301.69</v>
       </c>
       <c r="Y9" s="29">
-        <f>SUM(Y3:Y7)</f>
+        <f t="shared" si="2"/>
         <v>80301.69</v>
       </c>
       <c r="Z9" s="29">
-        <f>SUM(Z3:Z7)</f>
+        <f t="shared" si="2"/>
         <v>80301.69</v>
       </c>
       <c r="AA9" s="29">
-        <f>SUM(AA3:AA7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AB9" s="29">
-        <f>SUM(AB3:AB7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC9" s="29">
-        <f>SUM(AC3:AC7)</f>
+        <f t="shared" si="2"/>
         <v>23690032.950000003</v>
       </c>
       <c r="AD9" s="29">
-        <f>SUM(AD3:AD7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AE9" s="29">
-        <f>SUM(AE3:AE7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF9" s="29">
-        <f>SUM(AF3:AF7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG9" s="29">
-        <f>SUM(AG3:AG7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH9" s="29">
-        <f>SUM(AH3:AH7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI9" s="29">
-        <f>SUM(AI3:AI7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ9" s="29">
-        <f>SUM(AJ3:AJ7)</f>
+        <f t="shared" ref="AJ9:BA9" si="3">SUM(AJ3:AJ7)</f>
         <v>0</v>
       </c>
       <c r="AK9" s="29">
-        <f>SUM(AK3:AK7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL9" s="29">
-        <f>SUM(AL3:AL7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AM9" s="29">
-        <f>SUM(AM3:AM7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AN9" s="29">
-        <f>SUM(AN3:AN7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AO9" s="29">
-        <f>SUM(AO3:AO7)</f>
+        <f t="shared" si="3"/>
         <v>24795000</v>
       </c>
       <c r="AP9" s="29">
-        <f>SUM(AP3:AP7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AQ9" s="29">
-        <f>SUM(AQ3:AQ7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AR9" s="29">
-        <f>SUM(AR3:AR7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AS9" s="29">
-        <f>SUM(AS3:AS7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AT9" s="29">
-        <f>SUM(AT3:AT7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AU9" s="29">
-        <f>SUM(AU3:AU7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AV9" s="29">
-        <f>SUM(AV3:AV7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AW9" s="29">
-        <f>SUM(AW3:AW7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX9" s="29">
-        <f>SUM(AX3:AX7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AY9" s="29">
-        <f>SUM(AY3:AY7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AZ9" s="29">
-        <f>SUM(AZ3:AZ7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA9" s="29">
-        <f>SUM(BA3:BA7)</f>
+        <f t="shared" si="3"/>
         <v>24795000</v>
       </c>
       <c r="BB9" s="30">
@@ -9071,7 +11131,7 @@
         <v>15619413.554294141</v>
       </c>
       <c r="BB13" s="41">
-        <f>SUM(E13:BA13)</f>
+        <f t="shared" ref="BB13:BB22" si="4">SUM(E13:BA13)</f>
         <v>42649550.918097198</v>
       </c>
       <c r="BC13" s="41"/>
@@ -9314,7 +11374,7 @@
         <v>422491</v>
       </c>
       <c r="BB14" s="41">
-        <f>SUM(E14:BA14)</f>
+        <f t="shared" si="4"/>
         <v>7488507.898190002</v>
       </c>
       <c r="BC14" s="41"/>
@@ -9357,207 +11417,207 @@
         <v>48</v>
       </c>
       <c r="D15" s="32">
-        <f>SUM(D13:D14)</f>
+        <f t="shared" ref="D15:AI15" si="5">SUM(D13:D14)</f>
         <v>50138058.816287197</v>
       </c>
       <c r="E15" s="32">
-        <f>SUM(E13:E14)</f>
+        <f t="shared" si="5"/>
         <v>10303181.373645578</v>
       </c>
       <c r="F15" s="32">
-        <f>SUM(F13:F14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G15" s="32">
-        <f>SUM(G13:G14)</f>
+        <f t="shared" si="5"/>
         <v>499493.76322999998</v>
       </c>
       <c r="H15" s="32">
-        <f>SUM(H13:H14)</f>
+        <f t="shared" si="5"/>
         <v>551259.15273999993</v>
       </c>
       <c r="I15" s="32">
-        <f>SUM(I13:I14)</f>
+        <f t="shared" si="5"/>
         <v>499493.76322999998</v>
       </c>
       <c r="J15" s="32">
-        <f>SUM(J13:J14)</f>
+        <f t="shared" si="5"/>
         <v>349453.18216999999</v>
       </c>
       <c r="K15" s="32">
-        <f>SUM(K13:K14)</f>
+        <f t="shared" si="5"/>
         <v>297703.64415999997</v>
       </c>
       <c r="L15" s="32">
-        <f>SUM(L13:L14)</f>
+        <f t="shared" si="5"/>
         <v>347964.05344000005</v>
       </c>
       <c r="M15" s="32">
-        <f>SUM(M13:M14)</f>
+        <f t="shared" si="5"/>
         <v>287030.13692000002</v>
       </c>
       <c r="N15" s="32">
-        <f>SUM(N13:N14)</f>
+        <f t="shared" si="5"/>
         <v>337754.32874000003</v>
       </c>
       <c r="O15" s="32">
-        <f>SUM(O13:O14)</f>
+        <f t="shared" si="5"/>
         <v>132301.60090000002</v>
       </c>
       <c r="P15" s="32">
-        <f>SUM(P13:P14)</f>
+        <f t="shared" si="5"/>
         <v>132306.99041</v>
       </c>
       <c r="Q15" s="32">
-        <f>SUM(Q13:Q14)</f>
+        <f t="shared" si="5"/>
         <v>132301.60090000002</v>
       </c>
       <c r="R15" s="32">
-        <f>SUM(R13:R14)</f>
+        <f t="shared" si="5"/>
         <v>132306.99041</v>
       </c>
       <c r="S15" s="32">
-        <f>SUM(S13:S14)</f>
+        <f t="shared" si="5"/>
         <v>130565.86812</v>
       </c>
       <c r="T15" s="32">
-        <f>SUM(T13:T14)</f>
+        <f t="shared" si="5"/>
         <v>130571.28350999999</v>
       </c>
       <c r="U15" s="32">
-        <f>SUM(U13:U14)</f>
+        <f t="shared" si="5"/>
         <v>55087.902730000002</v>
       </c>
       <c r="V15" s="32">
-        <f>SUM(V13:V14)</f>
+        <f t="shared" si="5"/>
         <v>55087.902730000002</v>
       </c>
       <c r="W15" s="32">
-        <f>SUM(W13:W14)</f>
+        <f t="shared" si="5"/>
         <v>53487.153560000006</v>
       </c>
       <c r="X15" s="32">
-        <f>SUM(X13:X14)</f>
+        <f t="shared" si="5"/>
         <v>51955.193430000007</v>
       </c>
       <c r="Y15" s="32">
-        <f>SUM(Y13:Y14)</f>
+        <f t="shared" si="5"/>
         <v>51955.193430000007</v>
       </c>
       <c r="Z15" s="32">
-        <f>SUM(Z13:Z14)</f>
+        <f t="shared" si="5"/>
         <v>51955.193430000007</v>
       </c>
       <c r="AA15" s="32">
-        <f>SUM(AA13:AA14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB15" s="32">
-        <f>SUM(AB13:AB14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC15" s="32">
-        <f>SUM(AC13:AC14)</f>
+        <f t="shared" si="5"/>
         <v>3471033.4358633407</v>
       </c>
       <c r="AD15" s="32">
-        <f>SUM(AD13:AD14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE15" s="32">
-        <f>SUM(AE13:AE14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF15" s="32">
-        <f>SUM(AF13:AF14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG15" s="32">
-        <f>SUM(AG13:AG14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AH15" s="32">
-        <f>SUM(AH13:AH14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AI15" s="32">
-        <f>SUM(AI13:AI14)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AJ15" s="32">
-        <f>SUM(AJ13:AJ14)</f>
+        <f t="shared" ref="AJ15:BO15" si="6">SUM(AJ13:AJ14)</f>
         <v>0</v>
       </c>
       <c r="AK15" s="32">
-        <f>SUM(AK13:AK14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AL15" s="32">
-        <f>SUM(AL13:AL14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AM15" s="32">
-        <f>SUM(AM13:AM14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AN15" s="32">
-        <f>SUM(AN13:AN14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AO15" s="32">
-        <f>SUM(AO13:AO14)</f>
+        <f t="shared" si="6"/>
         <v>16041904.554294141</v>
       </c>
       <c r="AP15" s="32">
-        <f>SUM(AP13:AP14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ15" s="32">
-        <f>SUM(AQ13:AQ14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR15" s="32">
-        <f>SUM(AR13:AR14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS15" s="32">
-        <f>SUM(AS13:AS14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT15" s="32">
-        <f>SUM(AT13:AT14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU15" s="32">
-        <f>SUM(AU13:AU14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV15" s="32">
-        <f>SUM(AV13:AV14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW15" s="32">
-        <f>SUM(AW13:AW14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX15" s="32">
-        <f>SUM(AX13:AX14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY15" s="32">
-        <f>SUM(AY13:AY14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ15" s="32">
-        <f>SUM(AZ13:AZ14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA15" s="32">
-        <f>SUM(BA13:BA14)</f>
+        <f t="shared" si="6"/>
         <v>16041904.554294141</v>
       </c>
       <c r="BB15" s="41">
-        <f>SUM(E15:BA15)</f>
+        <f t="shared" si="4"/>
         <v>50138058.816287197</v>
       </c>
       <c r="BC15" s="41"/>
@@ -9800,7 +11860,7 @@
         <v>8522586.4457058571</v>
       </c>
       <c r="BB16" s="41">
-        <f>SUM(E16:BA16)</f>
+        <f t="shared" si="4"/>
         <v>23271327.268883705</v>
       </c>
       <c r="BC16" s="43"/>
@@ -10043,7 +12103,7 @@
         <v>230509</v>
       </c>
       <c r="BB17" s="41">
-        <f>SUM(E17:BA17)</f>
+        <f t="shared" si="4"/>
         <v>4085692.8718100009</v>
       </c>
       <c r="BC17" s="43"/>
@@ -10077,7 +12137,7 @@
     </row>
     <row r="18" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="31" t="s">
-        <v>90</v>
+        <v>177</v>
       </c>
       <c r="B18" s="33" t="s">
         <v>81</v>
@@ -10086,207 +12146,207 @@
         <v>51</v>
       </c>
       <c r="D18" s="32">
-        <f>SUM(D16:D17)</f>
+        <f t="shared" ref="D18:AI18" si="7">SUM(D16:D17)</f>
         <v>27357020.140693706</v>
       </c>
       <c r="E18" s="32">
-        <f>SUM(E16:E17)</f>
+        <f t="shared" si="7"/>
         <v>5621745.8024486918</v>
       </c>
       <c r="F18" s="32">
-        <f>SUM(F16:F17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G18" s="32">
-        <f>SUM(G16:G17)</f>
+        <f t="shared" si="7"/>
         <v>272521.32676999999</v>
       </c>
       <c r="H18" s="32">
-        <f>SUM(H16:H17)</f>
+        <f t="shared" si="7"/>
         <v>300764.26725999994</v>
       </c>
       <c r="I18" s="32">
-        <f>SUM(I16:I17)</f>
+        <f t="shared" si="7"/>
         <v>272521.32676999999</v>
       </c>
       <c r="J18" s="32">
-        <f>SUM(J16:J17)</f>
+        <f t="shared" si="7"/>
         <v>190659.92782999997</v>
       </c>
       <c r="K18" s="32">
-        <f>SUM(K16:K17)</f>
+        <f t="shared" si="7"/>
         <v>162425.63583999997</v>
       </c>
       <c r="L18" s="32">
-        <f>SUM(L16:L17)</f>
+        <f t="shared" si="7"/>
         <v>189847.46656</v>
       </c>
       <c r="M18" s="32">
-        <f>SUM(M16:M17)</f>
+        <f t="shared" si="7"/>
         <v>156602.22308</v>
       </c>
       <c r="N18" s="32">
-        <f>SUM(N16:N17)</f>
+        <f t="shared" si="7"/>
         <v>184277.09125999999</v>
       </c>
       <c r="O18" s="32">
-        <f>SUM(O16:O17)</f>
+        <f t="shared" si="7"/>
         <v>72183.099100000007</v>
       </c>
       <c r="P18" s="32">
-        <f>SUM(P16:P17)</f>
+        <f t="shared" si="7"/>
         <v>72186.03959</v>
       </c>
       <c r="Q18" s="32">
-        <f>SUM(Q16:Q17)</f>
+        <f t="shared" si="7"/>
         <v>72183.099100000007</v>
       </c>
       <c r="R18" s="32">
-        <f>SUM(R16:R17)</f>
+        <f t="shared" si="7"/>
         <v>72186.03959</v>
       </c>
       <c r="S18" s="32">
-        <f>SUM(S16:S17)</f>
+        <f t="shared" si="7"/>
         <v>71236.091879999993</v>
       </c>
       <c r="T18" s="32">
-        <f>SUM(T16:T17)</f>
+        <f t="shared" si="7"/>
         <v>71239.046489999993</v>
       </c>
       <c r="U18" s="32">
-        <f>SUM(U16:U17)</f>
+        <f t="shared" si="7"/>
         <v>30055.687269999999</v>
       </c>
       <c r="V18" s="32">
-        <f>SUM(V16:V17)</f>
+        <f t="shared" si="7"/>
         <v>30055.687269999999</v>
       </c>
       <c r="W18" s="32">
-        <f>SUM(W16:W17)</f>
+        <f t="shared" si="7"/>
         <v>29182.326440000001</v>
       </c>
       <c r="X18" s="32">
-        <f>SUM(X16:X17)</f>
+        <f t="shared" si="7"/>
         <v>28346.496569999999</v>
       </c>
       <c r="Y18" s="32">
-        <f>SUM(Y16:Y17)</f>
+        <f t="shared" si="7"/>
         <v>28346.496569999999</v>
       </c>
       <c r="Z18" s="32">
-        <f>SUM(Z16:Z17)</f>
+        <f t="shared" si="7"/>
         <v>28346.496569999999</v>
       </c>
       <c r="AA18" s="32">
-        <f>SUM(AA16:AA17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB18" s="32">
-        <f>SUM(AB16:AB17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC18" s="32">
-        <f>SUM(AC16:AC17)</f>
+        <f t="shared" si="7"/>
         <v>1893917.5750232993</v>
       </c>
       <c r="AD18" s="32">
-        <f>SUM(AD16:AD17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE18" s="32">
-        <f>SUM(AE16:AE17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF18" s="32">
-        <f>SUM(AF16:AF17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG18" s="32">
-        <f>SUM(AG16:AG17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH18" s="32">
-        <f>SUM(AH16:AH17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AI18" s="32">
-        <f>SUM(AI16:AI17)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AJ18" s="32">
-        <f>SUM(AJ16:AJ17)</f>
+        <f t="shared" ref="AJ18:BO18" si="8">SUM(AJ16:AJ17)</f>
         <v>0</v>
       </c>
       <c r="AK18" s="32">
-        <f>SUM(AK16:AK17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AL18" s="32">
-        <f>SUM(AL16:AL17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AM18" s="32">
-        <f>SUM(AM16:AM17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AN18" s="32">
-        <f>SUM(AN16:AN17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AO18" s="32">
-        <f>SUM(AO16:AO17)</f>
+        <f t="shared" si="8"/>
         <v>8753095.4457058571</v>
       </c>
       <c r="AP18" s="32">
-        <f>SUM(AP16:AP17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AQ18" s="32">
-        <f>SUM(AQ16:AQ17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AR18" s="32">
-        <f>SUM(AR16:AR17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AS18" s="32">
-        <f>SUM(AS16:AS17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AT18" s="32">
-        <f>SUM(AT16:AT17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AU18" s="32">
-        <f>SUM(AU16:AU17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AV18" s="32">
-        <f>SUM(AV16:AV17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AW18" s="32">
-        <f>SUM(AW16:AW17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AX18" s="32">
-        <f>SUM(AX16:AX17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AY18" s="32">
-        <f>SUM(AY16:AY17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AZ18" s="32">
-        <f>SUM(AZ16:AZ17)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BA18" s="32">
-        <f>SUM(BA16:BA17)</f>
+        <f t="shared" si="8"/>
         <v>8753095.4457058571</v>
       </c>
       <c r="BB18" s="41">
-        <f>SUM(E18:BA18)</f>
+        <f t="shared" si="4"/>
         <v>27357020.140693706</v>
       </c>
       <c r="BC18" s="43"/>
@@ -10338,199 +12398,199 @@
         <v>28762280.73</v>
       </c>
       <c r="F19" s="30">
-        <f>F4</f>
+        <f t="shared" ref="F19:BA19" si="9">F4</f>
         <v>0</v>
       </c>
       <c r="G19" s="30">
-        <f>G4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H19" s="30">
-        <f>H4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I19" s="30">
-        <f>I4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J19" s="30">
-        <f>J4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K19" s="30">
-        <f>K4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L19" s="30">
-        <f>L4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M19" s="30">
-        <f>M4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N19" s="30">
-        <f>N4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O19" s="30">
-        <f>O4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P19" s="30">
-        <f>P4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q19" s="30">
-        <f>Q4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R19" s="30">
-        <f>R4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S19" s="30">
-        <f>S4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T19" s="30">
-        <f>T4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U19" s="30">
-        <f>U4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V19" s="30">
-        <f>V4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W19" s="30">
-        <f>W4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X19" s="30">
-        <f>X4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y19" s="30">
-        <f>Y4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z19" s="30">
-        <f>Z4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA19" s="30">
-        <f>AA4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB19" s="30">
-        <f>AB4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC19" s="30">
-        <f>AC4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD19" s="30">
-        <f>AD4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE19" s="30">
-        <f>AE4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF19" s="30">
-        <f>AF4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AG19" s="30">
-        <f>AG4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH19" s="30">
-        <f>AH4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AI19" s="30">
-        <f>AI4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ19" s="30">
-        <f>AJ4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AK19" s="30">
-        <f>AK4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL19" s="30">
-        <f>AL4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM19" s="30">
-        <f>AM4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AN19" s="30">
-        <f>AN4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AO19" s="30">
-        <f>AO4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AP19" s="30">
-        <f>AP4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AQ19" s="30">
-        <f>AQ4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AR19" s="30">
-        <f>AR4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AS19" s="30">
-        <f>AS4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AT19" s="30">
-        <f>AT4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AU19" s="30">
-        <f>AU4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AV19" s="30">
-        <f>AV4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AW19" s="30">
-        <f>AW4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AX19" s="30">
-        <f>AX4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AY19" s="30">
-        <f>AY4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AZ19" s="30">
-        <f>AZ4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BA19" s="30">
-        <f>BA4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BB19" s="30">
-        <f>SUM(E19:BA19)</f>
+        <f t="shared" si="4"/>
         <v>28762280.73</v>
       </c>
       <c r="BC19" s="28"/>
@@ -10774,7 +12834,7 @@
         <v>0</v>
       </c>
       <c r="BB20" s="30">
-        <f>SUM(E20:BA20)</f>
+        <f t="shared" si="4"/>
         <v>11239020</v>
       </c>
     </row>
@@ -10990,7 +13050,7 @@
         <v>0</v>
       </c>
       <c r="BB21" s="30">
-        <f>SUM(E21:BA21)</f>
+        <f t="shared" si="4"/>
         <v>44560980.313019082</v>
       </c>
       <c r="BC21" s="30">
@@ -11210,7 +13270,7 @@
         <v>0</v>
       </c>
       <c r="BB22" s="30">
-        <f>SUM(E22:BA22)</f>
+        <f t="shared" si="4"/>
         <v>3242640</v>
       </c>
     </row>
@@ -11219,207 +13279,207 @@
         <v>84</v>
       </c>
       <c r="D23" s="29">
-        <f>SUM(D20:D22)</f>
+        <f t="shared" ref="D23:AI23" si="10">SUM(D20:D22)</f>
         <v>59042640.313019089</v>
       </c>
       <c r="E23" s="29">
-        <f>SUM(E20:E22)</f>
+        <f t="shared" si="10"/>
         <v>21432792.093905725</v>
       </c>
       <c r="F23" s="29">
-        <f>SUM(F20:F22)</f>
+        <f t="shared" si="10"/>
         <v>1525903.83</v>
       </c>
       <c r="G23" s="29">
-        <f>SUM(G20:G22)</f>
+        <f t="shared" si="10"/>
         <v>1525903.83</v>
       </c>
       <c r="H23" s="29">
-        <f>SUM(H20:H22)</f>
+        <f t="shared" si="10"/>
         <v>1525903.83</v>
       </c>
       <c r="I23" s="29">
-        <f>SUM(I20:I22)</f>
+        <f t="shared" si="10"/>
         <v>1475497.5066666666</v>
       </c>
       <c r="J23" s="29">
-        <f>SUM(J20:J22)</f>
+        <f t="shared" si="10"/>
         <v>1475497.5066666666</v>
       </c>
       <c r="K23" s="29">
-        <f>SUM(K20:K22)</f>
+        <f t="shared" si="10"/>
         <v>1475497.5066666666</v>
       </c>
       <c r="L23" s="29">
-        <f>SUM(L20:L22)</f>
+        <f t="shared" si="10"/>
         <v>1565091.5666666667</v>
       </c>
       <c r="M23" s="29">
-        <f>SUM(M20:M22)</f>
+        <f t="shared" si="10"/>
         <v>1565091.5666666667</v>
       </c>
       <c r="N23" s="29">
-        <f>SUM(N20:N22)</f>
+        <f t="shared" si="10"/>
         <v>1565091.5666666667</v>
       </c>
       <c r="O23" s="29">
-        <f>SUM(O20:O22)</f>
+        <f t="shared" si="10"/>
         <v>1861762.523333333</v>
       </c>
       <c r="P23" s="29">
-        <f>SUM(P20:P22)</f>
+        <f t="shared" si="10"/>
         <v>1861762.523333333</v>
       </c>
       <c r="Q23" s="29">
-        <f>SUM(Q20:Q22)</f>
+        <f t="shared" si="10"/>
         <v>1861762.523333333</v>
       </c>
       <c r="R23" s="29">
-        <f>SUM(R20:R22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S23" s="29">
-        <f>SUM(S20:S22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T23" s="29">
-        <f>SUM(T20:T22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U23" s="29">
-        <f>SUM(U20:U22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="V23" s="29">
-        <f>SUM(V20:V22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="W23" s="29">
-        <f>SUM(W20:W22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X23" s="29">
-        <f>SUM(X20:X22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Y23" s="29">
-        <f>SUM(Y20:Y22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Z23" s="29">
-        <f>SUM(Z20:Z22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AA23" s="29">
-        <f>SUM(AA20:AA22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB23" s="29">
-        <f>SUM(AB20:AB22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AC23" s="29">
-        <f>SUM(AC20:AC22)</f>
+        <f t="shared" si="10"/>
         <v>18325081.939113364</v>
       </c>
       <c r="AD23" s="29">
-        <f>SUM(AD20:AD22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AE23" s="29">
-        <f>SUM(AE20:AE22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AF23" s="29">
-        <f>SUM(AF20:AF22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AG23" s="29">
-        <f>SUM(AG20:AG22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AH23" s="29">
-        <f>SUM(AH20:AH22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AI23" s="29">
-        <f>SUM(AI20:AI22)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ23" s="29">
-        <f>SUM(AJ20:AJ22)</f>
+        <f t="shared" ref="AJ23:BO23" si="11">SUM(AJ20:AJ22)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="29">
-        <f>SUM(AK20:AK22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL23" s="29">
-        <f>SUM(AL20:AL22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AM23" s="29">
-        <f>SUM(AM20:AM22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AN23" s="29">
-        <f>SUM(AN20:AN22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO23" s="29">
-        <f>SUM(AO20:AO22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP23" s="29">
-        <f>SUM(AP20:AP22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ23" s="29">
-        <f>SUM(AQ20:AQ22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR23" s="29">
-        <f>SUM(AR20:AR22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS23" s="29">
-        <f>SUM(AS20:AS22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT23" s="29">
-        <f>SUM(AT20:AT22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU23" s="29">
-        <f>SUM(AU20:AU22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV23" s="29">
-        <f>SUM(AV20:AV22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW23" s="29">
-        <f>SUM(AW20:AW22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX23" s="29">
-        <f>SUM(AX20:AX22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY23" s="29">
-        <f>SUM(AY20:AY22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ23" s="29">
-        <f>SUM(AZ20:AZ22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA23" s="29">
-        <f>SUM(BA20:BA22)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BB23" s="29">
-        <f>SUM(BB20:BB22)</f>
+        <f t="shared" si="11"/>
         <v>59042640.313019082</v>
       </c>
     </row>
@@ -11428,209 +13488,210 @@
         <v>77</v>
       </c>
       <c r="D24" s="29">
-        <f>SUM(D13:D22)</f>
-        <v>242795078.95698088</v>
+        <f>D15+D18+D19+D23</f>
+        <v>165300000</v>
       </c>
       <c r="E24" s="29">
-        <f>SUM(E20:E22)</f>
-        <v>21432792.093905725</v>
+        <f t="shared" ref="E24:BA24" si="12">E15+E18+E19+E23</f>
+        <v>66119999.999999993</v>
       </c>
       <c r="F24" s="29">
-        <f>SUM(F20:F22)</f>
+        <f t="shared" si="12"/>
         <v>1525903.83</v>
       </c>
       <c r="G24" s="29">
-        <f>SUM(G20:G22)</f>
-        <v>1525903.83</v>
+        <f t="shared" si="12"/>
+        <v>2297918.92</v>
       </c>
       <c r="H24" s="29">
-        <f>SUM(H20:H22)</f>
-        <v>1525903.83</v>
+        <f t="shared" si="12"/>
+        <v>2377927.25</v>
       </c>
       <c r="I24" s="29">
-        <f>SUM(I20:I22)</f>
-        <v>1475497.5066666666</v>
+        <f t="shared" si="12"/>
+        <v>2247512.5966666667</v>
       </c>
       <c r="J24" s="29">
-        <f>SUM(J20:J22)</f>
-        <v>1475497.5066666666</v>
+        <f t="shared" si="12"/>
+        <v>2015610.6166666667</v>
       </c>
       <c r="K24" s="29">
-        <f>SUM(K20:K22)</f>
-        <v>1475497.5066666666</v>
+        <f t="shared" si="12"/>
+        <v>1935626.7866666666</v>
       </c>
       <c r="L24" s="29">
-        <f>SUM(L20:L22)</f>
-        <v>1565091.5666666667</v>
+        <f t="shared" si="12"/>
+        <v>2102903.0866666669</v>
       </c>
       <c r="M24" s="29">
-        <f>SUM(M20:M22)</f>
-        <v>1565091.5666666667</v>
+        <f t="shared" si="12"/>
+        <v>2008723.9266666668</v>
       </c>
       <c r="N24" s="29">
-        <f>SUM(N20:N22)</f>
-        <v>1565091.5666666667</v>
+        <f t="shared" si="12"/>
+        <v>2087122.9866666668</v>
       </c>
       <c r="O24" s="29">
-        <f>SUM(O20:O22)</f>
-        <v>1861762.523333333</v>
+        <f t="shared" si="12"/>
+        <v>2066247.2233333329</v>
       </c>
       <c r="P24" s="29">
-        <f>SUM(P20:P22)</f>
-        <v>1861762.523333333</v>
+        <f t="shared" si="12"/>
+        <v>2066255.553333333</v>
       </c>
       <c r="Q24" s="29">
-        <f>SUM(Q20:Q22)</f>
-        <v>1861762.523333333</v>
+        <f t="shared" si="12"/>
+        <v>2066247.2233333329</v>
       </c>
       <c r="R24" s="29">
-        <f>SUM(R20:R22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>204493.03</v>
       </c>
       <c r="S24" s="29">
-        <f>SUM(S20:S22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>201801.96</v>
       </c>
       <c r="T24" s="29">
-        <f>SUM(T20:T22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>201810.33</v>
       </c>
       <c r="U24" s="29">
-        <f>SUM(U20:U22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>85143.59</v>
       </c>
       <c r="V24" s="29">
-        <f>SUM(V20:V22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>85143.59</v>
       </c>
       <c r="W24" s="29">
-        <f>SUM(W20:W22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>82669.48000000001</v>
       </c>
       <c r="X24" s="29">
-        <f>SUM(X20:X22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>80301.69</v>
       </c>
       <c r="Y24" s="29">
-        <f>SUM(Y20:Y22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>80301.69</v>
       </c>
       <c r="Z24" s="29">
-        <f>SUM(Z20:Z22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>80301.69</v>
       </c>
       <c r="AA24" s="29">
-        <f>SUM(AA20:AA22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AB24" s="29">
-        <f>SUM(AB20:AB22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AC24" s="29">
-        <f>SUM(AC20:AC22)</f>
-        <v>18325081.939113364</v>
+        <f t="shared" si="12"/>
+        <v>23690032.950000003</v>
       </c>
       <c r="AD24" s="29">
-        <f>SUM(AD20:AD22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AE24" s="29">
-        <f>SUM(AE20:AE22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AF24" s="29">
-        <f>SUM(AF20:AF22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AG24" s="29">
-        <f>SUM(AG20:AG22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AH24" s="29">
-        <f>SUM(AH20:AH22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AI24" s="29">
-        <f>SUM(AI20:AI22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AJ24" s="29">
-        <f>SUM(AJ20:AJ22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AK24" s="29">
-        <f>SUM(AK20:AK22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AL24" s="29">
-        <f>SUM(AL20:AL22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AM24" s="29">
-        <f>SUM(AM20:AM22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN24" s="29">
-        <f>SUM(AN20:AN22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO24" s="29">
-        <f>SUM(AO20:AO22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>24795000</v>
       </c>
       <c r="AP24" s="29">
-        <f>SUM(AP20:AP22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AQ24" s="29">
-        <f>SUM(AQ20:AQ22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR24" s="29">
-        <f>SUM(AR20:AR22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AS24" s="29">
-        <f>SUM(AS20:AS22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AT24" s="29">
-        <f>SUM(AT20:AT22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AU24" s="29">
-        <f>SUM(AU20:AU22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AV24" s="29">
-        <f>SUM(AV20:AV22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW24" s="29">
-        <f>SUM(AW20:AW22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AX24" s="29">
-        <f>SUM(AX20:AX22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AY24" s="29">
-        <f>SUM(AY20:AY22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AZ24" s="29">
-        <f>SUM(AZ20:AZ22)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BA24" s="29">
-        <f>SUM(BA20:BA22)</f>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>24795000</v>
       </c>
       <c r="BB24" s="30">
         <f>BB15+BB18+BB19+BB23</f>
         <v>165300000</v>
       </c>
+      <c r="BC24" s="30"/>
     </row>
     <row r="25" spans="1:82" x14ac:dyDescent="0.2">
       <c r="E25" s="29"/>
@@ -11684,9 +13745,6 @@
       <c r="BA25" s="29"/>
       <c r="BB25" s="30"/>
     </row>
-    <row r="26" spans="1:82" x14ac:dyDescent="0.2">
-      <c r="D26" s="30"/>
-    </row>
     <row r="45" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E45" s="29"/>
     </row>
@@ -11707,20 +13765,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9218DFE5-209B-2241-8847-333DF7C258A2}">
-  <dimension ref="A2:W19"/>
+  <dimension ref="A2:BA56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="18.1640625" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:23" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="45"/>
+      <c r="B2" s="50"/>
       <c r="C2" s="34" t="s">
         <v>79</v>
       </c>
@@ -11781,13 +13843,13 @@
       <c r="V2" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="W2" s="46" t="s">
+      <c r="W2" s="48" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
       <c r="C3" s="28">
         <v>46295</v>
       </c>
@@ -11848,9 +13910,9 @@
       <c r="V3" s="28">
         <v>46873</v>
       </c>
-      <c r="W3" s="46"/>
-    </row>
-    <row r="4" spans="1:23" s="33" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+      <c r="W3" s="48"/>
+    </row>
+    <row r="4" spans="1:23" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="44" t="s">
         <v>98</v>
       </c>
@@ -11938,7 +14000,7 @@
         <v>80301.69</v>
       </c>
       <c r="W4" s="41">
-        <f>SUM(C4:V4)</f>
+        <f t="shared" ref="W4:W20" si="0">SUM(C4:V4)</f>
         <v>6615200.7700000014</v>
       </c>
     </row>
@@ -12030,7 +14092,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="30">
-        <f>SUM(C5:V5)</f>
+        <f t="shared" si="0"/>
         <v>816666.70000000007</v>
       </c>
     </row>
@@ -12122,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="30">
-        <f>SUM(C6:V6)</f>
+        <f t="shared" si="0"/>
         <v>1268811.9199999995</v>
       </c>
     </row>
@@ -12214,7 +14276,7 @@
         <v>1190.07</v>
       </c>
       <c r="W7" s="30">
-        <f>SUM(C7:V7)</f>
+        <f t="shared" si="0"/>
         <v>23801.399999999998</v>
       </c>
     </row>
@@ -12306,7 +14368,7 @@
         <v>22376.07</v>
       </c>
       <c r="W8" s="30">
-        <f>SUM(C8:V8)</f>
+        <f t="shared" si="0"/>
         <v>447521.40000000008</v>
       </c>
     </row>
@@ -12398,7 +14460,7 @@
         <v>10710.64</v>
       </c>
       <c r="W9" s="30">
-        <f>SUM(C9:V9)</f>
+        <f t="shared" si="0"/>
         <v>214212.8000000001</v>
       </c>
     </row>
@@ -12490,7 +14552,7 @@
         <v>23648.84</v>
       </c>
       <c r="W10" s="30">
-        <f>SUM(C10:V10)</f>
+        <f t="shared" si="0"/>
         <v>472976.80000000022</v>
       </c>
     </row>
@@ -12582,7 +14644,7 @@
         <v>22376.07</v>
       </c>
       <c r="W11" s="30">
-        <f>SUM(C11:V11)</f>
+        <f t="shared" si="0"/>
         <v>447521.40000000008</v>
       </c>
     </row>
@@ -12674,7 +14736,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="30">
-        <f>SUM(C12:V12)</f>
+        <f t="shared" si="0"/>
         <v>1965903.1999999997</v>
       </c>
     </row>
@@ -12766,7 +14828,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="30">
-        <f>SUM(C13:V13)</f>
+        <f t="shared" si="0"/>
         <v>496608.35000000003</v>
       </c>
     </row>
@@ -12858,458 +14920,1126 @@
         <v>0</v>
       </c>
       <c r="W14" s="30">
-        <f>SUM(C14:V14)</f>
+        <f t="shared" si="0"/>
         <v>461176.79999999993</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="47"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="29">
-        <f>C5+SUM(C7:C11)+C13</f>
+        <f t="shared" ref="C15:V15" si="1">C5+SUM(C7:C11)+C13</f>
         <v>116960.02</v>
       </c>
       <c r="D15" s="29">
-        <f>D5+SUM(D7:D11)+D13</f>
+        <f t="shared" si="1"/>
         <v>196968.35</v>
       </c>
       <c r="E15" s="29">
-        <f>E5+SUM(E7:E11)+E13</f>
+        <f t="shared" si="1"/>
         <v>116960.02</v>
       </c>
       <c r="F15" s="29">
-        <f>F5+SUM(F7:F11)+F13</f>
+        <f t="shared" si="1"/>
         <v>196968.35</v>
       </c>
       <c r="G15" s="29">
-        <f>G5+SUM(G7:G11)+G13</f>
+        <f t="shared" si="1"/>
         <v>116960.02</v>
       </c>
       <c r="H15" s="29">
-        <f>H5+SUM(H7:H11)+H13</f>
+        <f t="shared" si="1"/>
         <v>196968.35</v>
       </c>
       <c r="I15" s="29">
-        <f>I5+SUM(I7:I11)+I13</f>
+        <f t="shared" si="1"/>
         <v>116960.02</v>
       </c>
       <c r="J15" s="29">
-        <f>J5+SUM(J7:J11)+J13</f>
+        <f t="shared" si="1"/>
         <v>196968.35</v>
       </c>
       <c r="K15" s="29">
-        <f>K5+SUM(K7:K11)+K13</f>
+        <f t="shared" si="1"/>
         <v>196960.02000000002</v>
       </c>
       <c r="L15" s="29">
-        <f>L5+SUM(L7:L11)+L13</f>
+        <f t="shared" si="1"/>
         <v>196968.35</v>
       </c>
       <c r="M15" s="29">
-        <f>M5+SUM(M7:M11)+M13</f>
+        <f t="shared" si="1"/>
         <v>196960.02000000002</v>
       </c>
       <c r="N15" s="29">
-        <f>N5+SUM(N7:N11)+N13</f>
+        <f t="shared" si="1"/>
         <v>196968.35</v>
       </c>
       <c r="O15" s="29">
-        <f>O5+SUM(O7:O11)+O13</f>
+        <f t="shared" si="1"/>
         <v>196960.06</v>
       </c>
       <c r="P15" s="29">
-        <f>P5+SUM(P7:P11)+P13</f>
+        <f t="shared" si="1"/>
         <v>196968.43</v>
       </c>
       <c r="Q15" s="29">
-        <f>Q5+SUM(Q7:Q11)+Q13</f>
+        <f t="shared" si="1"/>
         <v>80301.69</v>
       </c>
       <c r="R15" s="29">
-        <f>R5+SUM(R7:R11)+R13</f>
+        <f t="shared" si="1"/>
         <v>80301.69</v>
       </c>
       <c r="S15" s="29">
-        <f>S5+SUM(S7:S11)+S13</f>
+        <f t="shared" si="1"/>
         <v>80301.69</v>
       </c>
       <c r="T15" s="29">
-        <f>T5+SUM(T7:T11)+T13</f>
+        <f t="shared" si="1"/>
         <v>80301.69</v>
       </c>
       <c r="U15" s="29">
-        <f>U5+SUM(U7:U11)+U13</f>
+        <f t="shared" si="1"/>
         <v>80301.69</v>
       </c>
       <c r="V15" s="29">
-        <f>V5+SUM(V7:V11)+V13</f>
+        <f t="shared" si="1"/>
         <v>80301.69</v>
       </c>
       <c r="W15" s="30">
-        <f>SUM(C15:V15)</f>
+        <f t="shared" si="0"/>
         <v>2919308.85</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="47"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="30">
-        <f>C6+C12+C14</f>
+        <f t="shared" ref="C16:V16" si="2">C6+C12+C14</f>
         <v>655055.06999999995</v>
       </c>
       <c r="D16" s="30">
-        <f>D6+D12+D14</f>
+        <f t="shared" si="2"/>
         <v>655055.06999999995</v>
       </c>
       <c r="E16" s="30">
-        <f>E6+E12+E14</f>
+        <f t="shared" si="2"/>
         <v>655055.06999999995</v>
       </c>
       <c r="F16" s="30">
-        <f>F6+F12+F14</f>
+        <f t="shared" si="2"/>
         <v>343144.75999999995</v>
       </c>
       <c r="G16" s="30">
-        <f>G6+G12+G14</f>
+        <f t="shared" si="2"/>
         <v>343169.25999999995</v>
       </c>
       <c r="H16" s="30">
-        <f>H6+H12+H14</f>
+        <f t="shared" si="2"/>
         <v>340843.17</v>
       </c>
       <c r="I16" s="30">
-        <f>I6+I12+I14</f>
+        <f t="shared" si="2"/>
         <v>326672.33999999997</v>
       </c>
       <c r="J16" s="30">
-        <f>J6+J12+J14</f>
+        <f t="shared" si="2"/>
         <v>325063.06999999995</v>
       </c>
       <c r="K16" s="30">
-        <f>K6+K12+K14</f>
+        <f t="shared" si="2"/>
         <v>7524.68</v>
       </c>
       <c r="L16" s="30">
-        <f>L6+L12+L14</f>
+        <f t="shared" si="2"/>
         <v>7524.68</v>
       </c>
       <c r="M16" s="30">
-        <f>M6+M12+M14</f>
+        <f t="shared" si="2"/>
         <v>7524.68</v>
       </c>
       <c r="N16" s="30">
-        <f>N6+N12+N14</f>
+        <f t="shared" si="2"/>
         <v>7524.68</v>
       </c>
       <c r="O16" s="30">
-        <f>O6+O12+O14</f>
+        <f t="shared" si="2"/>
         <v>4841.8999999999996</v>
       </c>
       <c r="P16" s="30">
-        <f>P6+P12+P14</f>
+        <f t="shared" si="2"/>
         <v>4841.8999999999996</v>
       </c>
       <c r="Q16" s="30">
-        <f>Q6+Q12+Q14</f>
+        <f t="shared" si="2"/>
         <v>4841.8999999999996</v>
       </c>
       <c r="R16" s="30">
-        <f>R6+R12+R14</f>
+        <f t="shared" si="2"/>
         <v>4841.8999999999996</v>
       </c>
       <c r="S16" s="30">
-        <f>S6+S12+S14</f>
+        <f t="shared" si="2"/>
         <v>2367.79</v>
       </c>
       <c r="T16" s="30">
-        <f>T6+T12+T14</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U16" s="30">
-        <f>U6+U12+U14</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V16" s="30">
-        <f>V6+V12+V14</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W16" s="30">
-        <f>SUM(C16:V16)</f>
+        <f t="shared" si="0"/>
         <v>3695891.9199999995</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A17" s="48" t="s">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A17" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="48"/>
+      <c r="B17" s="47"/>
       <c r="C17" s="30">
-        <f>C4*64.7%</f>
+        <f t="shared" ref="C17:V17" si="3">C4*64.7%</f>
         <v>499493.76322999998</v>
       </c>
       <c r="D17" s="30">
-        <f>D4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>551259.15273999993</v>
       </c>
       <c r="E17" s="30">
-        <f>E4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>499493.76322999998</v>
       </c>
       <c r="F17" s="30">
-        <f>F4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>349453.18216999999</v>
       </c>
       <c r="G17" s="30">
-        <f>G4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>297703.64415999997</v>
       </c>
       <c r="H17" s="30">
-        <f>H4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>347964.05344000005</v>
       </c>
       <c r="I17" s="30">
-        <f>I4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>287030.13692000002</v>
       </c>
       <c r="J17" s="30">
-        <f>J4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>337754.32874000003</v>
       </c>
       <c r="K17" s="30">
-        <f>K4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>132301.60090000002</v>
       </c>
       <c r="L17" s="30">
-        <f>L4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>132306.99041</v>
       </c>
       <c r="M17" s="30">
-        <f>M4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>132301.60090000002</v>
       </c>
       <c r="N17" s="30">
-        <f>N4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>132306.99041</v>
       </c>
       <c r="O17" s="30">
-        <f>O4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>130565.86812</v>
       </c>
       <c r="P17" s="30">
-        <f>P4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>130571.28350999999</v>
       </c>
       <c r="Q17" s="30">
-        <f>Q4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>55087.902730000002</v>
       </c>
       <c r="R17" s="30">
-        <f>R4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>55087.902730000002</v>
       </c>
       <c r="S17" s="30">
-        <f>S4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>53487.153560000006</v>
       </c>
       <c r="T17" s="30">
-        <f>T4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>51955.193430000007</v>
       </c>
       <c r="U17" s="30">
-        <f>U4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>51955.193430000007</v>
       </c>
       <c r="V17" s="30">
-        <f>V4*64.7%</f>
+        <f t="shared" si="3"/>
         <v>51955.193430000007</v>
       </c>
       <c r="W17" s="30">
-        <f>SUM(C17:V17)</f>
+        <f t="shared" si="0"/>
         <v>4280034.8981900001</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A18" s="48" t="s">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A18" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="B18" s="48"/>
+      <c r="B18" s="47"/>
       <c r="C18" s="30">
-        <f>C4*35.3%</f>
+        <f t="shared" ref="C18:V18" si="4">C4*35.3%</f>
         <v>272521.32676999999</v>
       </c>
       <c r="D18" s="30">
-        <f>D4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>300764.26725999994</v>
       </c>
       <c r="E18" s="30">
-        <f>E4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>272521.32676999999</v>
       </c>
       <c r="F18" s="30">
-        <f>F4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>190659.92782999997</v>
       </c>
       <c r="G18" s="30">
-        <f>G4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>162425.63583999997</v>
       </c>
       <c r="H18" s="30">
-        <f>H4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>189847.46656</v>
       </c>
       <c r="I18" s="30">
-        <f>I4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>156602.22308</v>
       </c>
       <c r="J18" s="30">
-        <f>J4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>184277.09125999999</v>
       </c>
       <c r="K18" s="30">
-        <f>K4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>72183.099100000007</v>
       </c>
       <c r="L18" s="30">
-        <f>L4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>72186.03959</v>
       </c>
       <c r="M18" s="30">
-        <f>M4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>72183.099100000007</v>
       </c>
       <c r="N18" s="30">
-        <f>N4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>72186.03959</v>
       </c>
       <c r="O18" s="30">
-        <f>O4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>71236.091879999993</v>
       </c>
       <c r="P18" s="30">
-        <f>P4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>71239.046489999993</v>
       </c>
       <c r="Q18" s="30">
-        <f>Q4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>30055.687269999999</v>
       </c>
       <c r="R18" s="30">
-        <f>R4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>30055.687269999999</v>
       </c>
       <c r="S18" s="30">
-        <f>S4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>29182.326440000001</v>
       </c>
       <c r="T18" s="30">
-        <f>T4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>28346.496569999999</v>
       </c>
       <c r="U18" s="30">
-        <f>U4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>28346.496569999999</v>
       </c>
       <c r="V18" s="30">
-        <f>V4*35.3%</f>
+        <f t="shared" si="4"/>
         <v>28346.496569999999</v>
       </c>
       <c r="W18" s="30">
-        <f>SUM(C18:V18)</f>
+        <f t="shared" si="0"/>
         <v>2335165.8718099995</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="33" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="41">
-        <f>C18-C15</f>
-        <v>155561.30676999997</v>
-      </c>
-      <c r="D19" s="41">
-        <f t="shared" ref="D19:V19" si="0">D18-D15</f>
-        <v>103795.91725999993</v>
-      </c>
-      <c r="E19" s="41">
+    <row r="19" spans="1:53" s="33" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="41"/>
+    </row>
+    <row r="20" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="30">
+        <f>SUM(C7:C11,C5,C13)</f>
+        <v>116960.02</v>
+      </c>
+      <c r="D20" s="30">
+        <f t="shared" ref="D20:V20" si="5">SUM(D7:D11,D5,D13)</f>
+        <v>196968.35</v>
+      </c>
+      <c r="E20" s="30">
+        <f t="shared" si="5"/>
+        <v>116960.02</v>
+      </c>
+      <c r="F20" s="30">
+        <f t="shared" si="5"/>
+        <v>196968.35</v>
+      </c>
+      <c r="G20" s="30">
+        <f t="shared" si="5"/>
+        <v>116960.02</v>
+      </c>
+      <c r="H20" s="30">
+        <f t="shared" si="5"/>
+        <v>196968.35</v>
+      </c>
+      <c r="I20" s="30">
+        <f t="shared" si="5"/>
+        <v>116960.02</v>
+      </c>
+      <c r="J20" s="30">
+        <f t="shared" si="5"/>
+        <v>196968.35</v>
+      </c>
+      <c r="K20" s="30">
+        <f t="shared" si="5"/>
+        <v>196960.02000000002</v>
+      </c>
+      <c r="L20" s="30">
+        <f t="shared" si="5"/>
+        <v>196968.35</v>
+      </c>
+      <c r="M20" s="30">
+        <f t="shared" si="5"/>
+        <v>196960.02000000002</v>
+      </c>
+      <c r="N20" s="30">
+        <f t="shared" si="5"/>
+        <v>196968.35</v>
+      </c>
+      <c r="O20" s="30">
+        <f t="shared" si="5"/>
+        <v>196960.06</v>
+      </c>
+      <c r="P20" s="30">
+        <f t="shared" si="5"/>
+        <v>196968.43</v>
+      </c>
+      <c r="Q20" s="30">
+        <f t="shared" si="5"/>
+        <v>80301.69</v>
+      </c>
+      <c r="R20" s="30">
+        <f t="shared" si="5"/>
+        <v>80301.69</v>
+      </c>
+      <c r="S20" s="30">
+        <f t="shared" si="5"/>
+        <v>80301.69</v>
+      </c>
+      <c r="T20" s="30">
+        <f t="shared" si="5"/>
+        <v>80301.69</v>
+      </c>
+      <c r="U20" s="30">
+        <f t="shared" si="5"/>
+        <v>80301.69</v>
+      </c>
+      <c r="V20" s="30">
+        <f t="shared" si="5"/>
+        <v>80301.69</v>
+      </c>
+      <c r="W20" s="30">
         <f t="shared" si="0"/>
-        <v>155561.30676999997</v>
-      </c>
-      <c r="F19" s="41">
-        <f t="shared" si="0"/>
-        <v>-6308.4221700000344</v>
-      </c>
-      <c r="G19" s="41">
-        <f t="shared" si="0"/>
-        <v>45465.615839999969</v>
-      </c>
-      <c r="H19" s="41">
-        <f t="shared" si="0"/>
-        <v>-7120.8834400000051</v>
-      </c>
-      <c r="I19" s="41">
-        <f t="shared" si="0"/>
-        <v>39642.203079999992</v>
-      </c>
-      <c r="J19" s="41">
-        <f t="shared" si="0"/>
-        <v>-12691.258740000019</v>
-      </c>
-      <c r="K19" s="41">
-        <f t="shared" si="0"/>
-        <v>-124776.92090000001</v>
-      </c>
-      <c r="L19" s="41">
-        <f t="shared" si="0"/>
-        <v>-124782.31041000001</v>
-      </c>
-      <c r="M19" s="41">
-        <f t="shared" si="0"/>
-        <v>-124776.92090000001</v>
-      </c>
-      <c r="N19" s="41">
-        <f t="shared" si="0"/>
-        <v>-124782.31041000001</v>
-      </c>
-      <c r="O19" s="41">
-        <f t="shared" si="0"/>
-        <v>-125723.96812000001</v>
-      </c>
-      <c r="P19" s="41">
-        <f t="shared" si="0"/>
-        <v>-125729.38351</v>
-      </c>
-      <c r="Q19" s="41">
-        <f t="shared" si="0"/>
-        <v>-50246.002730000007</v>
-      </c>
-      <c r="R19" s="41">
-        <f t="shared" si="0"/>
-        <v>-50246.002730000007</v>
-      </c>
-      <c r="S19" s="41">
-        <f t="shared" si="0"/>
-        <v>-51119.363559999998</v>
-      </c>
-      <c r="T19" s="41">
-        <f t="shared" si="0"/>
-        <v>-51955.193429999999</v>
-      </c>
-      <c r="U19" s="41">
-        <f t="shared" si="0"/>
-        <v>-51955.193429999999</v>
-      </c>
-      <c r="V19" s="41">
-        <f t="shared" si="0"/>
-        <v>-51955.193429999999</v>
+        <v>2919308.85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:53" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="102" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="102"/>
+      <c r="C27" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="102" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A28" s="102"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="103">
+        <v>46230</v>
+      </c>
+      <c r="E28" s="75">
+        <f>'Fluxo de pagamentos'!AI2</f>
+        <v>46935</v>
+      </c>
+      <c r="F28" s="104">
+        <f>'Fluxo de pagamentos'!AU2</f>
+        <v>47300</v>
+      </c>
+      <c r="G28" s="104">
+        <f>'Fluxo de pagamentos'!BG2</f>
+        <v>47665</v>
+      </c>
+      <c r="H28" s="102"/>
+    </row>
+    <row r="29" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A29" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="39"/>
+      <c r="C29" s="97">
+        <f>'Fluxo de pagamentos'!J7</f>
+        <v>4959000</v>
+      </c>
+      <c r="D29" s="40">
+        <f>'Fluxo de pagamentos'!K7</f>
+        <v>3000000</v>
+      </c>
+      <c r="E29" s="40">
+        <f>'Fluxo de pagamentos'!AI7</f>
+        <v>653000</v>
+      </c>
+      <c r="F29" s="40">
+        <f>'Fluxo de pagamentos'!AU7</f>
+        <v>653000</v>
+      </c>
+      <c r="G29" s="40">
+        <f>'Fluxo de pagamentos'!BG7</f>
+        <v>653000</v>
+      </c>
+      <c r="H29" s="40">
+        <f>SUM(D29:G29)</f>
+        <v>4959000</v>
+      </c>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
+      <c r="AB29" s="29"/>
+      <c r="AC29" s="29"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="29"/>
+      <c r="AF29" s="29"/>
+      <c r="AG29" s="29"/>
+      <c r="AH29" s="29"/>
+      <c r="AI29" s="29"/>
+      <c r="AJ29" s="29"/>
+      <c r="AK29" s="29"/>
+      <c r="AL29" s="29"/>
+      <c r="AM29" s="29"/>
+      <c r="AN29" s="29"/>
+      <c r="AO29" s="29"/>
+      <c r="AP29" s="29"/>
+      <c r="AQ29" s="29"/>
+      <c r="AR29" s="29"/>
+      <c r="AS29" s="29"/>
+      <c r="AT29" s="29"/>
+      <c r="AU29" s="29"/>
+      <c r="AV29" s="29"/>
+      <c r="AW29" s="29"/>
+      <c r="AX29" s="29"/>
+      <c r="AY29" s="29"/>
+      <c r="AZ29" s="29"/>
+      <c r="BA29" s="30"/>
+    </row>
+    <row r="30" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A30" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="97">
+        <f>C29*64.7%</f>
+        <v>3208473</v>
+      </c>
+      <c r="D30" s="97">
+        <f>D29*64.7%</f>
+        <v>1941000</v>
+      </c>
+      <c r="E30" s="97">
+        <f>E29*64.7%</f>
+        <v>422491</v>
+      </c>
+      <c r="F30" s="97">
+        <f>F29*64.7%</f>
+        <v>422491</v>
+      </c>
+      <c r="G30" s="97">
+        <f>G29*64.7%</f>
+        <v>422491</v>
+      </c>
+      <c r="H30" s="40">
+        <f t="shared" ref="H30:H31" si="6">SUM(D30:G30)</f>
+        <v>3208473</v>
+      </c>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
+      <c r="AG30" s="30"/>
+      <c r="AH30" s="30"/>
+      <c r="AI30" s="30"/>
+      <c r="AJ30" s="30"/>
+      <c r="AK30" s="30"/>
+      <c r="AL30" s="30"/>
+      <c r="AM30" s="30"/>
+      <c r="AN30" s="30"/>
+      <c r="AO30" s="30"/>
+      <c r="AP30" s="30"/>
+      <c r="AQ30" s="30"/>
+      <c r="AR30" s="30"/>
+      <c r="AS30" s="30"/>
+      <c r="AT30" s="30"/>
+      <c r="AU30" s="30"/>
+      <c r="AV30" s="30"/>
+      <c r="AW30" s="30"/>
+      <c r="AX30" s="30"/>
+      <c r="AY30" s="30"/>
+      <c r="AZ30" s="30"/>
+      <c r="BA30" s="30"/>
+    </row>
+    <row r="31" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A31" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="97">
+        <f>C29*35.3%</f>
+        <v>1750527</v>
+      </c>
+      <c r="D31" s="97">
+        <f>D29*35.3%</f>
+        <v>1059000</v>
+      </c>
+      <c r="E31" s="97">
+        <f>E29*35.3%</f>
+        <v>230509</v>
+      </c>
+      <c r="F31" s="97">
+        <f>F29*35.3%</f>
+        <v>230509</v>
+      </c>
+      <c r="G31" s="97">
+        <f>G29*35.3%</f>
+        <v>230509</v>
+      </c>
+      <c r="H31" s="40">
+        <f t="shared" si="6"/>
+        <v>1750527</v>
+      </c>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="30"/>
+      <c r="AD31" s="30"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="30"/>
+      <c r="AG31" s="30"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="30"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="30"/>
+      <c r="AM31" s="30"/>
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="30"/>
+      <c r="AP31" s="30"/>
+      <c r="AQ31" s="30"/>
+      <c r="AR31" s="30"/>
+      <c r="AS31" s="30"/>
+      <c r="AT31" s="30"/>
+      <c r="AU31" s="30"/>
+      <c r="AV31" s="30"/>
+      <c r="AW31" s="30"/>
+      <c r="AX31" s="30"/>
+      <c r="AY31" s="30"/>
+      <c r="AZ31" s="30"/>
+      <c r="BA31" s="30"/>
+    </row>
+    <row r="34" spans="3:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="100" t="s">
+        <v>183</v>
+      </c>
+      <c r="D34" s="100"/>
+      <c r="F34" s="100" t="s">
+        <v>184</v>
+      </c>
+      <c r="G34" s="100"/>
+    </row>
+    <row r="35" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C35" s="101" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="101" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" s="101" t="s">
+        <v>104</v>
+      </c>
+      <c r="G35" s="101" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C36" s="75">
+        <v>46295</v>
+      </c>
+      <c r="D36" s="97">
+        <f>C17</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="F36" s="75">
+        <v>46295</v>
+      </c>
+      <c r="G36" s="97">
+        <f>C18</f>
+        <v>272521.32676999999</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C37" s="75">
+        <v>46326</v>
+      </c>
+      <c r="D37" s="97">
+        <f>D17</f>
+        <v>551259.15273999993</v>
+      </c>
+      <c r="F37" s="75">
+        <v>46326</v>
+      </c>
+      <c r="G37" s="97">
+        <f>D18</f>
+        <v>300764.26725999994</v>
+      </c>
+    </row>
+    <row r="38" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C38" s="75">
+        <v>46356</v>
+      </c>
+      <c r="D38" s="97">
+        <f>E17</f>
+        <v>499493.76322999998</v>
+      </c>
+      <c r="F38" s="75">
+        <v>46356</v>
+      </c>
+      <c r="G38" s="97">
+        <f>E18</f>
+        <v>272521.32676999999</v>
+      </c>
+    </row>
+    <row r="39" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C39" s="75">
+        <v>46387</v>
+      </c>
+      <c r="D39" s="97">
+        <f>F17</f>
+        <v>349453.18216999999</v>
+      </c>
+      <c r="F39" s="75">
+        <v>46387</v>
+      </c>
+      <c r="G39" s="97">
+        <f>F18</f>
+        <v>190659.92782999997</v>
+      </c>
+    </row>
+    <row r="40" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C40" s="75">
+        <v>46418</v>
+      </c>
+      <c r="D40" s="97">
+        <f>G17</f>
+        <v>297703.64415999997</v>
+      </c>
+      <c r="F40" s="75">
+        <v>46418</v>
+      </c>
+      <c r="G40" s="97">
+        <f>G18</f>
+        <v>162425.63583999997</v>
+      </c>
+    </row>
+    <row r="41" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C41" s="75">
+        <v>46446</v>
+      </c>
+      <c r="D41" s="97">
+        <f>H17</f>
+        <v>347964.05344000005</v>
+      </c>
+      <c r="F41" s="75">
+        <v>46446</v>
+      </c>
+      <c r="G41" s="97">
+        <f>H18</f>
+        <v>189847.46656</v>
+      </c>
+    </row>
+    <row r="42" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C42" s="75">
+        <v>46477</v>
+      </c>
+      <c r="D42" s="97">
+        <f>I17</f>
+        <v>287030.13692000002</v>
+      </c>
+      <c r="F42" s="75">
+        <v>46477</v>
+      </c>
+      <c r="G42" s="97">
+        <f>I18</f>
+        <v>156602.22308</v>
+      </c>
+    </row>
+    <row r="43" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C43" s="75">
+        <v>46507</v>
+      </c>
+      <c r="D43" s="97">
+        <f>J17</f>
+        <v>337754.32874000003</v>
+      </c>
+      <c r="F43" s="75">
+        <v>46507</v>
+      </c>
+      <c r="G43" s="97">
+        <f>J18</f>
+        <v>184277.09125999999</v>
+      </c>
+    </row>
+    <row r="44" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C44" s="75">
+        <v>46538</v>
+      </c>
+      <c r="D44" s="97">
+        <f>K17</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="F44" s="75">
+        <v>46538</v>
+      </c>
+      <c r="G44" s="97">
+        <f>K18</f>
+        <v>72183.099100000007</v>
+      </c>
+    </row>
+    <row r="45" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C45" s="75">
+        <v>46568</v>
+      </c>
+      <c r="D45" s="97">
+        <f>L17</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="F45" s="75">
+        <v>46568</v>
+      </c>
+      <c r="G45" s="97">
+        <f>L18</f>
+        <v>72186.03959</v>
+      </c>
+    </row>
+    <row r="46" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C46" s="75">
+        <v>46599</v>
+      </c>
+      <c r="D46" s="97">
+        <f>M17</f>
+        <v>132301.60090000002</v>
+      </c>
+      <c r="F46" s="75">
+        <v>46599</v>
+      </c>
+      <c r="G46" s="97">
+        <f>M18</f>
+        <v>72183.099100000007</v>
+      </c>
+    </row>
+    <row r="47" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C47" s="75">
+        <v>46630</v>
+      </c>
+      <c r="D47" s="97">
+        <f>N17</f>
+        <v>132306.99041</v>
+      </c>
+      <c r="F47" s="75">
+        <v>46630</v>
+      </c>
+      <c r="G47" s="97">
+        <f>N18</f>
+        <v>72186.03959</v>
+      </c>
+    </row>
+    <row r="48" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C48" s="75">
+        <v>46660</v>
+      </c>
+      <c r="D48" s="97">
+        <f>O17</f>
+        <v>130565.86812</v>
+      </c>
+      <c r="F48" s="75">
+        <v>46660</v>
+      </c>
+      <c r="G48" s="97">
+        <f>O18</f>
+        <v>71236.091879999993</v>
+      </c>
+    </row>
+    <row r="49" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C49" s="75">
+        <v>46691</v>
+      </c>
+      <c r="D49" s="97">
+        <f>P17</f>
+        <v>130571.28350999999</v>
+      </c>
+      <c r="F49" s="75">
+        <v>46691</v>
+      </c>
+      <c r="G49" s="97">
+        <f>P18</f>
+        <v>71239.046489999993</v>
+      </c>
+    </row>
+    <row r="50" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C50" s="75">
+        <v>46721</v>
+      </c>
+      <c r="D50" s="97">
+        <f>Q17</f>
+        <v>55087.902730000002</v>
+      </c>
+      <c r="F50" s="75">
+        <v>46721</v>
+      </c>
+      <c r="G50" s="97">
+        <f>Q18</f>
+        <v>30055.687269999999</v>
+      </c>
+    </row>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C51" s="75">
+        <v>46752</v>
+      </c>
+      <c r="D51" s="97">
+        <f>R17</f>
+        <v>55087.902730000002</v>
+      </c>
+      <c r="F51" s="75">
+        <v>46752</v>
+      </c>
+      <c r="G51" s="97">
+        <f>R18</f>
+        <v>30055.687269999999</v>
+      </c>
+    </row>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C52" s="75">
+        <v>46783</v>
+      </c>
+      <c r="D52" s="97">
+        <f>S17</f>
+        <v>53487.153560000006</v>
+      </c>
+      <c r="F52" s="75">
+        <v>46783</v>
+      </c>
+      <c r="G52" s="97">
+        <f>S18</f>
+        <v>29182.326440000001</v>
+      </c>
+    </row>
+    <row r="53" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C53" s="75">
+        <v>46812</v>
+      </c>
+      <c r="D53" s="97">
+        <f>T17</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="F53" s="75">
+        <v>46812</v>
+      </c>
+      <c r="G53" s="97">
+        <f>T18</f>
+        <v>28346.496569999999</v>
+      </c>
+    </row>
+    <row r="54" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C54" s="75">
+        <v>46843</v>
+      </c>
+      <c r="D54" s="97">
+        <f>U17</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="F54" s="75">
+        <v>46843</v>
+      </c>
+      <c r="G54" s="97">
+        <f>U18</f>
+        <v>28346.496569999999</v>
+      </c>
+    </row>
+    <row r="55" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C55" s="75">
+        <v>46873</v>
+      </c>
+      <c r="D55" s="97">
+        <f>V17</f>
+        <v>51955.193430000007</v>
+      </c>
+      <c r="F55" s="75">
+        <v>46873</v>
+      </c>
+      <c r="G55" s="97">
+        <f>V18</f>
+        <v>28346.496569999999</v>
+      </c>
+    </row>
+    <row r="56" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C56" s="93" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56" s="97">
+        <f>SUM(D36:D55)</f>
+        <v>4280034.8981900001</v>
+      </c>
+      <c r="F56" s="93" t="s">
+        <v>74</v>
+      </c>
+      <c r="G56" s="97">
+        <f>SUM(G36:G55)</f>
+        <v>2335165.8718099995</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="11">
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="W2:W3"/>
@@ -13319,10 +16049,1220 @@
     <mergeCell ref="A2:B3"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2819EE-B1D7-CF43-B118-590F97033B56}">
+  <dimension ref="A2:B24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="60"/>
+    </row>
+    <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="56">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="88" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="88"/>
+    </row>
+    <row r="15" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="87" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="86"/>
+    </row>
+    <row r="16" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="85">
+        <v>46326</v>
+      </c>
+      <c r="B16" s="86"/>
+    </row>
+    <row r="17" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="81">
+        <v>46418</v>
+      </c>
+      <c r="B17" s="86"/>
+    </row>
+    <row r="18" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="81">
+        <v>46507</v>
+      </c>
+      <c r="B18" s="86"/>
+    </row>
+    <row r="19" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="81">
+        <v>46599</v>
+      </c>
+      <c r="B19" s="86"/>
+    </row>
+    <row r="20" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="81">
+        <v>46965</v>
+      </c>
+      <c r="B20" s="86"/>
+    </row>
+    <row r="21" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="81">
+        <v>47330</v>
+      </c>
+      <c r="B21" s="86"/>
+    </row>
+    <row r="22" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="81">
+        <v>47695</v>
+      </c>
+      <c r="B22" s="86"/>
+    </row>
+    <row r="23" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B15:B22"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5139F6C-08F6-C743-9097-9CE0AB900249}">
+  <dimension ref="A2:B24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="60"/>
+    </row>
+    <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="56">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="88" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="88"/>
+    </row>
+    <row r="15" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="87" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="86"/>
+    </row>
+    <row r="16" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="85">
+        <v>46326</v>
+      </c>
+      <c r="B16" s="86"/>
+    </row>
+    <row r="17" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="81">
+        <v>46418</v>
+      </c>
+      <c r="B17" s="86"/>
+    </row>
+    <row r="18" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="81">
+        <v>46507</v>
+      </c>
+      <c r="B18" s="86"/>
+    </row>
+    <row r="19" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="81">
+        <v>46599</v>
+      </c>
+      <c r="B19" s="86"/>
+    </row>
+    <row r="20" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="81">
+        <v>46965</v>
+      </c>
+      <c r="B20" s="86"/>
+    </row>
+    <row r="21" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="81">
+        <v>47330</v>
+      </c>
+      <c r="B21" s="86"/>
+    </row>
+    <row r="22" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="81">
+        <v>47695</v>
+      </c>
+      <c r="B22" s="86"/>
+    </row>
+    <row r="23" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B15:B22"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7261C320-A372-0547-92C1-2CB5E56FC242}">
+  <dimension ref="A2:E26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.1640625" customWidth="1"/>
+    <col min="4" max="4" width="49.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+    </row>
+    <row r="3" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+    </row>
+    <row r="4" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="69"/>
+    </row>
+    <row r="5" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="72"/>
+    </row>
+    <row r="6" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="68"/>
+      <c r="D6" s="69"/>
+    </row>
+    <row r="7" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="68"/>
+      <c r="D7" s="69"/>
+    </row>
+    <row r="8" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="67">
+        <v>141</v>
+      </c>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+    </row>
+    <row r="9" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="83"/>
+      <c r="D9" s="84"/>
+    </row>
+    <row r="10" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="68"/>
+      <c r="D10" s="69"/>
+    </row>
+    <row r="11" spans="1:5" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="68"/>
+      <c r="D11" s="69"/>
+    </row>
+    <row r="12" spans="1:5" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="68"/>
+      <c r="D12" s="69"/>
+    </row>
+    <row r="13" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="105"/>
+    </row>
+    <row r="14" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="106"/>
+      <c r="E14" s="62"/>
+    </row>
+    <row r="15" spans="1:5" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="81">
+        <v>46244</v>
+      </c>
+      <c r="B15" s="45">
+        <v>46265</v>
+      </c>
+      <c r="C15" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D15" s="106"/>
+      <c r="E15" s="80"/>
+    </row>
+    <row r="16" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="81">
+        <v>46275</v>
+      </c>
+      <c r="B16" s="45">
+        <v>46295</v>
+      </c>
+      <c r="C16" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D16" s="106"/>
+      <c r="E16" s="80"/>
+    </row>
+    <row r="17" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="81">
+        <v>46305</v>
+      </c>
+      <c r="B17" s="45">
+        <v>46326</v>
+      </c>
+      <c r="C17" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D17" s="106"/>
+      <c r="E17" s="80"/>
+    </row>
+    <row r="18" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="81">
+        <v>46336</v>
+      </c>
+      <c r="B18" s="45">
+        <v>46356</v>
+      </c>
+      <c r="C18" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D18" s="106"/>
+      <c r="E18" s="80"/>
+    </row>
+    <row r="19" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="81">
+        <v>46366</v>
+      </c>
+      <c r="B19" s="45">
+        <v>46387</v>
+      </c>
+      <c r="C19" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D19" s="106"/>
+      <c r="E19" s="80"/>
+    </row>
+    <row r="20" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="81">
+        <v>46397</v>
+      </c>
+      <c r="B20" s="45">
+        <v>46418</v>
+      </c>
+      <c r="C20" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D20" s="106"/>
+      <c r="E20" s="80"/>
+    </row>
+    <row r="21" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="81">
+        <v>46428</v>
+      </c>
+      <c r="B21" s="45">
+        <v>46446</v>
+      </c>
+      <c r="C21" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D21" s="106"/>
+      <c r="E21" s="80"/>
+    </row>
+    <row r="22" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="81">
+        <v>46456</v>
+      </c>
+      <c r="B22" s="45">
+        <v>46477</v>
+      </c>
+      <c r="C22" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D22" s="106"/>
+      <c r="E22" s="80"/>
+    </row>
+    <row r="23" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="81">
+        <v>46487</v>
+      </c>
+      <c r="B23" s="45">
+        <v>46507</v>
+      </c>
+      <c r="C23" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D23" s="106"/>
+      <c r="E23" s="80"/>
+    </row>
+    <row r="24" spans="1:5" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="81">
+        <v>46517</v>
+      </c>
+      <c r="B24" s="45">
+        <v>46538</v>
+      </c>
+      <c r="C24" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D24" s="106"/>
+      <c r="E24" s="80"/>
+    </row>
+    <row r="25" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="81">
+        <v>46548</v>
+      </c>
+      <c r="B25" s="45">
+        <v>46568</v>
+      </c>
+      <c r="C25" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D25" s="106"/>
+      <c r="E25" s="80"/>
+    </row>
+    <row r="26" spans="1:5" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="81">
+        <v>46578</v>
+      </c>
+      <c r="B26" s="45">
+        <v>46599</v>
+      </c>
+      <c r="C26" s="79">
+        <v>270220</v>
+      </c>
+      <c r="D26" s="106"/>
+      <c r="E26" s="80"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:D26"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3028D04-198A-4A4F-A542-E99883417EBD}">
+  <dimension ref="A2:E27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.1640625" customWidth="1"/>
+    <col min="4" max="4" width="48.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+    </row>
+    <row r="3" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+    </row>
+    <row r="4" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="69"/>
+    </row>
+    <row r="5" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="70" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="72"/>
+    </row>
+    <row r="6" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="68"/>
+      <c r="D6" s="69"/>
+    </row>
+    <row r="7" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="68"/>
+      <c r="D7" s="69"/>
+    </row>
+    <row r="8" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="67">
+        <v>141</v>
+      </c>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+    </row>
+    <row r="9" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="83"/>
+      <c r="D9" s="84"/>
+    </row>
+    <row r="10" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="68"/>
+      <c r="D10" s="69"/>
+    </row>
+    <row r="11" spans="1:5" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="68"/>
+      <c r="D11" s="69"/>
+    </row>
+    <row r="12" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="68"/>
+      <c r="D12" s="69"/>
+    </row>
+    <row r="13" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+    </row>
+    <row r="14" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="77"/>
+    </row>
+    <row r="15" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="76"/>
+      <c r="E15" s="62"/>
+    </row>
+    <row r="16" spans="1:5" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="81">
+        <v>46244</v>
+      </c>
+      <c r="B16" s="45">
+        <v>46265</v>
+      </c>
+      <c r="C16" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D16" s="76"/>
+      <c r="E16" s="80"/>
+    </row>
+    <row r="17" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="81">
+        <v>46275</v>
+      </c>
+      <c r="B17" s="45">
+        <v>46295</v>
+      </c>
+      <c r="C17" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D17" s="76"/>
+      <c r="E17" s="80"/>
+    </row>
+    <row r="18" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="81">
+        <v>46305</v>
+      </c>
+      <c r="B18" s="45">
+        <v>46326</v>
+      </c>
+      <c r="C18" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D18" s="76"/>
+      <c r="E18" s="80"/>
+    </row>
+    <row r="19" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="81">
+        <v>46336</v>
+      </c>
+      <c r="B19" s="45">
+        <v>46356</v>
+      </c>
+      <c r="C19" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D19" s="76"/>
+      <c r="E19" s="80"/>
+    </row>
+    <row r="20" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="81">
+        <v>46366</v>
+      </c>
+      <c r="B20" s="45">
+        <v>46387</v>
+      </c>
+      <c r="C20" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D20" s="76"/>
+      <c r="E20" s="80"/>
+    </row>
+    <row r="21" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="81">
+        <v>46397</v>
+      </c>
+      <c r="B21" s="45">
+        <v>46418</v>
+      </c>
+      <c r="C21" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D21" s="76"/>
+      <c r="E21" s="80"/>
+    </row>
+    <row r="22" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="81">
+        <v>46428</v>
+      </c>
+      <c r="B22" s="45">
+        <v>46446</v>
+      </c>
+      <c r="C22" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D22" s="76"/>
+      <c r="E22" s="80"/>
+    </row>
+    <row r="23" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="81">
+        <v>46456</v>
+      </c>
+      <c r="B23" s="45">
+        <v>46477</v>
+      </c>
+      <c r="C23" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D23" s="76"/>
+      <c r="E23" s="80"/>
+    </row>
+    <row r="24" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="81">
+        <v>46487</v>
+      </c>
+      <c r="B24" s="45">
+        <v>46507</v>
+      </c>
+      <c r="C24" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D24" s="76"/>
+      <c r="E24" s="80"/>
+    </row>
+    <row r="25" spans="1:5" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="81">
+        <v>46517</v>
+      </c>
+      <c r="B25" s="45">
+        <v>46538</v>
+      </c>
+      <c r="C25" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="80"/>
+    </row>
+    <row r="26" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="81">
+        <v>46548</v>
+      </c>
+      <c r="B26" s="45">
+        <v>46568</v>
+      </c>
+      <c r="C26" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D26" s="76"/>
+      <c r="E26" s="80"/>
+    </row>
+    <row r="27" spans="1:5" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="81">
+        <v>46578</v>
+      </c>
+      <c r="B27" s="45">
+        <v>46599</v>
+      </c>
+      <c r="C27" s="79">
+        <v>936585</v>
+      </c>
+      <c r="D27" s="76"/>
+      <c r="E27" s="80"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:D27"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0159473-6E36-314A-B2B9-46824FB666CF}">
+  <dimension ref="A2:B24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="60"/>
+    </row>
+    <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="54">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="56">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="55">
+        <v>21432792.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D46A44-B432-0A4F-92D4-CF2493D6E153}">
+  <dimension ref="A2:B24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="60"/>
+    </row>
+    <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="54">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="56">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="55">
+        <v>28762281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8f7f4e79-e3ee-400b-8307-611f30480393" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009BCAD43DEBE5F94985BAF5880255A369" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2fb35b598400d5f193579b3bf1feff08">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5a6c962e-89a5-491f-bc13-c4fa6b6d71f2" xmlns:ns4="8f7f4e79-e3ee-400b-8307-611f30480393" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8bbe51196fddd356df0d3ff3527ead97" ns3:_="" ns4:_="">
     <xsd:import namespace="5a6c962e-89a5-491f-bc13-c4fa6b6d71f2"/>
@@ -13567,24 +17507,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{408326D6-065C-406F-8763-8F7641131D26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="5a6c962e-89a5-491f-bc13-c4fa6b6d71f2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8f7f4e79-e3ee-400b-8307-611f30480393"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8f7f4e79-e3ee-400b-8307-611f30480393" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4ACE698-005D-404B-9AED-9E97E91093BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9842BADD-DE89-47D9-B611-88F6E4A2D1F9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13603,31 +17551,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4ACE698-005D-404B-9AED-9E97E91093BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{408326D6-065C-406F-8763-8F7641131D26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="5a6c962e-89a5-491f-bc13-c4fa6b6d71f2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8f7f4e79-e3ee-400b-8307-611f30480393"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4ba98965-3a24-460d-b0e1-6f272f1d0f46}" enabled="1" method="Privileged" siteId="{85b28421-d45a-4b07-889d-24b528c7f250}" removed="0"/>

--- a/Anexo Fluxo de Pagamento Nio x Onitel.xlsx
+++ b/Anexo Fluxo de Pagamento Nio x Onitel.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/silvio/Library/CloudStorage/GoogleDrive-eucastrosilvio@gmail.com/Meu Drive/1A Grupo Tigon Drive/Grupo Tigon Estratégico/Vtal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D28D786-65CD-4A4E-9BEA-D6DD5A88C735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787515AB-015D-9C41-B1F9-ECA739098C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="580" windowWidth="23840" windowHeight="15120" activeTab="2" xr2:uid="{64F40452-A3D8-4C49-BFF5-9F85CDF9315C}"/>
+    <workbookView xWindow="1760" yWindow="580" windowWidth="23840" windowHeight="15120" activeTab="1" xr2:uid="{64F40452-A3D8-4C49-BFF5-9F85CDF9315C}"/>
   </bookViews>
   <sheets>
     <sheet name="Fluxo de pagamentos" sheetId="5" r:id="rId1"/>
-    <sheet name="Resumo Fluxo de Pagamentos" sheetId="6" r:id="rId2"/>
+    <sheet name="Resumo Fluxo de Pagamentos" sheetId="23" r:id="rId2"/>
     <sheet name="Escrow e IT Serviços" sheetId="7" r:id="rId3"/>
     <sheet name="Variação Monetária Telecom" sheetId="19" r:id="rId4"/>
     <sheet name="Variação Monetária Serviços" sheetId="18" r:id="rId5"/>
@@ -757,7 +757,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -779,6 +779,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -926,7 +932,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1015,21 +1021,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1051,16 +1042,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1068,6 +1050,111 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1078,75 +1165,20 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1154,43 +1186,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="43" fontId="0" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="43" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -7186,258 +7207,244 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
     </row>
     <row r="3" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="66"/>
+      <c r="C3" s="95"/>
     </row>
     <row r="4" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="69"/>
+      <c r="C4" s="83"/>
     </row>
     <row r="5" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="70">
+      <c r="B5" s="87">
         <v>46230</v>
       </c>
-      <c r="C5" s="72"/>
+      <c r="C5" s="89"/>
     </row>
     <row r="6" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="69"/>
+      <c r="C6" s="83"/>
     </row>
     <row r="7" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="69"/>
+      <c r="C7" s="83"/>
     </row>
     <row r="8" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="67">
+      <c r="B8" s="81">
         <v>141</v>
       </c>
-      <c r="C8" s="69"/>
+      <c r="C8" s="83"/>
     </row>
     <row r="9" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="82">
+      <c r="B9" s="90">
         <v>1059000</v>
       </c>
-      <c r="C9" s="84"/>
+      <c r="C9" s="92"/>
     </row>
     <row r="10" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="69"/>
+      <c r="C10" s="83"/>
     </row>
     <row r="11" spans="1:3" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="69"/>
+      <c r="C11" s="83"/>
     </row>
     <row r="12" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="C12" s="69"/>
+      <c r="C12" s="83"/>
     </row>
     <row r="14" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
     </row>
     <row r="15" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="66"/>
+      <c r="C15" s="95"/>
     </row>
     <row r="16" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="69"/>
+      <c r="C16" s="83"/>
     </row>
     <row r="17" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="70">
+      <c r="B17" s="87">
         <v>46240</v>
       </c>
-      <c r="C17" s="72"/>
+      <c r="C17" s="89"/>
     </row>
     <row r="18" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="69"/>
+      <c r="C18" s="83"/>
     </row>
     <row r="19" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="69"/>
+      <c r="C19" s="83"/>
     </row>
     <row r="20" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="67">
+      <c r="B20" s="81">
         <v>1431</v>
       </c>
-      <c r="C20" s="69"/>
+      <c r="C20" s="83"/>
     </row>
     <row r="21" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="52" t="s">
+      <c r="A21" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="82">
+      <c r="B21" s="90">
         <v>1059000</v>
       </c>
-      <c r="C21" s="84"/>
+      <c r="C21" s="92"/>
     </row>
     <row r="22" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="69"/>
+      <c r="C22" s="83"/>
     </row>
     <row r="23" spans="1:3" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="69"/>
+      <c r="C23" s="83"/>
     </row>
     <row r="24" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="69"/>
+      <c r="C24" s="83"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="94" t="s">
+      <c r="A25" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="95"/>
-      <c r="C25" s="96"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="100"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="63" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="90" t="s">
+      <c r="B26" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="91"/>
+      <c r="C26" s="101"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="75">
+      <c r="A27" s="57">
         <v>46965</v>
       </c>
       <c r="B27" s="40">
         <v>230509</v>
       </c>
-      <c r="C27" s="92"/>
+      <c r="C27" s="102"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="75">
+      <c r="A28" s="57">
         <v>47330</v>
       </c>
       <c r="B28" s="40">
         <v>230509</v>
       </c>
-      <c r="C28" s="92"/>
+      <c r="C28" s="102"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="75">
+      <c r="A29" s="57">
         <v>47695</v>
       </c>
       <c r="B29" s="40">
         <v>230509</v>
       </c>
-      <c r="C29" s="92"/>
+      <c r="C29" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="B23:C23"/>
@@ -7448,6 +7455,20 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7466,342 +7487,348 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
     </row>
     <row r="3" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="66"/>
+      <c r="C3" s="95"/>
     </row>
     <row r="4" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="69"/>
+      <c r="C4" s="83"/>
     </row>
     <row r="5" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="87" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="72"/>
+      <c r="C5" s="89"/>
     </row>
     <row r="6" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="69"/>
+      <c r="C6" s="83"/>
     </row>
     <row r="7" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="69"/>
+      <c r="C7" s="83"/>
     </row>
     <row r="8" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="67">
+      <c r="B8" s="81">
         <v>141</v>
       </c>
-      <c r="C8" s="69"/>
+      <c r="C8" s="83"/>
     </row>
     <row r="9" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="90" t="s">
         <v>171</v>
       </c>
-      <c r="C9" s="84"/>
+      <c r="C9" s="92"/>
     </row>
     <row r="10" spans="1:7" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="69"/>
+      <c r="C10" s="83"/>
     </row>
     <row r="11" spans="1:7" s="33" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="81" t="s">
         <v>172</v>
       </c>
-      <c r="C11" s="69"/>
+      <c r="C11" s="83"/>
     </row>
     <row r="12" spans="1:7" s="33" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="81" t="s">
         <v>173</v>
       </c>
-      <c r="C12" s="69"/>
+      <c r="C12" s="83"/>
     </row>
     <row r="13" spans="1:7" s="33" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="C13" s="78"/>
+      <c r="C13" s="79"/>
     </row>
     <row r="14" spans="1:7" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="98" t="s">
+      <c r="A14" s="103" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="105"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="85"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="106"/>
+      <c r="C15" s="86"/>
     </row>
     <row r="16" spans="1:7" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="81">
+      <c r="A16" s="60">
         <v>46295</v>
       </c>
-      <c r="B16" s="79">
+      <c r="B16" s="58">
         <f>'Escrow e IT Serviços'!C18</f>
         <v>272521.32676999999</v>
       </c>
-      <c r="C16" s="106"/>
+      <c r="C16" s="86"/>
     </row>
     <row r="17" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="81">
+      <c r="A17" s="60">
         <v>46326</v>
       </c>
-      <c r="B17" s="79">
+      <c r="B17" s="58">
         <f>'Escrow e IT Serviços'!D18</f>
         <v>300764.26725999994</v>
       </c>
-      <c r="C17" s="106"/>
+      <c r="C17" s="86"/>
     </row>
     <row r="18" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="81">
+      <c r="A18" s="60">
         <v>46356</v>
       </c>
-      <c r="B18" s="79">
+      <c r="B18" s="58">
         <f>'Escrow e IT Serviços'!E18</f>
         <v>272521.32676999999</v>
       </c>
-      <c r="C18" s="106"/>
+      <c r="C18" s="86"/>
     </row>
     <row r="19" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="81">
+      <c r="A19" s="60">
         <v>46387</v>
       </c>
-      <c r="B19" s="79">
+      <c r="B19" s="58">
         <f>'Escrow e IT Serviços'!F18</f>
         <v>190659.92782999997</v>
       </c>
-      <c r="C19" s="106"/>
+      <c r="C19" s="86"/>
     </row>
     <row r="20" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="81">
+      <c r="A20" s="60">
         <v>46418</v>
       </c>
-      <c r="B20" s="79">
+      <c r="B20" s="58">
         <f>'Escrow e IT Serviços'!G18</f>
         <v>162425.63583999997</v>
       </c>
-      <c r="C20" s="106"/>
+      <c r="C20" s="86"/>
     </row>
     <row r="21" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="81">
+      <c r="A21" s="60">
         <v>46446</v>
       </c>
-      <c r="B21" s="79">
+      <c r="B21" s="58">
         <f>'Escrow e IT Serviços'!H18</f>
         <v>189847.46656</v>
       </c>
-      <c r="C21" s="106"/>
+      <c r="C21" s="86"/>
     </row>
     <row r="22" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="81">
+      <c r="A22" s="60">
         <v>46477</v>
       </c>
-      <c r="B22" s="79">
+      <c r="B22" s="58">
         <f>'Escrow e IT Serviços'!I18</f>
         <v>156602.22308</v>
       </c>
-      <c r="C22" s="106"/>
+      <c r="C22" s="86"/>
     </row>
     <row r="23" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="81">
+      <c r="A23" s="60">
         <v>46507</v>
       </c>
-      <c r="B23" s="79">
+      <c r="B23" s="58">
         <f>'Escrow e IT Serviços'!J18</f>
         <v>184277.09125999999</v>
       </c>
-      <c r="C23" s="106"/>
+      <c r="C23" s="86"/>
     </row>
     <row r="24" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="81">
+      <c r="A24" s="60">
         <v>46538</v>
       </c>
-      <c r="B24" s="79">
+      <c r="B24" s="58">
         <f>'Escrow e IT Serviços'!K18</f>
         <v>72183.099100000007</v>
       </c>
-      <c r="C24" s="106"/>
+      <c r="C24" s="86"/>
     </row>
     <row r="25" spans="1:3" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="81">
+      <c r="A25" s="60">
         <v>46568</v>
       </c>
-      <c r="B25" s="79">
+      <c r="B25" s="58">
         <f>'Escrow e IT Serviços'!L18</f>
         <v>72186.03959</v>
       </c>
-      <c r="C25" s="106"/>
+      <c r="C25" s="86"/>
     </row>
     <row r="26" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="81">
+      <c r="A26" s="60">
         <v>46599</v>
       </c>
-      <c r="B26" s="79">
+      <c r="B26" s="58">
         <f>'Escrow e IT Serviços'!M18</f>
         <v>72183.099100000007</v>
       </c>
-      <c r="C26" s="106"/>
+      <c r="C26" s="86"/>
     </row>
     <row r="27" spans="1:3" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="81">
+      <c r="A27" s="60">
         <v>46630</v>
       </c>
-      <c r="B27" s="79">
+      <c r="B27" s="58">
         <f>'Escrow e IT Serviços'!N18</f>
         <v>72186.03959</v>
       </c>
-      <c r="C27" s="106"/>
+      <c r="C27" s="86"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="81">
+      <c r="A28" s="60">
         <v>46660</v>
       </c>
-      <c r="B28" s="79">
+      <c r="B28" s="58">
         <f>'Escrow e IT Serviços'!O18</f>
         <v>71236.091879999993</v>
       </c>
-      <c r="C28" s="106"/>
+      <c r="C28" s="86"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="81">
+      <c r="A29" s="60">
         <v>46691</v>
       </c>
-      <c r="B29" s="79">
+      <c r="B29" s="58">
         <f>'Escrow e IT Serviços'!P18</f>
         <v>71239.046489999993</v>
       </c>
-      <c r="C29" s="106"/>
+      <c r="C29" s="86"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="81">
+      <c r="A30" s="60">
         <v>46721</v>
       </c>
-      <c r="B30" s="79">
+      <c r="B30" s="58">
         <f>'Escrow e IT Serviços'!Q18</f>
         <v>30055.687269999999</v>
       </c>
-      <c r="C30" s="106"/>
+      <c r="C30" s="86"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="81">
+      <c r="A31" s="60">
         <v>46752</v>
       </c>
-      <c r="B31" s="79">
+      <c r="B31" s="58">
         <f>'Escrow e IT Serviços'!R18</f>
         <v>30055.687269999999</v>
       </c>
-      <c r="C31" s="106"/>
+      <c r="C31" s="86"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="81">
+      <c r="A32" s="60">
         <v>46783</v>
       </c>
-      <c r="B32" s="79">
+      <c r="B32" s="58">
         <f>'Escrow e IT Serviços'!S18</f>
         <v>29182.326440000001</v>
       </c>
-      <c r="C32" s="106"/>
+      <c r="C32" s="86"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="81">
+      <c r="A33" s="60">
         <v>46812</v>
       </c>
-      <c r="B33" s="79">
+      <c r="B33" s="58">
         <f>'Escrow e IT Serviços'!T18</f>
         <v>28346.496569999999</v>
       </c>
-      <c r="C33" s="106"/>
+      <c r="C33" s="86"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="81">
+      <c r="A34" s="60">
         <v>46843</v>
       </c>
-      <c r="B34" s="79">
+      <c r="B34" s="58">
         <f>'Escrow e IT Serviços'!U18</f>
         <v>28346.496569999999</v>
       </c>
-      <c r="C34" s="106"/>
+      <c r="C34" s="86"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="81">
+      <c r="A35" s="60">
         <v>46873</v>
       </c>
-      <c r="B35" s="79">
+      <c r="B35" s="58">
         <f>'Escrow e IT Serviços'!V18</f>
         <v>28346.496569999999</v>
       </c>
-      <c r="C35" s="106"/>
+      <c r="C35" s="86"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="97">
+      <c r="B36" s="66">
         <f>SUM(B16:B35)</f>
         <v>2335165.8718099995</v>
       </c>
-      <c r="C36" s="106"/>
+      <c r="C36" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="C14:C36"/>
     <mergeCell ref="B8:C8"/>
@@ -7810,12 +7837,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7831,88 +7852,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="104" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="59"/>
+      <c r="B1" s="105"/>
     </row>
     <row r="2" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="48" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="51" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="54">
+      <c r="B4" s="49">
         <v>46230</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="51" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="51" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="56">
+      <c r="B7" s="51">
         <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="55">
+      <c r="B8" s="50">
         <v>4562745.8</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="51" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="51" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="51" t="s">
         <v>111</v>
       </c>
     </row>
@@ -7936,315 +7957,315 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
     </row>
     <row r="3" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="66"/>
+      <c r="C3" s="95"/>
     </row>
     <row r="4" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="69"/>
+      <c r="C4" s="83"/>
     </row>
     <row r="5" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="87" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="72"/>
+      <c r="C5" s="89"/>
     </row>
     <row r="6" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="81" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="69"/>
+      <c r="C6" s="83"/>
     </row>
     <row r="7" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="69"/>
+      <c r="C7" s="83"/>
     </row>
     <row r="8" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="67">
+      <c r="B8" s="81">
         <v>141</v>
       </c>
-      <c r="C8" s="69"/>
+      <c r="C8" s="83"/>
     </row>
     <row r="9" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="84"/>
+      <c r="C9" s="92"/>
     </row>
     <row r="10" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="69"/>
+      <c r="C10" s="83"/>
     </row>
     <row r="11" spans="1:3" s="33" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="81" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="69"/>
+      <c r="C11" s="83"/>
     </row>
     <row r="12" spans="1:3" s="33" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="81" t="s">
         <v>167</v>
       </c>
-      <c r="C12" s="69"/>
+      <c r="C12" s="83"/>
     </row>
     <row r="13" spans="1:3" s="33" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="C13" s="78"/>
+      <c r="C13" s="79"/>
     </row>
     <row r="14" spans="1:3" s="33" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="98" t="s">
+      <c r="A14" s="103" t="s">
         <v>182</v>
       </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="61"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="53"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="62"/>
+      <c r="C15" s="54"/>
     </row>
     <row r="16" spans="1:3" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="81">
+      <c r="A16" s="60">
         <v>46295</v>
       </c>
-      <c r="B16" s="79">
+      <c r="B16" s="58">
         <f>'Escrow e IT Serviços'!C17</f>
         <v>499493.76322999998</v>
       </c>
-      <c r="C16" s="80"/>
+      <c r="C16" s="59"/>
     </row>
     <row r="17" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="81">
+      <c r="A17" s="60">
         <v>46326</v>
       </c>
-      <c r="B17" s="79">
+      <c r="B17" s="58">
         <f>'Escrow e IT Serviços'!D17</f>
         <v>551259.15273999993</v>
       </c>
-      <c r="C17" s="80"/>
+      <c r="C17" s="59"/>
     </row>
     <row r="18" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="81">
+      <c r="A18" s="60">
         <v>46356</v>
       </c>
-      <c r="B18" s="79">
+      <c r="B18" s="58">
         <f>'Escrow e IT Serviços'!E17</f>
         <v>499493.76322999998</v>
       </c>
-      <c r="C18" s="80"/>
+      <c r="C18" s="59"/>
     </row>
     <row r="19" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="81">
+      <c r="A19" s="60">
         <v>46387</v>
       </c>
-      <c r="B19" s="79">
+      <c r="B19" s="58">
         <f>'Escrow e IT Serviços'!F17</f>
         <v>349453.18216999999</v>
       </c>
-      <c r="C19" s="80"/>
+      <c r="C19" s="59"/>
     </row>
     <row r="20" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="81">
+      <c r="A20" s="60">
         <v>46418</v>
       </c>
-      <c r="B20" s="79">
+      <c r="B20" s="58">
         <f>'Escrow e IT Serviços'!G17</f>
         <v>297703.64415999997</v>
       </c>
-      <c r="C20" s="80"/>
+      <c r="C20" s="59"/>
     </row>
     <row r="21" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="81">
+      <c r="A21" s="60">
         <v>46446</v>
       </c>
-      <c r="B21" s="79">
+      <c r="B21" s="58">
         <f>'Escrow e IT Serviços'!H17</f>
         <v>347964.05344000005</v>
       </c>
-      <c r="C21" s="80"/>
+      <c r="C21" s="59"/>
     </row>
     <row r="22" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="81">
+      <c r="A22" s="60">
         <v>46477</v>
       </c>
-      <c r="B22" s="79">
+      <c r="B22" s="58">
         <f>'Escrow e IT Serviços'!I17</f>
         <v>287030.13692000002</v>
       </c>
-      <c r="C22" s="80"/>
+      <c r="C22" s="59"/>
     </row>
     <row r="23" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="81">
+      <c r="A23" s="60">
         <v>46507</v>
       </c>
-      <c r="B23" s="79">
+      <c r="B23" s="58">
         <f>'Escrow e IT Serviços'!J17</f>
         <v>337754.32874000003</v>
       </c>
-      <c r="C23" s="80"/>
+      <c r="C23" s="59"/>
     </row>
     <row r="24" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="81">
+      <c r="A24" s="60">
         <v>46538</v>
       </c>
-      <c r="B24" s="79">
+      <c r="B24" s="58">
         <f>'Escrow e IT Serviços'!K17</f>
         <v>132301.60090000002</v>
       </c>
-      <c r="C24" s="80"/>
+      <c r="C24" s="59"/>
     </row>
     <row r="25" spans="1:3" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="81">
+      <c r="A25" s="60">
         <v>46568</v>
       </c>
-      <c r="B25" s="79">
+      <c r="B25" s="58">
         <f>'Escrow e IT Serviços'!L17</f>
         <v>132306.99041</v>
       </c>
-      <c r="C25" s="80"/>
+      <c r="C25" s="59"/>
     </row>
     <row r="26" spans="1:3" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="81">
+      <c r="A26" s="60">
         <v>46599</v>
       </c>
-      <c r="B26" s="79">
+      <c r="B26" s="58">
         <f>'Escrow e IT Serviços'!M17</f>
         <v>132301.60090000002</v>
       </c>
-      <c r="C26" s="80"/>
+      <c r="C26" s="59"/>
     </row>
     <row r="27" spans="1:3" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="81">
+      <c r="A27" s="60">
         <v>46630</v>
       </c>
-      <c r="B27" s="79">
+      <c r="B27" s="58">
         <f>'Escrow e IT Serviços'!N17</f>
         <v>132306.99041</v>
       </c>
-      <c r="C27" s="80"/>
+      <c r="C27" s="59"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="81">
+      <c r="A28" s="60">
         <v>46660</v>
       </c>
-      <c r="B28" s="79">
+      <c r="B28" s="58">
         <f>'Escrow e IT Serviços'!O17</f>
         <v>130565.86812</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="81">
+      <c r="A29" s="60">
         <v>46691</v>
       </c>
-      <c r="B29" s="79">
+      <c r="B29" s="58">
         <f>'Escrow e IT Serviços'!P17</f>
         <v>130571.28350999999</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="81">
+      <c r="A30" s="60">
         <v>46721</v>
       </c>
-      <c r="B30" s="79">
+      <c r="B30" s="58">
         <f>'Escrow e IT Serviços'!Q17</f>
         <v>55087.902730000002</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="81">
+      <c r="A31" s="60">
         <v>46752</v>
       </c>
-      <c r="B31" s="79">
+      <c r="B31" s="58">
         <f>'Escrow e IT Serviços'!R17</f>
         <v>55087.902730000002</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="81">
+      <c r="A32" s="60">
         <v>46783</v>
       </c>
-      <c r="B32" s="79">
+      <c r="B32" s="58">
         <f>'Escrow e IT Serviços'!S17</f>
         <v>53487.153560000006</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="81">
+      <c r="A33" s="60">
         <v>46812</v>
       </c>
-      <c r="B33" s="79">
+      <c r="B33" s="58">
         <f>'Escrow e IT Serviços'!T17</f>
         <v>51955.193430000007</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="81">
+      <c r="A34" s="60">
         <v>46843</v>
       </c>
-      <c r="B34" s="79">
+      <c r="B34" s="58">
         <f>'Escrow e IT Serviços'!U17</f>
         <v>51955.193430000007</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="81">
+      <c r="A35" s="60">
         <v>46873</v>
       </c>
-      <c r="B35" s="79">
+      <c r="B35" s="58">
         <f>'Escrow e IT Serviços'!V17</f>
         <v>51955.193430000007</v>
       </c>
@@ -8253,13 +8274,19 @@
       <c r="A36" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="97">
+      <c r="B36" s="66">
         <f>SUM(B16:B35)</f>
         <v>4280034.8981900001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
@@ -8267,12 +8294,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8289,244 +8310,254 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
     </row>
     <row r="3" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="66"/>
+      <c r="C3" s="95"/>
     </row>
     <row r="4" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="69"/>
+      <c r="C4" s="83"/>
     </row>
     <row r="5" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="70">
+      <c r="B5" s="87">
         <v>46230</v>
       </c>
-      <c r="C5" s="72"/>
+      <c r="C5" s="89"/>
     </row>
     <row r="6" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="69"/>
+      <c r="C6" s="83"/>
     </row>
     <row r="7" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="69"/>
+      <c r="C7" s="83"/>
     </row>
     <row r="8" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="67">
+      <c r="B8" s="81">
         <v>141</v>
       </c>
-      <c r="C8" s="69"/>
+      <c r="C8" s="83"/>
     </row>
     <row r="9" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="82">
+      <c r="B9" s="90">
         <v>1941000</v>
       </c>
-      <c r="C9" s="84"/>
+      <c r="C9" s="92"/>
     </row>
     <row r="10" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="69"/>
+      <c r="C10" s="83"/>
     </row>
     <row r="11" spans="1:3" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="69"/>
+      <c r="C11" s="83"/>
     </row>
     <row r="12" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="C12" s="69"/>
+      <c r="C12" s="83"/>
     </row>
     <row r="14" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
     </row>
     <row r="15" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="66"/>
+      <c r="C15" s="95"/>
     </row>
     <row r="16" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="69"/>
+      <c r="C16" s="83"/>
     </row>
     <row r="17" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="70">
+      <c r="B17" s="87">
         <v>46240</v>
       </c>
-      <c r="C17" s="72"/>
+      <c r="C17" s="89"/>
     </row>
     <row r="18" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="69"/>
+      <c r="C18" s="83"/>
     </row>
     <row r="19" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="69"/>
+      <c r="C19" s="83"/>
     </row>
     <row r="20" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="67">
+      <c r="B20" s="81">
         <v>1431</v>
       </c>
-      <c r="C20" s="69"/>
+      <c r="C20" s="83"/>
     </row>
     <row r="21" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="52" t="s">
+      <c r="A21" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="82">
+      <c r="B21" s="90">
         <v>1941000</v>
       </c>
-      <c r="C21" s="84"/>
+      <c r="C21" s="92"/>
     </row>
     <row r="22" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="69"/>
+      <c r="C22" s="83"/>
     </row>
     <row r="23" spans="1:3" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="C23" s="69"/>
+      <c r="C23" s="83"/>
     </row>
     <row r="24" spans="1:3" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="69"/>
+      <c r="C24" s="83"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="94" t="s">
+      <c r="A25" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="95"/>
-      <c r="C25" s="96"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="100"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="63" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="90" t="s">
+      <c r="B26" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="91"/>
+      <c r="C26" s="101"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="75">
+      <c r="A27" s="57">
         <v>46965</v>
       </c>
       <c r="B27" s="40">
         <v>422491</v>
       </c>
-      <c r="C27" s="92"/>
+      <c r="C27" s="102"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="75">
+      <c r="A28" s="57">
         <v>47330</v>
       </c>
       <c r="B28" s="40">
         <v>422491</v>
       </c>
-      <c r="C28" s="92"/>
+      <c r="C28" s="102"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="75">
+      <c r="A29" s="57">
         <v>47695</v>
       </c>
       <c r="B29" s="40">
         <v>422491</v>
       </c>
-      <c r="C29" s="92"/>
+      <c r="C29" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="B12:C12"/>
@@ -8541,16 +8572,6 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8566,88 +8587,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="59"/>
+      <c r="B1" s="105"/>
     </row>
     <row r="2" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="48" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="51" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="54">
+      <c r="B4" s="49">
         <v>46230</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="51" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="51" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="56">
+      <c r="B7" s="51">
         <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="55">
+      <c r="B8" s="50">
         <v>8362181.3700000001</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="51" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="51" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="51" t="s">
         <v>111</v>
       </c>
     </row>
@@ -8660,14 +8681,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9126A784-1C98-9F45-AB74-8C05D98CDB5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1668A7-14B9-714D-8077-09B8988D1B00}">
   <dimension ref="A1:CD51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
     <col min="6" max="17" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="20" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -10115,7 +10136,7 @@
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
       <c r="D8" s="40">
-        <f t="shared" ref="D8:AI8" si="0">SUM(D5:D7)</f>
+        <f t="shared" ref="D8:BB8" si="0">SUM(D5:D7)</f>
         <v>59042640.313019089</v>
       </c>
       <c r="E8" s="29">
@@ -10243,79 +10264,79 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="29">
-        <f t="shared" ref="AJ8:BO8" si="1">SUM(AJ5:AJ7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AK8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AL8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AM8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AN8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AO8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AP8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AQ8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AR8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AS8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AT8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AU8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AV8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AW8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AX8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AY8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AZ8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BA8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BB8" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>59042640.313019089</v>
       </c>
     </row>
@@ -10326,203 +10347,203 @@
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
       <c r="D9" s="40">
-        <f t="shared" ref="D9:AI9" si="2">SUM(D3:D7)</f>
+        <f t="shared" ref="D9:BA9" si="1">SUM(D3:D7)</f>
         <v>165300000</v>
       </c>
       <c r="E9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>66119999.999999993</v>
       </c>
       <c r="F9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>772015.09</v>
       </c>
       <c r="H9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5429734.9100000001</v>
       </c>
       <c r="I9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>772015.09</v>
       </c>
       <c r="J9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>540113.11</v>
       </c>
       <c r="K9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4886621.7999999989</v>
       </c>
       <c r="L9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>537811.52</v>
       </c>
       <c r="M9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>443632.36</v>
       </c>
       <c r="N9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5217306.12</v>
       </c>
       <c r="O9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>204484.7</v>
       </c>
       <c r="P9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>204493.03</v>
       </c>
       <c r="Q9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5789772.2699999996</v>
       </c>
       <c r="R9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>204493.03</v>
       </c>
       <c r="S9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>201801.96</v>
       </c>
       <c r="T9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>201810.33</v>
       </c>
       <c r="U9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>85143.59</v>
       </c>
       <c r="V9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>85143.59</v>
       </c>
       <c r="W9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>82669.48000000001</v>
       </c>
       <c r="X9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>80301.69</v>
       </c>
       <c r="Y9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>80301.69</v>
       </c>
       <c r="Z9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>80301.69</v>
       </c>
       <c r="AA9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>23690032.950000003</v>
       </c>
       <c r="AD9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AI9" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ9" s="29">
-        <f t="shared" ref="AJ9:BA9" si="3">SUM(AJ3:AJ7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AL9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AM9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AN9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AO9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>24795000</v>
       </c>
       <c r="AP9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AQ9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AR9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AS9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AT9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AU9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AV9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AW9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AY9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AZ9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BA9" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>24795000</v>
       </c>
       <c r="BB9" s="30">
@@ -11131,7 +11152,7 @@
         <v>15619413.554294141</v>
       </c>
       <c r="BB13" s="41">
-        <f t="shared" ref="BB13:BB22" si="4">SUM(E13:BA13)</f>
+        <f t="shared" ref="BB13:BB22" si="2">SUM(E13:BA13)</f>
         <v>42649550.918097198</v>
       </c>
       <c r="BC13" s="41"/>
@@ -11163,248 +11184,248 @@
       <c r="CC13" s="43"/>
       <c r="CD13" s="43"/>
     </row>
-    <row r="14" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A14" s="31" t="s">
+    <row r="14" spans="1:82" s="107" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="106" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="107" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="32">
-        <f>('Fluxo de pagamentos'!J7+'Fluxo de pagamentos'!J8)*64.7%</f>
-        <v>7488507.898190001</v>
-      </c>
-      <c r="E14" s="32">
+      <c r="D14" s="108">
+        <f>D15-D13</f>
+        <v>7489765.1670694575</v>
+      </c>
+      <c r="E14" s="108">
         <f>('Fluxo de pagamentos'!K7+'Fluxo de pagamentos'!K8)*64.7%</f>
         <v>1941000</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="108">
         <f>('Fluxo de pagamentos'!L7+'Fluxo de pagamentos'!L8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="108">
         <f>('Fluxo de pagamentos'!M7+'Fluxo de pagamentos'!M8)*64.7%</f>
         <v>499493.76322999998</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="108">
         <f>('Fluxo de pagamentos'!N7+'Fluxo de pagamentos'!N8)*64.7%</f>
         <v>551259.15273999993</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="108">
         <f>('Fluxo de pagamentos'!O7+'Fluxo de pagamentos'!O8)*64.7%</f>
         <v>499493.76322999998</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="108">
         <f>('Fluxo de pagamentos'!P7+'Fluxo de pagamentos'!P8)*64.7%</f>
         <v>349453.18216999999</v>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="108">
         <f>('Fluxo de pagamentos'!Q7+'Fluxo de pagamentos'!Q8)*64.7%</f>
         <v>297703.64415999997</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="108">
         <f>('Fluxo de pagamentos'!R7+'Fluxo de pagamentos'!R8)*64.7%</f>
         <v>347964.05344000005</v>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="108">
         <f>('Fluxo de pagamentos'!S7+'Fluxo de pagamentos'!S8)*64.7%</f>
         <v>287030.13692000002</v>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="108">
         <f>('Fluxo de pagamentos'!T7+'Fluxo de pagamentos'!T8)*64.7%</f>
         <v>337754.32874000003</v>
       </c>
-      <c r="O14" s="32">
+      <c r="O14" s="108">
         <f>('Fluxo de pagamentos'!U7+'Fluxo de pagamentos'!U8)*64.7%</f>
         <v>132301.60090000002</v>
       </c>
-      <c r="P14" s="32">
+      <c r="P14" s="108">
         <f>('Fluxo de pagamentos'!V7+'Fluxo de pagamentos'!V8)*64.7%</f>
         <v>132306.99041</v>
       </c>
-      <c r="Q14" s="32">
+      <c r="Q14" s="108">
         <f>('Fluxo de pagamentos'!W7+'Fluxo de pagamentos'!W8)*64.7%</f>
         <v>132301.60090000002</v>
       </c>
-      <c r="R14" s="32">
+      <c r="R14" s="108">
         <f>('Fluxo de pagamentos'!X7+'Fluxo de pagamentos'!X8)*64.7%</f>
         <v>132306.99041</v>
       </c>
-      <c r="S14" s="32">
+      <c r="S14" s="108">
         <f>('Fluxo de pagamentos'!Y7+'Fluxo de pagamentos'!Y8)*64.7%</f>
         <v>130565.86812</v>
       </c>
-      <c r="T14" s="32">
+      <c r="T14" s="108">
         <f>('Fluxo de pagamentos'!Z7+'Fluxo de pagamentos'!Z8)*64.7%</f>
         <v>130571.28350999999</v>
       </c>
-      <c r="U14" s="32">
+      <c r="U14" s="108">
         <f>('Fluxo de pagamentos'!AA7+'Fluxo de pagamentos'!AA8)*64.7%</f>
         <v>55087.902730000002</v>
       </c>
-      <c r="V14" s="32">
+      <c r="V14" s="108">
         <f>('Fluxo de pagamentos'!AB7+'Fluxo de pagamentos'!AB8)*64.7%</f>
         <v>55087.902730000002</v>
       </c>
-      <c r="W14" s="32">
+      <c r="W14" s="108">
         <f>('Fluxo de pagamentos'!AC7+'Fluxo de pagamentos'!AC8)*64.7%</f>
         <v>53487.153560000006</v>
       </c>
-      <c r="X14" s="32">
+      <c r="X14" s="108">
         <f>('Fluxo de pagamentos'!AD7+'Fluxo de pagamentos'!AD8)*64.7%</f>
         <v>51955.193430000007</v>
       </c>
-      <c r="Y14" s="32">
+      <c r="Y14" s="108">
         <f>('Fluxo de pagamentos'!AE7+'Fluxo de pagamentos'!AE8)*64.7%</f>
         <v>51955.193430000007</v>
       </c>
-      <c r="Z14" s="32">
+      <c r="Z14" s="108">
         <f>('Fluxo de pagamentos'!AF7+'Fluxo de pagamentos'!AF8)*64.7%</f>
         <v>51955.193430000007</v>
       </c>
-      <c r="AA14" s="32">
+      <c r="AA14" s="108">
         <f>('Fluxo de pagamentos'!AG7+'Fluxo de pagamentos'!AG8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="32">
+      <c r="AB14" s="108">
         <f>('Fluxo de pagamentos'!AH7+'Fluxo de pagamentos'!AH8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="32">
+      <c r="AC14" s="108">
         <f>('Fluxo de pagamentos'!AI7+'Fluxo de pagamentos'!AI8)*64.7%</f>
         <v>422491</v>
       </c>
-      <c r="AD14" s="32">
+      <c r="AD14" s="108">
         <f>('Fluxo de pagamentos'!AJ7+'Fluxo de pagamentos'!AJ8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="32">
+      <c r="AE14" s="108">
         <f>('Fluxo de pagamentos'!AK7+'Fluxo de pagamentos'!AK8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="32">
+      <c r="AF14" s="108">
         <f>('Fluxo de pagamentos'!AL7+'Fluxo de pagamentos'!AL8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="32">
+      <c r="AG14" s="108">
         <f>('Fluxo de pagamentos'!AM7+'Fluxo de pagamentos'!AM8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AH14" s="32">
+      <c r="AH14" s="108">
         <f>('Fluxo de pagamentos'!AN7+'Fluxo de pagamentos'!AN8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AI14" s="32">
+      <c r="AI14" s="108">
         <f>('Fluxo de pagamentos'!AO7+'Fluxo de pagamentos'!AO8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AJ14" s="32">
+      <c r="AJ14" s="108">
         <f>('Fluxo de pagamentos'!AP7+'Fluxo de pagamentos'!AP8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AK14" s="32">
+      <c r="AK14" s="108">
         <f>('Fluxo de pagamentos'!AQ7+'Fluxo de pagamentos'!AQ8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AL14" s="32">
+      <c r="AL14" s="108">
         <f>('Fluxo de pagamentos'!AR7+'Fluxo de pagamentos'!AR8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AM14" s="32">
+      <c r="AM14" s="108">
         <f>('Fluxo de pagamentos'!AS7+'Fluxo de pagamentos'!AS8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AN14" s="32">
+      <c r="AN14" s="108">
         <f>('Fluxo de pagamentos'!AT7+'Fluxo de pagamentos'!AT8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="32">
+      <c r="AO14" s="108">
         <f>('Fluxo de pagamentos'!AU7+'Fluxo de pagamentos'!AU8)*64.7%</f>
         <v>422491</v>
       </c>
-      <c r="AP14" s="32">
+      <c r="AP14" s="108">
         <f>('Fluxo de pagamentos'!AV7+'Fluxo de pagamentos'!AV8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AQ14" s="32">
+      <c r="AQ14" s="108">
         <f>('Fluxo de pagamentos'!AW7+'Fluxo de pagamentos'!AW8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="32">
+      <c r="AR14" s="108">
         <f>('Fluxo de pagamentos'!AX7+'Fluxo de pagamentos'!AX8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AS14" s="32">
+      <c r="AS14" s="108">
         <f>('Fluxo de pagamentos'!AY7+'Fluxo de pagamentos'!AY8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AT14" s="32">
+      <c r="AT14" s="108">
         <f>('Fluxo de pagamentos'!AZ7+'Fluxo de pagamentos'!AZ8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AU14" s="32">
+      <c r="AU14" s="108">
         <f>('Fluxo de pagamentos'!BA7+'Fluxo de pagamentos'!BA8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AV14" s="32">
+      <c r="AV14" s="108">
         <f>('Fluxo de pagamentos'!BB7+'Fluxo de pagamentos'!BB8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AW14" s="32">
+      <c r="AW14" s="108">
         <f>('Fluxo de pagamentos'!BC7+'Fluxo de pagamentos'!BC8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AX14" s="32">
+      <c r="AX14" s="108">
         <f>('Fluxo de pagamentos'!BD7+'Fluxo de pagamentos'!BD8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AY14" s="32">
+      <c r="AY14" s="108">
         <f>('Fluxo de pagamentos'!BE7+'Fluxo de pagamentos'!BE8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="AZ14" s="32">
+      <c r="AZ14" s="108">
         <f>('Fluxo de pagamentos'!BF7+'Fluxo de pagamentos'!BF8)*64.7%</f>
         <v>0</v>
       </c>
-      <c r="BA14" s="32">
+      <c r="BA14" s="108">
         <f>('Fluxo de pagamentos'!BG7+'Fluxo de pagamentos'!BG8)*64.7%</f>
         <v>422491</v>
       </c>
-      <c r="BB14" s="41">
-        <f t="shared" si="4"/>
+      <c r="BB14" s="109">
+        <f t="shared" si="2"/>
         <v>7488507.898190002</v>
       </c>
-      <c r="BC14" s="41"/>
-      <c r="BD14" s="42"/>
-      <c r="BE14" s="43"/>
-      <c r="BF14" s="43"/>
-      <c r="BG14" s="43"/>
-      <c r="BH14" s="43"/>
-      <c r="BI14" s="43"/>
-      <c r="BJ14" s="43"/>
-      <c r="BK14" s="43"/>
-      <c r="BL14" s="43"/>
-      <c r="BM14" s="43"/>
-      <c r="BN14" s="43"/>
-      <c r="BO14" s="43"/>
-      <c r="BP14" s="43"/>
-      <c r="BQ14" s="43"/>
-      <c r="BR14" s="43"/>
-      <c r="BS14" s="43"/>
-      <c r="BT14" s="43"/>
-      <c r="BU14" s="43"/>
-      <c r="BV14" s="43"/>
-      <c r="BW14" s="43"/>
-      <c r="BX14" s="43"/>
-      <c r="BY14" s="43"/>
-      <c r="BZ14" s="43"/>
-      <c r="CA14" s="43"/>
-      <c r="CB14" s="43"/>
-      <c r="CC14" s="43"/>
-      <c r="CD14" s="43"/>
+      <c r="BC14" s="109"/>
+      <c r="BD14" s="110"/>
+      <c r="BE14" s="111"/>
+      <c r="BF14" s="111"/>
+      <c r="BG14" s="111"/>
+      <c r="BH14" s="111"/>
+      <c r="BI14" s="111"/>
+      <c r="BJ14" s="111"/>
+      <c r="BK14" s="111"/>
+      <c r="BL14" s="111"/>
+      <c r="BM14" s="111"/>
+      <c r="BN14" s="111"/>
+      <c r="BO14" s="111"/>
+      <c r="BP14" s="111"/>
+      <c r="BQ14" s="111"/>
+      <c r="BR14" s="111"/>
+      <c r="BS14" s="111"/>
+      <c r="BT14" s="111"/>
+      <c r="BU14" s="111"/>
+      <c r="BV14" s="111"/>
+      <c r="BW14" s="111"/>
+      <c r="BX14" s="111"/>
+      <c r="BY14" s="111"/>
+      <c r="BZ14" s="111"/>
+      <c r="CA14" s="111"/>
+      <c r="CB14" s="111"/>
+      <c r="CC14" s="111"/>
+      <c r="CD14" s="111"/>
     </row>
     <row r="15" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="31" t="s">
@@ -11417,208 +11438,208 @@
         <v>48</v>
       </c>
       <c r="D15" s="32">
-        <f t="shared" ref="D15:AI15" si="5">SUM(D13:D14)</f>
-        <v>50138058.816287197</v>
+        <f>D3*64.7%</f>
+        <v>50139316.085166655</v>
       </c>
       <c r="E15" s="32">
-        <f t="shared" si="5"/>
-        <v>10303181.373645578</v>
+        <f>E3*64.7%</f>
+        <v>10303427.882932995</v>
       </c>
       <c r="F15" s="32">
-        <f t="shared" si="5"/>
+        <f>SUM(F13:F14)</f>
         <v>0</v>
       </c>
       <c r="G15" s="32">
-        <f t="shared" si="5"/>
+        <f>G3*64.7%</f>
         <v>499493.76322999998</v>
       </c>
       <c r="H15" s="32">
-        <f t="shared" si="5"/>
+        <f>H3*64.7%</f>
         <v>551259.15273999993</v>
       </c>
       <c r="I15" s="32">
-        <f t="shared" si="5"/>
+        <f>I3*64.7%</f>
         <v>499493.76322999998</v>
       </c>
       <c r="J15" s="32">
-        <f t="shared" si="5"/>
+        <f>J3*64.7%</f>
         <v>349453.18216999999</v>
       </c>
       <c r="K15" s="32">
-        <f t="shared" si="5"/>
+        <f>K3*64.7%</f>
         <v>297703.64415999997</v>
       </c>
       <c r="L15" s="32">
-        <f t="shared" si="5"/>
+        <f>L3*64.7%</f>
         <v>347964.05344000005</v>
       </c>
       <c r="M15" s="32">
-        <f t="shared" si="5"/>
+        <f>M3*64.7%</f>
         <v>287030.13692000002</v>
       </c>
       <c r="N15" s="32">
-        <f t="shared" si="5"/>
+        <f>N3*64.7%</f>
         <v>337754.32874000003</v>
       </c>
       <c r="O15" s="32">
-        <f t="shared" si="5"/>
+        <f>O3*64.7%</f>
         <v>132301.60090000002</v>
       </c>
       <c r="P15" s="32">
-        <f t="shared" si="5"/>
+        <f>P3*64.7%</f>
         <v>132306.99041</v>
       </c>
       <c r="Q15" s="32">
-        <f t="shared" si="5"/>
+        <f>Q3*64.7%</f>
         <v>132301.60090000002</v>
       </c>
       <c r="R15" s="32">
-        <f t="shared" si="5"/>
+        <f>R3*64.7%</f>
         <v>132306.99041</v>
       </c>
       <c r="S15" s="32">
-        <f t="shared" si="5"/>
+        <f>S3*64.7%</f>
         <v>130565.86812</v>
       </c>
       <c r="T15" s="32">
-        <f t="shared" si="5"/>
+        <f>T3*64.7%</f>
         <v>130571.28350999999</v>
       </c>
       <c r="U15" s="32">
-        <f t="shared" si="5"/>
+        <f>U3*64.7%</f>
         <v>55087.902730000002</v>
       </c>
       <c r="V15" s="32">
-        <f t="shared" si="5"/>
+        <f>V3*64.7%</f>
         <v>55087.902730000002</v>
       </c>
       <c r="W15" s="32">
-        <f t="shared" si="5"/>
+        <f>W3*64.7%</f>
         <v>53487.153560000006</v>
       </c>
       <c r="X15" s="32">
-        <f t="shared" si="5"/>
+        <f>X3*64.7%</f>
         <v>51955.193430000007</v>
       </c>
       <c r="Y15" s="32">
-        <f t="shared" si="5"/>
+        <f>Y3*64.7%</f>
         <v>51955.193430000007</v>
       </c>
       <c r="Z15" s="32">
-        <f t="shared" si="5"/>
+        <f>Z3*64.7%</f>
         <v>51955.193430000007</v>
       </c>
       <c r="AA15" s="32">
-        <f t="shared" si="5"/>
+        <f>SUM(AA13:AA14)</f>
         <v>0</v>
       </c>
       <c r="AB15" s="32">
-        <f t="shared" si="5"/>
+        <f>SUM(AB13:AB14)</f>
         <v>0</v>
       </c>
       <c r="AC15" s="32">
-        <f t="shared" si="5"/>
-        <v>3471033.4358633407</v>
+        <f>AC3*64.7%</f>
+        <v>3471123.3040436562</v>
       </c>
       <c r="AD15" s="32">
-        <f t="shared" si="5"/>
+        <f>SUM(AD13:AD14)</f>
         <v>0</v>
       </c>
       <c r="AE15" s="32">
-        <f t="shared" si="5"/>
+        <f>SUM(AE13:AE14)</f>
         <v>0</v>
       </c>
       <c r="AF15" s="32">
-        <f t="shared" si="5"/>
+        <f>SUM(AF13:AF14)</f>
         <v>0</v>
       </c>
       <c r="AG15" s="32">
-        <f t="shared" si="5"/>
+        <f>SUM(AG13:AG14)</f>
         <v>0</v>
       </c>
       <c r="AH15" s="32">
-        <f t="shared" si="5"/>
+        <f>SUM(AH13:AH14)</f>
         <v>0</v>
       </c>
       <c r="AI15" s="32">
-        <f t="shared" si="5"/>
+        <f>SUM(AI13:AI14)</f>
         <v>0</v>
       </c>
       <c r="AJ15" s="32">
-        <f t="shared" ref="AJ15:BO15" si="6">SUM(AJ13:AJ14)</f>
+        <f>SUM(AJ13:AJ14)</f>
         <v>0</v>
       </c>
       <c r="AK15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AK13:AK14)</f>
         <v>0</v>
       </c>
       <c r="AL15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AL13:AL14)</f>
         <v>0</v>
       </c>
       <c r="AM15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AM13:AM14)</f>
         <v>0</v>
       </c>
       <c r="AN15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AN13:AN14)</f>
         <v>0</v>
       </c>
       <c r="AO15" s="32">
-        <f t="shared" si="6"/>
-        <v>16041904.554294141</v>
+        <f>AO3*64.7%</f>
+        <v>16042365</v>
       </c>
       <c r="AP15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AP13:AP14)</f>
         <v>0</v>
       </c>
       <c r="AQ15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AQ13:AQ14)</f>
         <v>0</v>
       </c>
       <c r="AR15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AR13:AR14)</f>
         <v>0</v>
       </c>
       <c r="AS15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AS13:AS14)</f>
         <v>0</v>
       </c>
       <c r="AT15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AT13:AT14)</f>
         <v>0</v>
       </c>
       <c r="AU15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AU13:AU14)</f>
         <v>0</v>
       </c>
       <c r="AV15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AV13:AV14)</f>
         <v>0</v>
       </c>
       <c r="AW15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AW13:AW14)</f>
         <v>0</v>
       </c>
       <c r="AX15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AX13:AX14)</f>
         <v>0</v>
       </c>
       <c r="AY15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AY13:AY14)</f>
         <v>0</v>
       </c>
       <c r="AZ15" s="32">
-        <f t="shared" si="6"/>
+        <f>SUM(AZ13:AZ14)</f>
         <v>0</v>
       </c>
       <c r="BA15" s="32">
-        <f t="shared" si="6"/>
-        <v>16041904.554294141</v>
-      </c>
-      <c r="BB15" s="41">
-        <f t="shared" si="4"/>
-        <v>50138058.816287197</v>
+        <f>BA3*64.7%</f>
+        <v>16042365</v>
+      </c>
+      <c r="BB15" s="32">
+        <f>BB3*64.7%</f>
+        <v>50139316.085166655</v>
       </c>
       <c r="BC15" s="41"/>
       <c r="BD15" s="42"/>
@@ -11860,7 +11881,7 @@
         <v>8522586.4457058571</v>
       </c>
       <c r="BB16" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23271327.268883705</v>
       </c>
       <c r="BC16" s="43"/>
@@ -11892,248 +11913,248 @@
       <c r="CC16" s="43"/>
       <c r="CD16" s="43"/>
     </row>
-    <row r="17" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:82" s="107" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="106" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="107" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="107" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="32">
-        <f>('Fluxo de pagamentos'!J7+'Fluxo de pagamentos'!J8)*35.3%</f>
-        <v>4085692.8718100004</v>
-      </c>
-      <c r="E17" s="32">
-        <f>('Fluxo de pagamentos'!K7+'Fluxo de pagamentos'!K8)*35.3%</f>
-        <v>1059000</v>
-      </c>
-      <c r="F17" s="32">
-        <f>('Fluxo de pagamentos'!L7+'Fluxo de pagamentos'!L8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="32">
-        <f>('Fluxo de pagamentos'!M7+'Fluxo de pagamentos'!M8)*35.3%</f>
+      <c r="D17" s="108">
+        <f>D18-D16</f>
+        <v>4084435.602930557</v>
+      </c>
+      <c r="E17" s="108">
+        <f t="shared" ref="E17:BB17" si="3">E18-E16</f>
+        <v>1058753.4907125859</v>
+      </c>
+      <c r="F17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="108">
+        <f t="shared" si="3"/>
         <v>272521.32676999999</v>
       </c>
-      <c r="H17" s="32">
-        <f>('Fluxo de pagamentos'!N7+'Fluxo de pagamentos'!N8)*35.3%</f>
+      <c r="H17" s="108">
+        <f t="shared" si="3"/>
         <v>300764.26725999994</v>
       </c>
-      <c r="I17" s="32">
-        <f>('Fluxo de pagamentos'!O7+'Fluxo de pagamentos'!O8)*35.3%</f>
+      <c r="I17" s="108">
+        <f t="shared" si="3"/>
         <v>272521.32676999999</v>
       </c>
-      <c r="J17" s="32">
-        <f>('Fluxo de pagamentos'!P7+'Fluxo de pagamentos'!P8)*35.3%</f>
+      <c r="J17" s="108">
+        <f t="shared" si="3"/>
         <v>190659.92782999997</v>
       </c>
-      <c r="K17" s="32">
-        <f>('Fluxo de pagamentos'!Q7+'Fluxo de pagamentos'!Q8)*35.3%</f>
+      <c r="K17" s="108">
+        <f t="shared" si="3"/>
         <v>162425.63583999997</v>
       </c>
-      <c r="L17" s="32">
-        <f>('Fluxo de pagamentos'!R7+'Fluxo de pagamentos'!R8)*35.3%</f>
+      <c r="L17" s="108">
+        <f t="shared" si="3"/>
         <v>189847.46656</v>
       </c>
-      <c r="M17" s="32">
-        <f>('Fluxo de pagamentos'!S7+'Fluxo de pagamentos'!S8)*35.3%</f>
+      <c r="M17" s="108">
+        <f t="shared" si="3"/>
         <v>156602.22308</v>
       </c>
-      <c r="N17" s="32">
-        <f>('Fluxo de pagamentos'!T7+'Fluxo de pagamentos'!T8)*35.3%</f>
+      <c r="N17" s="108">
+        <f t="shared" si="3"/>
         <v>184277.09125999999</v>
       </c>
-      <c r="O17" s="32">
-        <f>('Fluxo de pagamentos'!U7+'Fluxo de pagamentos'!U8)*35.3%</f>
+      <c r="O17" s="108">
+        <f t="shared" si="3"/>
         <v>72183.099100000007</v>
       </c>
-      <c r="P17" s="32">
-        <f>('Fluxo de pagamentos'!V7+'Fluxo de pagamentos'!V8)*35.3%</f>
+      <c r="P17" s="108">
+        <f t="shared" si="3"/>
         <v>72186.03959</v>
       </c>
-      <c r="Q17" s="32">
-        <f>('Fluxo de pagamentos'!W7+'Fluxo de pagamentos'!W8)*35.3%</f>
+      <c r="Q17" s="108">
+        <f t="shared" si="3"/>
         <v>72183.099100000007</v>
       </c>
-      <c r="R17" s="32">
-        <f>('Fluxo de pagamentos'!X7+'Fluxo de pagamentos'!X8)*35.3%</f>
+      <c r="R17" s="108">
+        <f t="shared" si="3"/>
         <v>72186.03959</v>
       </c>
-      <c r="S17" s="32">
-        <f>('Fluxo de pagamentos'!Y7+'Fluxo de pagamentos'!Y8)*35.3%</f>
+      <c r="S17" s="108">
+        <f t="shared" si="3"/>
         <v>71236.091879999993</v>
       </c>
-      <c r="T17" s="32">
-        <f>('Fluxo de pagamentos'!Z7+'Fluxo de pagamentos'!Z8)*35.3%</f>
+      <c r="T17" s="108">
+        <f t="shared" si="3"/>
         <v>71239.046489999993</v>
       </c>
-      <c r="U17" s="32">
-        <f>('Fluxo de pagamentos'!AA7+'Fluxo de pagamentos'!AA8)*35.3%</f>
+      <c r="U17" s="108">
+        <f t="shared" si="3"/>
         <v>30055.687269999999</v>
       </c>
-      <c r="V17" s="32">
-        <f>('Fluxo de pagamentos'!AB7+'Fluxo de pagamentos'!AB8)*35.3%</f>
+      <c r="V17" s="108">
+        <f t="shared" si="3"/>
         <v>30055.687269999999</v>
       </c>
-      <c r="W17" s="32">
-        <f>('Fluxo de pagamentos'!AC7+'Fluxo de pagamentos'!AC8)*35.3%</f>
+      <c r="W17" s="108">
+        <f t="shared" si="3"/>
         <v>29182.326440000001</v>
       </c>
-      <c r="X17" s="32">
-        <f>('Fluxo de pagamentos'!AD7+'Fluxo de pagamentos'!AD8)*35.3%</f>
+      <c r="X17" s="108">
+        <f t="shared" si="3"/>
         <v>28346.496569999999</v>
       </c>
-      <c r="Y17" s="32">
-        <f>('Fluxo de pagamentos'!AE7+'Fluxo de pagamentos'!AE8)*35.3%</f>
+      <c r="Y17" s="108">
+        <f t="shared" si="3"/>
         <v>28346.496569999999</v>
       </c>
-      <c r="Z17" s="32">
-        <f>('Fluxo de pagamentos'!AF7+'Fluxo de pagamentos'!AF8)*35.3%</f>
+      <c r="Z17" s="108">
+        <f t="shared" si="3"/>
         <v>28346.496569999999</v>
       </c>
-      <c r="AA17" s="32">
-        <f>('Fluxo de pagamentos'!AG7+'Fluxo de pagamentos'!AG8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AB17" s="32">
-        <f>('Fluxo de pagamentos'!AH7+'Fluxo de pagamentos'!AH8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AC17" s="32">
-        <f>('Fluxo de pagamentos'!AI7+'Fluxo de pagamentos'!AI8)*35.3%</f>
-        <v>230509</v>
-      </c>
-      <c r="AD17" s="32">
-        <f>('Fluxo de pagamentos'!AJ7+'Fluxo de pagamentos'!AJ8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="32">
-        <f>('Fluxo de pagamentos'!AK7+'Fluxo de pagamentos'!AK8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AF17" s="32">
-        <f>('Fluxo de pagamentos'!AL7+'Fluxo de pagamentos'!AL8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AG17" s="32">
-        <f>('Fluxo de pagamentos'!AM7+'Fluxo de pagamentos'!AM8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AH17" s="32">
-        <f>('Fluxo de pagamentos'!AN7+'Fluxo de pagamentos'!AN8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AI17" s="32">
-        <f>('Fluxo de pagamentos'!AO7+'Fluxo de pagamentos'!AO8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="32">
-        <f>('Fluxo de pagamentos'!AP7+'Fluxo de pagamentos'!AP8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AK17" s="32">
-        <f>('Fluxo de pagamentos'!AQ7+'Fluxo de pagamentos'!AQ8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AL17" s="32">
-        <f>('Fluxo de pagamentos'!AR7+'Fluxo de pagamentos'!AR8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AM17" s="32">
-        <f>('Fluxo de pagamentos'!AS7+'Fluxo de pagamentos'!AS8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AN17" s="32">
-        <f>('Fluxo de pagamentos'!AT7+'Fluxo de pagamentos'!AT8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AO17" s="32">
-        <f>('Fluxo de pagamentos'!AU7+'Fluxo de pagamentos'!AU8)*35.3%</f>
-        <v>230509</v>
-      </c>
-      <c r="AP17" s="32">
-        <f>('Fluxo de pagamentos'!AV7+'Fluxo de pagamentos'!AV8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="32">
-        <f>('Fluxo de pagamentos'!AW7+'Fluxo de pagamentos'!AW8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AR17" s="32">
-        <f>('Fluxo de pagamentos'!AX7+'Fluxo de pagamentos'!AX8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AS17" s="32">
-        <f>('Fluxo de pagamentos'!AY7+'Fluxo de pagamentos'!AY8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AT17" s="32">
-        <f>('Fluxo de pagamentos'!AZ7+'Fluxo de pagamentos'!AZ8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AU17" s="32">
-        <f>('Fluxo de pagamentos'!BA7+'Fluxo de pagamentos'!BA8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AV17" s="32">
-        <f>('Fluxo de pagamentos'!BB7+'Fluxo de pagamentos'!BB8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AW17" s="32">
-        <f>('Fluxo de pagamentos'!BC7+'Fluxo de pagamentos'!BC8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AX17" s="32">
-        <f>('Fluxo de pagamentos'!BD7+'Fluxo de pagamentos'!BD8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AY17" s="32">
-        <f>('Fluxo de pagamentos'!BE7+'Fluxo de pagamentos'!BE8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="32">
-        <f>('Fluxo de pagamentos'!BF7+'Fluxo de pagamentos'!BF8)*35.3%</f>
-        <v>0</v>
-      </c>
-      <c r="BA17" s="32">
-        <f>('Fluxo de pagamentos'!BG7+'Fluxo de pagamentos'!BG8)*35.3%</f>
-        <v>230509</v>
-      </c>
-      <c r="BB17" s="41">
-        <f t="shared" si="4"/>
-        <v>4085692.8718100009</v>
-      </c>
-      <c r="BC17" s="43"/>
-      <c r="BD17" s="42"/>
-      <c r="BE17" s="43"/>
-      <c r="BF17" s="43"/>
-      <c r="BG17" s="43"/>
-      <c r="BH17" s="43"/>
-      <c r="BI17" s="43"/>
-      <c r="BJ17" s="43"/>
-      <c r="BK17" s="43"/>
-      <c r="BL17" s="43"/>
-      <c r="BM17" s="43"/>
-      <c r="BN17" s="43"/>
-      <c r="BO17" s="43"/>
-      <c r="BP17" s="43"/>
-      <c r="BQ17" s="43"/>
-      <c r="BR17" s="43"/>
-      <c r="BS17" s="43"/>
-      <c r="BT17" s="43"/>
-      <c r="BU17" s="43"/>
-      <c r="BV17" s="43"/>
-      <c r="BW17" s="43"/>
-      <c r="BX17" s="43"/>
-      <c r="BY17" s="43"/>
-      <c r="BZ17" s="43"/>
-      <c r="CA17" s="43"/>
-      <c r="CB17" s="43"/>
-      <c r="CC17" s="43"/>
-      <c r="CD17" s="43"/>
+      <c r="AA17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="108">
+        <f t="shared" si="3"/>
+        <v>230419.13181968452</v>
+      </c>
+      <c r="AD17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO17" s="108">
+        <f t="shared" si="3"/>
+        <v>230048.55429414287</v>
+      </c>
+      <c r="AP17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AS17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AT17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA17" s="108">
+        <f t="shared" si="3"/>
+        <v>230048.55429414287</v>
+      </c>
+      <c r="BB17" s="108">
+        <f t="shared" si="3"/>
+        <v>4084435.602930557</v>
+      </c>
+      <c r="BC17" s="111"/>
+      <c r="BD17" s="110"/>
+      <c r="BE17" s="111"/>
+      <c r="BF17" s="111"/>
+      <c r="BG17" s="111"/>
+      <c r="BH17" s="111"/>
+      <c r="BI17" s="111"/>
+      <c r="BJ17" s="111"/>
+      <c r="BK17" s="111"/>
+      <c r="BL17" s="111"/>
+      <c r="BM17" s="111"/>
+      <c r="BN17" s="111"/>
+      <c r="BO17" s="111"/>
+      <c r="BP17" s="111"/>
+      <c r="BQ17" s="111"/>
+      <c r="BR17" s="111"/>
+      <c r="BS17" s="111"/>
+      <c r="BT17" s="111"/>
+      <c r="BU17" s="111"/>
+      <c r="BV17" s="111"/>
+      <c r="BW17" s="111"/>
+      <c r="BX17" s="111"/>
+      <c r="BY17" s="111"/>
+      <c r="BZ17" s="111"/>
+      <c r="CA17" s="111"/>
+      <c r="CB17" s="111"/>
+      <c r="CC17" s="111"/>
+      <c r="CD17" s="111"/>
     </row>
     <row r="18" spans="1:82" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="31" t="s">
@@ -12146,208 +12167,208 @@
         <v>51</v>
       </c>
       <c r="D18" s="32">
-        <f t="shared" ref="D18:AI18" si="7">SUM(D16:D17)</f>
-        <v>27357020.140693706</v>
+        <f>D3*35.3%</f>
+        <v>27355762.871814262</v>
       </c>
       <c r="E18" s="32">
-        <f t="shared" si="7"/>
-        <v>5621745.8024486918</v>
+        <f t="shared" ref="E18:BB18" si="4">E3*35.3%</f>
+        <v>5621499.2931612777</v>
       </c>
       <c r="F18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>272521.32676999999</v>
       </c>
       <c r="H18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>300764.26725999994</v>
       </c>
       <c r="I18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>272521.32676999999</v>
       </c>
       <c r="J18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>190659.92782999997</v>
       </c>
       <c r="K18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>162425.63583999997</v>
       </c>
       <c r="L18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>189847.46656</v>
       </c>
       <c r="M18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>156602.22308</v>
       </c>
       <c r="N18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>184277.09125999999</v>
       </c>
       <c r="O18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>72183.099100000007</v>
       </c>
       <c r="P18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>72186.03959</v>
       </c>
       <c r="Q18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>72183.099100000007</v>
       </c>
       <c r="R18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>72186.03959</v>
       </c>
       <c r="S18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>71236.091879999993</v>
       </c>
       <c r="T18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>71239.046489999993</v>
       </c>
       <c r="U18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>30055.687269999999</v>
       </c>
       <c r="V18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>30055.687269999999</v>
       </c>
       <c r="W18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>29182.326440000001</v>
       </c>
       <c r="X18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>28346.496569999999</v>
       </c>
       <c r="Y18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>28346.496569999999</v>
       </c>
       <c r="Z18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>28346.496569999999</v>
       </c>
       <c r="AA18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC18" s="32">
-        <f t="shared" si="7"/>
-        <v>1893917.5750232993</v>
+        <f t="shared" si="4"/>
+        <v>1893827.7068429838</v>
       </c>
       <c r="AD18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AG18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AH18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AI18" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ18" s="32">
-        <f t="shared" ref="AJ18:BO18" si="8">SUM(AJ16:AJ17)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AL18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AM18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AN18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AO18" s="32">
-        <f t="shared" si="8"/>
-        <v>8753095.4457058571</v>
+        <f t="shared" si="4"/>
+        <v>8752635</v>
       </c>
       <c r="AP18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AQ18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AT18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AU18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AV18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AW18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AX18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AZ18" s="32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="BA18" s="32">
-        <f t="shared" si="8"/>
-        <v>8753095.4457058571</v>
-      </c>
-      <c r="BB18" s="41">
         <f t="shared" si="4"/>
-        <v>27357020.140693706</v>
+        <v>8752635</v>
+      </c>
+      <c r="BB18" s="32">
+        <f t="shared" si="4"/>
+        <v>27355762.871814262</v>
       </c>
       <c r="BC18" s="43"/>
       <c r="BD18" s="42"/>
@@ -12398,199 +12419,199 @@
         <v>28762280.73</v>
       </c>
       <c r="F19" s="30">
-        <f t="shared" ref="F19:BA19" si="9">F4</f>
+        <f>F4</f>
         <v>0</v>
       </c>
       <c r="G19" s="30">
-        <f t="shared" si="9"/>
+        <f>G4</f>
         <v>0</v>
       </c>
       <c r="H19" s="30">
-        <f t="shared" si="9"/>
+        <f>H4</f>
         <v>0</v>
       </c>
       <c r="I19" s="30">
-        <f t="shared" si="9"/>
+        <f>I4</f>
         <v>0</v>
       </c>
       <c r="J19" s="30">
-        <f t="shared" si="9"/>
+        <f>J4</f>
         <v>0</v>
       </c>
       <c r="K19" s="30">
-        <f t="shared" si="9"/>
+        <f>K4</f>
         <v>0</v>
       </c>
       <c r="L19" s="30">
-        <f t="shared" si="9"/>
+        <f>L4</f>
         <v>0</v>
       </c>
       <c r="M19" s="30">
-        <f t="shared" si="9"/>
+        <f>M4</f>
         <v>0</v>
       </c>
       <c r="N19" s="30">
-        <f t="shared" si="9"/>
+        <f>N4</f>
         <v>0</v>
       </c>
       <c r="O19" s="30">
-        <f t="shared" si="9"/>
+        <f>O4</f>
         <v>0</v>
       </c>
       <c r="P19" s="30">
-        <f t="shared" si="9"/>
+        <f>P4</f>
         <v>0</v>
       </c>
       <c r="Q19" s="30">
-        <f t="shared" si="9"/>
+        <f>Q4</f>
         <v>0</v>
       </c>
       <c r="R19" s="30">
-        <f t="shared" si="9"/>
+        <f>R4</f>
         <v>0</v>
       </c>
       <c r="S19" s="30">
-        <f t="shared" si="9"/>
+        <f>S4</f>
         <v>0</v>
       </c>
       <c r="T19" s="30">
-        <f t="shared" si="9"/>
+        <f>T4</f>
         <v>0</v>
       </c>
       <c r="U19" s="30">
-        <f t="shared" si="9"/>
+        <f>U4</f>
         <v>0</v>
       </c>
       <c r="V19" s="30">
-        <f t="shared" si="9"/>
+        <f>V4</f>
         <v>0</v>
       </c>
       <c r="W19" s="30">
-        <f t="shared" si="9"/>
+        <f>W4</f>
         <v>0</v>
       </c>
       <c r="X19" s="30">
-        <f t="shared" si="9"/>
+        <f>X4</f>
         <v>0</v>
       </c>
       <c r="Y19" s="30">
-        <f t="shared" si="9"/>
+        <f>Y4</f>
         <v>0</v>
       </c>
       <c r="Z19" s="30">
-        <f t="shared" si="9"/>
+        <f>Z4</f>
         <v>0</v>
       </c>
       <c r="AA19" s="30">
-        <f t="shared" si="9"/>
+        <f>AA4</f>
         <v>0</v>
       </c>
       <c r="AB19" s="30">
-        <f t="shared" si="9"/>
+        <f>AB4</f>
         <v>0</v>
       </c>
       <c r="AC19" s="30">
-        <f t="shared" si="9"/>
+        <f>AC4</f>
         <v>0</v>
       </c>
       <c r="AD19" s="30">
-        <f t="shared" si="9"/>
+        <f>AD4</f>
         <v>0</v>
       </c>
       <c r="AE19" s="30">
-        <f t="shared" si="9"/>
+        <f>AE4</f>
         <v>0</v>
       </c>
       <c r="AF19" s="30">
-        <f t="shared" si="9"/>
+        <f>AF4</f>
         <v>0</v>
       </c>
       <c r="AG19" s="30">
-        <f t="shared" si="9"/>
+        <f>AG4</f>
         <v>0</v>
       </c>
       <c r="AH19" s="30">
-        <f t="shared" si="9"/>
+        <f>AH4</f>
         <v>0</v>
       </c>
       <c r="AI19" s="30">
-        <f t="shared" si="9"/>
+        <f>AI4</f>
         <v>0</v>
       </c>
       <c r="AJ19" s="30">
-        <f t="shared" si="9"/>
+        <f>AJ4</f>
         <v>0</v>
       </c>
       <c r="AK19" s="30">
-        <f t="shared" si="9"/>
+        <f>AK4</f>
         <v>0</v>
       </c>
       <c r="AL19" s="30">
-        <f t="shared" si="9"/>
+        <f>AL4</f>
         <v>0</v>
       </c>
       <c r="AM19" s="30">
-        <f t="shared" si="9"/>
+        <f>AM4</f>
         <v>0</v>
       </c>
       <c r="AN19" s="30">
-        <f t="shared" si="9"/>
+        <f>AN4</f>
         <v>0</v>
       </c>
       <c r="AO19" s="30">
-        <f t="shared" si="9"/>
+        <f>AO4</f>
         <v>0</v>
       </c>
       <c r="AP19" s="30">
-        <f t="shared" si="9"/>
+        <f>AP4</f>
         <v>0</v>
       </c>
       <c r="AQ19" s="30">
-        <f t="shared" si="9"/>
+        <f>AQ4</f>
         <v>0</v>
       </c>
       <c r="AR19" s="30">
-        <f t="shared" si="9"/>
+        <f>AR4</f>
         <v>0</v>
       </c>
       <c r="AS19" s="30">
-        <f t="shared" si="9"/>
+        <f>AS4</f>
         <v>0</v>
       </c>
       <c r="AT19" s="30">
-        <f t="shared" si="9"/>
+        <f>AT4</f>
         <v>0</v>
       </c>
       <c r="AU19" s="30">
-        <f t="shared" si="9"/>
+        <f>AU4</f>
         <v>0</v>
       </c>
       <c r="AV19" s="30">
-        <f t="shared" si="9"/>
+        <f>AV4</f>
         <v>0</v>
       </c>
       <c r="AW19" s="30">
-        <f t="shared" si="9"/>
+        <f>AW4</f>
         <v>0</v>
       </c>
       <c r="AX19" s="30">
-        <f t="shared" si="9"/>
+        <f>AX4</f>
         <v>0</v>
       </c>
       <c r="AY19" s="30">
-        <f t="shared" si="9"/>
+        <f>AY4</f>
         <v>0</v>
       </c>
       <c r="AZ19" s="30">
-        <f t="shared" si="9"/>
+        <f>AZ4</f>
         <v>0</v>
       </c>
       <c r="BA19" s="30">
-        <f t="shared" si="9"/>
+        <f>BA4</f>
         <v>0</v>
       </c>
       <c r="BB19" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>28762280.73</v>
       </c>
       <c r="BC19" s="28"/>
@@ -12834,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="BB20" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>11239020</v>
       </c>
     </row>
@@ -13050,7 +13071,7 @@
         <v>0</v>
       </c>
       <c r="BB21" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>44560980.313019082</v>
       </c>
       <c r="BC21" s="30">
@@ -13270,7 +13291,7 @@
         <v>0</v>
       </c>
       <c r="BB22" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>3242640</v>
       </c>
     </row>
@@ -13279,207 +13300,207 @@
         <v>84</v>
       </c>
       <c r="D23" s="29">
-        <f t="shared" ref="D23:AI23" si="10">SUM(D20:D22)</f>
+        <f t="shared" ref="D23:BB23" si="5">SUM(D20:D22)</f>
         <v>59042640.313019089</v>
       </c>
       <c r="E23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>21432792.093905725</v>
       </c>
       <c r="F23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1525903.83</v>
       </c>
       <c r="G23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1525903.83</v>
       </c>
       <c r="H23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1525903.83</v>
       </c>
       <c r="I23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1475497.5066666666</v>
       </c>
       <c r="J23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1475497.5066666666</v>
       </c>
       <c r="K23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1475497.5066666666</v>
       </c>
       <c r="L23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1565091.5666666667</v>
       </c>
       <c r="M23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1565091.5666666667</v>
       </c>
       <c r="N23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1565091.5666666667</v>
       </c>
       <c r="O23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1861762.523333333</v>
       </c>
       <c r="P23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1861762.523333333</v>
       </c>
       <c r="Q23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1861762.523333333</v>
       </c>
       <c r="R23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>18325081.939113364</v>
       </c>
       <c r="AD23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AH23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AI23" s="29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AJ23" s="29">
-        <f t="shared" ref="AJ23:BO23" si="11">SUM(AJ20:AJ22)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AK23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AL23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AM23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AN23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AO23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AP23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AQ23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AR23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AS23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AT23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AU23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AV23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AW23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AX23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AZ23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="BA23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="BB23" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>59042640.313019082</v>
       </c>
     </row>
@@ -13492,204 +13513,204 @@
         <v>165300000</v>
       </c>
       <c r="E24" s="29">
-        <f t="shared" ref="E24:BA24" si="12">E15+E18+E19+E23</f>
+        <f t="shared" ref="E24:BA24" si="6">E15+E18+E19+E23</f>
         <v>66119999.999999993</v>
       </c>
       <c r="F24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1525903.83</v>
       </c>
       <c r="G24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2297918.92</v>
       </c>
       <c r="H24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2377927.25</v>
       </c>
       <c r="I24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2247512.5966666667</v>
       </c>
       <c r="J24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2015610.6166666667</v>
       </c>
       <c r="K24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>1935626.7866666666</v>
       </c>
       <c r="L24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2102903.0866666669</v>
       </c>
       <c r="M24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2008723.9266666668</v>
       </c>
       <c r="N24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2087122.9866666668</v>
       </c>
       <c r="O24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2066247.2233333329</v>
       </c>
       <c r="P24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2066255.553333333</v>
       </c>
       <c r="Q24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2066247.2233333329</v>
       </c>
       <c r="R24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>204493.03</v>
       </c>
       <c r="S24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>201801.96</v>
       </c>
       <c r="T24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>201810.33</v>
       </c>
       <c r="U24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>85143.59</v>
       </c>
       <c r="V24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>85143.59</v>
       </c>
       <c r="W24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>82669.48000000001</v>
       </c>
       <c r="X24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>80301.69</v>
       </c>
       <c r="Y24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>80301.69</v>
       </c>
       <c r="Z24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>80301.69</v>
       </c>
       <c r="AA24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>23690032.950000003</v>
       </c>
       <c r="AD24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AH24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AI24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AJ24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AL24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AM24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AN24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AO24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>24795000</v>
       </c>
       <c r="AP24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA24" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>24795000</v>
       </c>
       <c r="BB24" s="30">
-        <f>BB15+BB18+BB19+BB23</f>
-        <v>165300000</v>
+        <f>SUM(E24:BA24)</f>
+        <v>165299999.99999997</v>
       </c>
       <c r="BC24" s="30"/>
     </row>
@@ -13779,10 +13800,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:23" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="50"/>
+      <c r="B2" s="77"/>
       <c r="C2" s="34" t="s">
         <v>79</v>
       </c>
@@ -13843,13 +13864,13 @@
       <c r="V2" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="W2" s="48" t="s">
+      <c r="W2" s="75" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
       <c r="C3" s="28">
         <v>46295</v>
       </c>
@@ -13910,9 +13931,9 @@
       <c r="V3" s="28">
         <v>46873</v>
       </c>
-      <c r="W3" s="48"/>
-    </row>
-    <row r="4" spans="1:23" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="W3" s="75"/>
+    </row>
+    <row r="4" spans="1:23" s="33" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="44" t="s">
         <v>98</v>
       </c>
@@ -14925,10 +14946,10 @@
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="49"/>
+      <c r="B15" s="76"/>
       <c r="C15" s="29">
         <f t="shared" ref="C15:V15" si="1">C5+SUM(C7:C11)+C13</f>
         <v>116960.02</v>
@@ -15015,10 +15036,10 @@
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="49"/>
+      <c r="B16" s="76"/>
       <c r="C16" s="30">
         <f t="shared" ref="C16:V16" si="2">C6+C12+C14</f>
         <v>655055.06999999995</v>
@@ -15105,10 +15126,10 @@
       </c>
     </row>
     <row r="17" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A17" s="47" t="s">
+      <c r="A17" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="47"/>
+      <c r="B17" s="74"/>
       <c r="C17" s="30">
         <f t="shared" ref="C17:V17" si="3">C4*64.7%</f>
         <v>499493.76322999998</v>
@@ -15195,10 +15216,10 @@
       </c>
     </row>
     <row r="18" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="B18" s="47"/>
+      <c r="B18" s="74"/>
       <c r="C18" s="30">
         <f t="shared" ref="C18:V18" si="4">C4*35.3%</f>
         <v>272521.32676999999</v>
@@ -15285,8 +15306,8 @@
       </c>
     </row>
     <row r="19" spans="1:53" s="33" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="46"/>
-      <c r="B19" s="46"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="73"/>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
       <c r="E19" s="41"/>
@@ -15401,11 +15422,11 @@
       </c>
     </row>
     <row r="27" spans="1:53" ht="32" x14ac:dyDescent="0.2">
-      <c r="A27" s="102" t="s">
+      <c r="A27" s="71" t="s">
         <v>185</v>
       </c>
-      <c r="B27" s="102"/>
-      <c r="C27" s="101" t="s">
+      <c r="B27" s="71"/>
+      <c r="C27" s="68" t="s">
         <v>0</v>
       </c>
       <c r="D27" s="38" t="s">
@@ -15420,37 +15441,37 @@
       <c r="G27" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="H27" s="102" t="s">
+      <c r="H27" s="71" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A28" s="102"/>
-      <c r="B28" s="102"/>
+      <c r="A28" s="71"/>
+      <c r="B28" s="71"/>
       <c r="C28" s="39"/>
-      <c r="D28" s="103">
+      <c r="D28" s="69">
         <v>46230</v>
       </c>
-      <c r="E28" s="75">
+      <c r="E28" s="57">
         <f>'Fluxo de pagamentos'!AI2</f>
         <v>46935</v>
       </c>
-      <c r="F28" s="104">
+      <c r="F28" s="70">
         <f>'Fluxo de pagamentos'!AU2</f>
         <v>47300</v>
       </c>
-      <c r="G28" s="104">
+      <c r="G28" s="70">
         <f>'Fluxo de pagamentos'!BG2</f>
         <v>47665</v>
       </c>
-      <c r="H28" s="102"/>
+      <c r="H28" s="71"/>
     </row>
     <row r="29" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A29" s="39" t="s">
         <v>0</v>
       </c>
       <c r="B29" s="39"/>
-      <c r="C29" s="97">
+      <c r="C29" s="66">
         <f>'Fluxo de pagamentos'!J7</f>
         <v>4959000</v>
       </c>
@@ -15527,23 +15548,23 @@
       <c r="B30" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="C30" s="97">
+      <c r="C30" s="66">
         <f>C29*64.7%</f>
         <v>3208473</v>
       </c>
-      <c r="D30" s="97">
+      <c r="D30" s="66">
         <f>D29*64.7%</f>
         <v>1941000</v>
       </c>
-      <c r="E30" s="97">
+      <c r="E30" s="66">
         <f>E29*64.7%</f>
         <v>422491</v>
       </c>
-      <c r="F30" s="97">
+      <c r="F30" s="66">
         <f>F29*64.7%</f>
         <v>422491</v>
       </c>
-      <c r="G30" s="97">
+      <c r="G30" s="66">
         <f>G29*64.7%</f>
         <v>422491</v>
       </c>
@@ -15604,23 +15625,23 @@
       <c r="B31" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="C31" s="97">
+      <c r="C31" s="66">
         <f>C29*35.3%</f>
         <v>1750527</v>
       </c>
-      <c r="D31" s="97">
+      <c r="D31" s="66">
         <f>D29*35.3%</f>
         <v>1059000</v>
       </c>
-      <c r="E31" s="97">
+      <c r="E31" s="66">
         <f>E29*35.3%</f>
         <v>230509</v>
       </c>
-      <c r="F31" s="97">
+      <c r="F31" s="66">
         <f>F29*35.3%</f>
         <v>230509</v>
       </c>
-      <c r="G31" s="97">
+      <c r="G31" s="66">
         <f>G29*35.3%</f>
         <v>230509</v>
       </c>
@@ -15675,378 +15696,378 @@
       <c r="BA31" s="30"/>
     </row>
     <row r="34" spans="3:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C34" s="100" t="s">
+      <c r="C34" s="72" t="s">
         <v>183</v>
       </c>
-      <c r="D34" s="100"/>
-      <c r="F34" s="100" t="s">
+      <c r="D34" s="72"/>
+      <c r="F34" s="72" t="s">
         <v>184</v>
       </c>
-      <c r="G34" s="100"/>
+      <c r="G34" s="72"/>
     </row>
     <row r="35" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C35" s="101" t="s">
+      <c r="C35" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="101" t="s">
+      <c r="D35" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="101" t="s">
+      <c r="F35" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="G35" s="101" t="s">
+      <c r="G35" s="68" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="36" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C36" s="75">
+      <c r="C36" s="57">
         <v>46295</v>
       </c>
-      <c r="D36" s="97">
+      <c r="D36" s="66">
         <f>C17</f>
         <v>499493.76322999998</v>
       </c>
-      <c r="F36" s="75">
+      <c r="F36" s="57">
         <v>46295</v>
       </c>
-      <c r="G36" s="97">
+      <c r="G36" s="66">
         <f>C18</f>
         <v>272521.32676999999</v>
       </c>
     </row>
     <row r="37" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C37" s="75">
+      <c r="C37" s="57">
         <v>46326</v>
       </c>
-      <c r="D37" s="97">
+      <c r="D37" s="66">
         <f>D17</f>
         <v>551259.15273999993</v>
       </c>
-      <c r="F37" s="75">
+      <c r="F37" s="57">
         <v>46326</v>
       </c>
-      <c r="G37" s="97">
+      <c r="G37" s="66">
         <f>D18</f>
         <v>300764.26725999994</v>
       </c>
     </row>
     <row r="38" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C38" s="75">
+      <c r="C38" s="57">
         <v>46356</v>
       </c>
-      <c r="D38" s="97">
+      <c r="D38" s="66">
         <f>E17</f>
         <v>499493.76322999998</v>
       </c>
-      <c r="F38" s="75">
+      <c r="F38" s="57">
         <v>46356</v>
       </c>
-      <c r="G38" s="97">
+      <c r="G38" s="66">
         <f>E18</f>
         <v>272521.32676999999</v>
       </c>
     </row>
     <row r="39" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C39" s="75">
+      <c r="C39" s="57">
         <v>46387</v>
       </c>
-      <c r="D39" s="97">
+      <c r="D39" s="66">
         <f>F17</f>
         <v>349453.18216999999</v>
       </c>
-      <c r="F39" s="75">
+      <c r="F39" s="57">
         <v>46387</v>
       </c>
-      <c r="G39" s="97">
+      <c r="G39" s="66">
         <f>F18</f>
         <v>190659.92782999997</v>
       </c>
     </row>
     <row r="40" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C40" s="75">
+      <c r="C40" s="57">
         <v>46418</v>
       </c>
-      <c r="D40" s="97">
+      <c r="D40" s="66">
         <f>G17</f>
         <v>297703.64415999997</v>
       </c>
-      <c r="F40" s="75">
+      <c r="F40" s="57">
         <v>46418</v>
       </c>
-      <c r="G40" s="97">
+      <c r="G40" s="66">
         <f>G18</f>
         <v>162425.63583999997</v>
       </c>
     </row>
     <row r="41" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C41" s="75">
+      <c r="C41" s="57">
         <v>46446</v>
       </c>
-      <c r="D41" s="97">
+      <c r="D41" s="66">
         <f>H17</f>
         <v>347964.05344000005</v>
       </c>
-      <c r="F41" s="75">
+      <c r="F41" s="57">
         <v>46446</v>
       </c>
-      <c r="G41" s="97">
+      <c r="G41" s="66">
         <f>H18</f>
         <v>189847.46656</v>
       </c>
     </row>
     <row r="42" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C42" s="75">
+      <c r="C42" s="57">
         <v>46477</v>
       </c>
-      <c r="D42" s="97">
+      <c r="D42" s="66">
         <f>I17</f>
         <v>287030.13692000002</v>
       </c>
-      <c r="F42" s="75">
+      <c r="F42" s="57">
         <v>46477</v>
       </c>
-      <c r="G42" s="97">
+      <c r="G42" s="66">
         <f>I18</f>
         <v>156602.22308</v>
       </c>
     </row>
     <row r="43" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C43" s="75">
+      <c r="C43" s="57">
         <v>46507</v>
       </c>
-      <c r="D43" s="97">
+      <c r="D43" s="66">
         <f>J17</f>
         <v>337754.32874000003</v>
       </c>
-      <c r="F43" s="75">
+      <c r="F43" s="57">
         <v>46507</v>
       </c>
-      <c r="G43" s="97">
+      <c r="G43" s="66">
         <f>J18</f>
         <v>184277.09125999999</v>
       </c>
     </row>
     <row r="44" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C44" s="75">
+      <c r="C44" s="57">
         <v>46538</v>
       </c>
-      <c r="D44" s="97">
+      <c r="D44" s="66">
         <f>K17</f>
         <v>132301.60090000002</v>
       </c>
-      <c r="F44" s="75">
+      <c r="F44" s="57">
         <v>46538</v>
       </c>
-      <c r="G44" s="97">
+      <c r="G44" s="66">
         <f>K18</f>
         <v>72183.099100000007</v>
       </c>
     </row>
     <row r="45" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C45" s="75">
+      <c r="C45" s="57">
         <v>46568</v>
       </c>
-      <c r="D45" s="97">
+      <c r="D45" s="66">
         <f>L17</f>
         <v>132306.99041</v>
       </c>
-      <c r="F45" s="75">
+      <c r="F45" s="57">
         <v>46568</v>
       </c>
-      <c r="G45" s="97">
+      <c r="G45" s="66">
         <f>L18</f>
         <v>72186.03959</v>
       </c>
     </row>
     <row r="46" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C46" s="75">
+      <c r="C46" s="57">
         <v>46599</v>
       </c>
-      <c r="D46" s="97">
+      <c r="D46" s="66">
         <f>M17</f>
         <v>132301.60090000002</v>
       </c>
-      <c r="F46" s="75">
+      <c r="F46" s="57">
         <v>46599</v>
       </c>
-      <c r="G46" s="97">
+      <c r="G46" s="66">
         <f>M18</f>
         <v>72183.099100000007</v>
       </c>
     </row>
     <row r="47" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C47" s="75">
+      <c r="C47" s="57">
         <v>46630</v>
       </c>
-      <c r="D47" s="97">
+      <c r="D47" s="66">
         <f>N17</f>
         <v>132306.99041</v>
       </c>
-      <c r="F47" s="75">
+      <c r="F47" s="57">
         <v>46630</v>
       </c>
-      <c r="G47" s="97">
+      <c r="G47" s="66">
         <f>N18</f>
         <v>72186.03959</v>
       </c>
     </row>
     <row r="48" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C48" s="75">
+      <c r="C48" s="57">
         <v>46660</v>
       </c>
-      <c r="D48" s="97">
+      <c r="D48" s="66">
         <f>O17</f>
         <v>130565.86812</v>
       </c>
-      <c r="F48" s="75">
+      <c r="F48" s="57">
         <v>46660</v>
       </c>
-      <c r="G48" s="97">
+      <c r="G48" s="66">
         <f>O18</f>
         <v>71236.091879999993</v>
       </c>
     </row>
     <row r="49" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C49" s="75">
+      <c r="C49" s="57">
         <v>46691</v>
       </c>
-      <c r="D49" s="97">
+      <c r="D49" s="66">
         <f>P17</f>
         <v>130571.28350999999</v>
       </c>
-      <c r="F49" s="75">
+      <c r="F49" s="57">
         <v>46691</v>
       </c>
-      <c r="G49" s="97">
+      <c r="G49" s="66">
         <f>P18</f>
         <v>71239.046489999993</v>
       </c>
     </row>
     <row r="50" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C50" s="75">
+      <c r="C50" s="57">
         <v>46721</v>
       </c>
-      <c r="D50" s="97">
+      <c r="D50" s="66">
         <f>Q17</f>
         <v>55087.902730000002</v>
       </c>
-      <c r="F50" s="75">
+      <c r="F50" s="57">
         <v>46721</v>
       </c>
-      <c r="G50" s="97">
+      <c r="G50" s="66">
         <f>Q18</f>
         <v>30055.687269999999</v>
       </c>
     </row>
     <row r="51" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C51" s="75">
+      <c r="C51" s="57">
         <v>46752</v>
       </c>
-      <c r="D51" s="97">
+      <c r="D51" s="66">
         <f>R17</f>
         <v>55087.902730000002</v>
       </c>
-      <c r="F51" s="75">
+      <c r="F51" s="57">
         <v>46752</v>
       </c>
-      <c r="G51" s="97">
+      <c r="G51" s="66">
         <f>R18</f>
         <v>30055.687269999999</v>
       </c>
     </row>
     <row r="52" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C52" s="75">
+      <c r="C52" s="57">
         <v>46783</v>
       </c>
-      <c r="D52" s="97">
+      <c r="D52" s="66">
         <f>S17</f>
         <v>53487.153560000006</v>
       </c>
-      <c r="F52" s="75">
+      <c r="F52" s="57">
         <v>46783</v>
       </c>
-      <c r="G52" s="97">
+      <c r="G52" s="66">
         <f>S18</f>
         <v>29182.326440000001</v>
       </c>
     </row>
     <row r="53" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C53" s="75">
+      <c r="C53" s="57">
         <v>46812</v>
       </c>
-      <c r="D53" s="97">
+      <c r="D53" s="66">
         <f>T17</f>
         <v>51955.193430000007</v>
       </c>
-      <c r="F53" s="75">
+      <c r="F53" s="57">
         <v>46812</v>
       </c>
-      <c r="G53" s="97">
+      <c r="G53" s="66">
         <f>T18</f>
         <v>28346.496569999999</v>
       </c>
     </row>
     <row r="54" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C54" s="75">
+      <c r="C54" s="57">
         <v>46843</v>
       </c>
-      <c r="D54" s="97">
+      <c r="D54" s="66">
         <f>U17</f>
         <v>51955.193430000007</v>
       </c>
-      <c r="F54" s="75">
+      <c r="F54" s="57">
         <v>46843</v>
       </c>
-      <c r="G54" s="97">
+      <c r="G54" s="66">
         <f>U18</f>
         <v>28346.496569999999</v>
       </c>
     </row>
     <row r="55" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C55" s="75">
+      <c r="C55" s="57">
         <v>46873</v>
       </c>
-      <c r="D55" s="97">
+      <c r="D55" s="66">
         <f>V17</f>
         <v>51955.193430000007</v>
       </c>
-      <c r="F55" s="75">
+      <c r="F55" s="57">
         <v>46873</v>
       </c>
-      <c r="G55" s="97">
+      <c r="G55" s="66">
         <f>V18</f>
         <v>28346.496569999999</v>
       </c>
     </row>
     <row r="56" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C56" s="93" t="s">
+      <c r="C56" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="D56" s="97">
+      <c r="D56" s="66">
         <f>SUM(D36:D55)</f>
         <v>4280034.8981900001</v>
       </c>
-      <c r="F56" s="93" t="s">
+      <c r="F56" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="G56" s="97">
+      <c r="G56" s="66">
         <f>SUM(G36:G55)</f>
         <v>2335165.8718099995</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="W2:W3"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A2:B3"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -16063,144 +16084,144 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>186</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="78"/>
     </row>
     <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="48" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="51" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="49" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="51" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="51" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="51">
         <v>5120</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="50" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="51" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="51" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="51" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="79" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="88"/>
+      <c r="B14" s="79"/>
     </row>
     <row r="15" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="86"/>
+      <c r="B15" s="80"/>
     </row>
     <row r="16" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="85">
+      <c r="A16" s="61">
         <v>46326</v>
       </c>
-      <c r="B16" s="86"/>
+      <c r="B16" s="80"/>
     </row>
     <row r="17" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="81">
+      <c r="A17" s="60">
         <v>46418</v>
       </c>
-      <c r="B17" s="86"/>
+      <c r="B17" s="80"/>
     </row>
     <row r="18" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="81">
+      <c r="A18" s="60">
         <v>46507</v>
       </c>
-      <c r="B18" s="86"/>
+      <c r="B18" s="80"/>
     </row>
     <row r="19" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="81">
+      <c r="A19" s="60">
         <v>46599</v>
       </c>
-      <c r="B19" s="86"/>
+      <c r="B19" s="80"/>
     </row>
     <row r="20" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="81">
+      <c r="A20" s="60">
         <v>46965</v>
       </c>
-      <c r="B20" s="86"/>
+      <c r="B20" s="80"/>
     </row>
     <row r="21" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="81">
+      <c r="A21" s="60">
         <v>47330</v>
       </c>
-      <c r="B21" s="86"/>
+      <c r="B21" s="80"/>
     </row>
     <row r="22" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="81">
+      <c r="A22" s="60">
         <v>47695</v>
       </c>
-      <c r="B22" s="86"/>
+      <c r="B22" s="80"/>
     </row>
     <row r="23" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -16224,144 +16245,144 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="78"/>
     </row>
     <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="48" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="51" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="49" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="51" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="51" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="51">
         <v>5120</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="50" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="51" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="51" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="51" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="79" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="88"/>
+      <c r="B14" s="79"/>
     </row>
     <row r="15" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="86"/>
+      <c r="B15" s="80"/>
     </row>
     <row r="16" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="85">
+      <c r="A16" s="61">
         <v>46326</v>
       </c>
-      <c r="B16" s="86"/>
+      <c r="B16" s="80"/>
     </row>
     <row r="17" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="81">
+      <c r="A17" s="60">
         <v>46418</v>
       </c>
-      <c r="B17" s="86"/>
+      <c r="B17" s="80"/>
     </row>
     <row r="18" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="81">
+      <c r="A18" s="60">
         <v>46507</v>
       </c>
-      <c r="B18" s="86"/>
+      <c r="B18" s="80"/>
     </row>
     <row r="19" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="81">
+      <c r="A19" s="60">
         <v>46599</v>
       </c>
-      <c r="B19" s="86"/>
+      <c r="B19" s="80"/>
     </row>
     <row r="20" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="81">
+      <c r="A20" s="60">
         <v>46965</v>
       </c>
-      <c r="B20" s="86"/>
+      <c r="B20" s="80"/>
     </row>
     <row r="21" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="81">
+      <c r="A21" s="60">
         <v>47330</v>
       </c>
-      <c r="B21" s="86"/>
+      <c r="B21" s="80"/>
     </row>
     <row r="22" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="81">
+      <c r="A22" s="60">
         <v>47695</v>
       </c>
-      <c r="B22" s="86"/>
+      <c r="B22" s="80"/>
     </row>
     <row r="23" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -16386,297 +16407,292 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
     </row>
     <row r="3" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="66"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95"/>
     </row>
     <row r="4" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="83"/>
     </row>
     <row r="5" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="72"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="89"/>
     </row>
     <row r="6" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="83"/>
     </row>
     <row r="7" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="83"/>
     </row>
     <row r="8" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="67">
+      <c r="B8" s="81">
         <v>141</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="83"/>
     </row>
     <row r="9" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="92"/>
     </row>
     <row r="10" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="69"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="83"/>
     </row>
     <row r="11" spans="1:5" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="69"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="83"/>
     </row>
     <row r="12" spans="1:5" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83"/>
     </row>
     <row r="13" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="84" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="105"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="85"/>
     </row>
     <row r="14" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="B14" s="74" t="s">
+      <c r="B14" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="106"/>
-      <c r="E14" s="62"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="54"/>
     </row>
     <row r="15" spans="1:5" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="81">
+      <c r="A15" s="60">
         <v>46244</v>
       </c>
       <c r="B15" s="45">
         <v>46265</v>
       </c>
-      <c r="C15" s="79">
+      <c r="C15" s="58">
         <v>270220</v>
       </c>
-      <c r="D15" s="106"/>
-      <c r="E15" s="80"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="59"/>
     </row>
     <row r="16" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="81">
+      <c r="A16" s="60">
         <v>46275</v>
       </c>
       <c r="B16" s="45">
         <v>46295</v>
       </c>
-      <c r="C16" s="79">
+      <c r="C16" s="58">
         <v>270220</v>
       </c>
-      <c r="D16" s="106"/>
-      <c r="E16" s="80"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="59"/>
     </row>
     <row r="17" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="81">
+      <c r="A17" s="60">
         <v>46305</v>
       </c>
       <c r="B17" s="45">
         <v>46326</v>
       </c>
-      <c r="C17" s="79">
+      <c r="C17" s="58">
         <v>270220</v>
       </c>
-      <c r="D17" s="106"/>
-      <c r="E17" s="80"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="59"/>
     </row>
     <row r="18" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="81">
+      <c r="A18" s="60">
         <v>46336</v>
       </c>
       <c r="B18" s="45">
         <v>46356</v>
       </c>
-      <c r="C18" s="79">
+      <c r="C18" s="58">
         <v>270220</v>
       </c>
-      <c r="D18" s="106"/>
-      <c r="E18" s="80"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="59"/>
     </row>
     <row r="19" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="81">
+      <c r="A19" s="60">
         <v>46366</v>
       </c>
       <c r="B19" s="45">
         <v>46387</v>
       </c>
-      <c r="C19" s="79">
+      <c r="C19" s="58">
         <v>270220</v>
       </c>
-      <c r="D19" s="106"/>
-      <c r="E19" s="80"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="59"/>
     </row>
     <row r="20" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="81">
+      <c r="A20" s="60">
         <v>46397</v>
       </c>
       <c r="B20" s="45">
         <v>46418</v>
       </c>
-      <c r="C20" s="79">
+      <c r="C20" s="58">
         <v>270220</v>
       </c>
-      <c r="D20" s="106"/>
-      <c r="E20" s="80"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="59"/>
     </row>
     <row r="21" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="81">
+      <c r="A21" s="60">
         <v>46428</v>
       </c>
       <c r="B21" s="45">
         <v>46446</v>
       </c>
-      <c r="C21" s="79">
+      <c r="C21" s="58">
         <v>270220</v>
       </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="80"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="59"/>
     </row>
     <row r="22" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="81">
+      <c r="A22" s="60">
         <v>46456</v>
       </c>
       <c r="B22" s="45">
         <v>46477</v>
       </c>
-      <c r="C22" s="79">
+      <c r="C22" s="58">
         <v>270220</v>
       </c>
-      <c r="D22" s="106"/>
-      <c r="E22" s="80"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="59"/>
     </row>
     <row r="23" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="81">
+      <c r="A23" s="60">
         <v>46487</v>
       </c>
       <c r="B23" s="45">
         <v>46507</v>
       </c>
-      <c r="C23" s="79">
+      <c r="C23" s="58">
         <v>270220</v>
       </c>
-      <c r="D23" s="106"/>
-      <c r="E23" s="80"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="59"/>
     </row>
     <row r="24" spans="1:5" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="81">
+      <c r="A24" s="60">
         <v>46517</v>
       </c>
       <c r="B24" s="45">
         <v>46538</v>
       </c>
-      <c r="C24" s="79">
+      <c r="C24" s="58">
         <v>270220</v>
       </c>
-      <c r="D24" s="106"/>
-      <c r="E24" s="80"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="59"/>
     </row>
     <row r="25" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="81">
+      <c r="A25" s="60">
         <v>46548</v>
       </c>
       <c r="B25" s="45">
         <v>46568</v>
       </c>
-      <c r="C25" s="79">
+      <c r="C25" s="58">
         <v>270220</v>
       </c>
-      <c r="D25" s="106"/>
-      <c r="E25" s="80"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="59"/>
     </row>
     <row r="26" spans="1:5" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="81">
+      <c r="A26" s="60">
         <v>46578</v>
       </c>
       <c r="B26" s="45">
         <v>46599</v>
       </c>
-      <c r="C26" s="79">
+      <c r="C26" s="58">
         <v>270220</v>
       </c>
-      <c r="D26" s="106"/>
-      <c r="E26" s="80"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B4:D4"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:D26"/>
     <mergeCell ref="A2:D2"/>
@@ -16685,6 +16701,11 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B4:D4"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -16702,307 +16723,302 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
     </row>
     <row r="3" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="66"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95"/>
     </row>
     <row r="4" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="83"/>
     </row>
     <row r="5" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="87" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="72"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="89"/>
     </row>
     <row r="6" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="81" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="83"/>
     </row>
     <row r="7" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="83"/>
     </row>
     <row r="8" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="67">
+      <c r="B8" s="81">
         <v>141</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="83"/>
     </row>
     <row r="9" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="92"/>
     </row>
     <row r="10" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="69"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="83"/>
     </row>
     <row r="11" spans="1:5" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="81" t="s">
         <v>141</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="69"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="83"/>
     </row>
     <row r="12" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="81" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83"/>
     </row>
     <row r="13" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="79" t="s">
         <v>145</v>
       </c>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
     </row>
     <row r="14" spans="1:5" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="63" t="s">
+      <c r="A14" s="84" t="s">
         <v>149</v>
       </c>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="77"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="96"/>
     </row>
     <row r="15" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="76"/>
-      <c r="E15" s="62"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="54"/>
     </row>
     <row r="16" spans="1:5" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="81">
+      <c r="A16" s="60">
         <v>46244</v>
       </c>
       <c r="B16" s="45">
         <v>46265</v>
       </c>
-      <c r="C16" s="79">
+      <c r="C16" s="58">
         <v>936585</v>
       </c>
-      <c r="D16" s="76"/>
-      <c r="E16" s="80"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="59"/>
     </row>
     <row r="17" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="81">
+      <c r="A17" s="60">
         <v>46275</v>
       </c>
       <c r="B17" s="45">
         <v>46295</v>
       </c>
-      <c r="C17" s="79">
+      <c r="C17" s="58">
         <v>936585</v>
       </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="80"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="59"/>
     </row>
     <row r="18" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="81">
+      <c r="A18" s="60">
         <v>46305</v>
       </c>
       <c r="B18" s="45">
         <v>46326</v>
       </c>
-      <c r="C18" s="79">
+      <c r="C18" s="58">
         <v>936585</v>
       </c>
-      <c r="D18" s="76"/>
-      <c r="E18" s="80"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="59"/>
     </row>
     <row r="19" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="81">
+      <c r="A19" s="60">
         <v>46336</v>
       </c>
       <c r="B19" s="45">
         <v>46356</v>
       </c>
-      <c r="C19" s="79">
+      <c r="C19" s="58">
         <v>936585</v>
       </c>
-      <c r="D19" s="76"/>
-      <c r="E19" s="80"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="59"/>
     </row>
     <row r="20" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="81">
+      <c r="A20" s="60">
         <v>46366</v>
       </c>
       <c r="B20" s="45">
         <v>46387</v>
       </c>
-      <c r="C20" s="79">
+      <c r="C20" s="58">
         <v>936585</v>
       </c>
-      <c r="D20" s="76"/>
-      <c r="E20" s="80"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="59"/>
     </row>
     <row r="21" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="81">
+      <c r="A21" s="60">
         <v>46397</v>
       </c>
       <c r="B21" s="45">
         <v>46418</v>
       </c>
-      <c r="C21" s="79">
+      <c r="C21" s="58">
         <v>936585</v>
       </c>
-      <c r="D21" s="76"/>
-      <c r="E21" s="80"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="59"/>
     </row>
     <row r="22" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="81">
+      <c r="A22" s="60">
         <v>46428</v>
       </c>
       <c r="B22" s="45">
         <v>46446</v>
       </c>
-      <c r="C22" s="79">
+      <c r="C22" s="58">
         <v>936585</v>
       </c>
-      <c r="D22" s="76"/>
-      <c r="E22" s="80"/>
+      <c r="D22" s="97"/>
+      <c r="E22" s="59"/>
     </row>
     <row r="23" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="81">
+      <c r="A23" s="60">
         <v>46456</v>
       </c>
       <c r="B23" s="45">
         <v>46477</v>
       </c>
-      <c r="C23" s="79">
+      <c r="C23" s="58">
         <v>936585</v>
       </c>
-      <c r="D23" s="76"/>
-      <c r="E23" s="80"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="59"/>
     </row>
     <row r="24" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="81">
+      <c r="A24" s="60">
         <v>46487</v>
       </c>
       <c r="B24" s="45">
         <v>46507</v>
       </c>
-      <c r="C24" s="79">
+      <c r="C24" s="58">
         <v>936585</v>
       </c>
-      <c r="D24" s="76"/>
-      <c r="E24" s="80"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="59"/>
     </row>
     <row r="25" spans="1:5" s="44" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="81">
+      <c r="A25" s="60">
         <v>46517</v>
       </c>
       <c r="B25" s="45">
         <v>46538</v>
       </c>
-      <c r="C25" s="79">
+      <c r="C25" s="58">
         <v>936585</v>
       </c>
-      <c r="D25" s="76"/>
-      <c r="E25" s="80"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="59"/>
     </row>
     <row r="26" spans="1:5" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="81">
+      <c r="A26" s="60">
         <v>46548</v>
       </c>
       <c r="B26" s="45">
         <v>46568</v>
       </c>
-      <c r="C26" s="79">
+      <c r="C26" s="58">
         <v>936585</v>
       </c>
-      <c r="D26" s="76"/>
-      <c r="E26" s="80"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="59"/>
     </row>
     <row r="27" spans="1:5" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="81">
+      <c r="A27" s="60">
         <v>46578</v>
       </c>
       <c r="B27" s="45">
         <v>46599</v>
       </c>
-      <c r="C27" s="79">
+      <c r="C27" s="58">
         <v>936585</v>
       </c>
-      <c r="D27" s="76"/>
-      <c r="E27" s="80"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:D27"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B8:D8"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B13:D13"/>
@@ -17012,6 +17028,11 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:D27"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -17027,88 +17048,88 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="78"/>
     </row>
     <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="48" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="51" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="54">
+      <c r="B5" s="49">
         <v>46230</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="51" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="51" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="51">
         <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="55">
+      <c r="B9" s="50">
         <v>21432792.09</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="51" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="51" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="33" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="51" t="s">
         <v>138</v>
       </c>
     </row>
@@ -17141,88 +17162,88 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="78"/>
     </row>
     <row r="3" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="48" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="51" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="54">
+      <c r="B5" s="49">
         <v>46230</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="51" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="51" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="51">
         <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="55">
+      <c r="B9" s="50">
         <v>28762281</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="51" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="33" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="51" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="33" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="51" t="s">
         <v>134</v>
       </c>
     </row>
@@ -17254,15 +17275,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009BCAD43DEBE5F94985BAF5880255A369" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2fb35b598400d5f193579b3bf1feff08">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5a6c962e-89a5-491f-bc13-c4fa6b6d71f2" xmlns:ns4="8f7f4e79-e3ee-400b-8307-611f30480393" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8bbe51196fddd356df0d3ff3527ead97" ns3:_="" ns4:_="">
     <xsd:import namespace="5a6c962e-89a5-491f-bc13-c4fa6b6d71f2"/>
@@ -17507,6 +17519,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{408326D6-065C-406F-8763-8F7641131D26}">
   <ds:schemaRefs>
@@ -17525,14 +17546,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4ACE698-005D-404B-9AED-9E97E91093BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9842BADD-DE89-47D9-B611-88F6E4A2D1F9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17551,6 +17564,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4ACE698-005D-404B-9AED-9E97E91093BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4ba98965-3a24-460d-b0e1-6f272f1d0f46}" enabled="1" method="Privileged" siteId="{85b28421-d45a-4b07-889d-24b528c7f250}" removed="0"/>
